--- a/uploads/Plantilla.xlsx
+++ b/uploads/Plantilla.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Jhon\Vacunas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jhon\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267DE9B7-E019-4124-8745-16FB9DBCF969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DF0940-F840-4E25-8409-38A59ED67CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -967,7 +967,6 @@
   </cellStyleXfs>
   <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1079,9 +1078,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1089,13 +1085,17 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1132,6 +1132,18 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1153,11 +1165,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1165,15 +1174,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1300,6 +1300,24 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1336,28 +1354,10 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1369,29 +1369,29 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1690,102 +1690,102 @@
     <col min="15" max="15" width="6.140625" customWidth="1"/>
     <col min="16" max="16" width="6.28515625" customWidth="1"/>
     <col min="17" max="17" width="6.85546875" customWidth="1"/>
-    <col min="18" max="18" width="2.7109375" customWidth="1"/>
-    <col min="19" max="19" width="3" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.85546875" customWidth="1"/>
+    <col min="19" max="19" width="4.140625" customWidth="1"/>
+    <col min="20" max="20" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
+      <c r="M1" s="124"/>
+      <c r="N1" s="124"/>
+      <c r="O1" s="124"/>
+      <c r="P1" s="124"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="122"/>
-      <c r="E2" s="122"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="2" t="s">
+      <c r="B2" s="125"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="2" t="s">
+      <c r="H2" s="146"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="148"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
     </row>
     <row r="3" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
-      <c r="R3" s="18"/>
-      <c r="S3" s="18"/>
-      <c r="T3" s="18"/>
-      <c r="U3" s="18"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="18"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="17"/>
       <c r="L4" s="60" t="s">
         <v>70</v>
       </c>
@@ -1793,638 +1793,638 @@
       <c r="N4" s="60"/>
       <c r="O4" s="60"/>
       <c r="P4" s="60"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="18"/>
-      <c r="U4" s="18"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="17"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="120" t="s">
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="120"/>
-      <c r="K5" s="18"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="17"/>
       <c r="L5" s="60"/>
       <c r="M5" s="60"/>
       <c r="N5" s="60"/>
       <c r="O5" s="60"/>
       <c r="P5" s="60"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18"/>
-      <c r="S5" s="18"/>
-      <c r="T5" s="18"/>
-      <c r="U5" s="18"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="48"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="22" t="s">
+      <c r="A6" s="47"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="J6" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="18"/>
+      <c r="K6" s="17"/>
       <c r="L6" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="M6" s="48" t="s">
+      <c r="M6" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="N6" s="48"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="125" t="s">
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="125"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="18"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="17"/>
       <c r="L7" s="56"/>
-      <c r="M7" s="22" t="s">
+      <c r="M7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="N7" s="22" t="s">
+      <c r="N7" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="22" t="s">
+      <c r="O7" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="P7" s="22" t="s">
+      <c r="P7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="18"/>
-      <c r="S7" s="18"/>
-      <c r="T7" s="18"/>
-      <c r="U7" s="18"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="74"/>
-      <c r="B8" s="74"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="125" t="s">
+      <c r="A8" s="63"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="131" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="40" t="s">
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="18"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="18"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="17"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="74"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="74"/>
-      <c r="D9" s="125" t="s">
+      <c r="A9" s="63"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="131" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="40" t="s">
+      <c r="E9" s="131"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="18"/>
-      <c r="T9" s="18"/>
-      <c r="U9" s="18"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="125" t="s">
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="40" t="s">
+      <c r="E10" s="131"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="18"/>
-      <c r="T10" s="18"/>
-      <c r="U10" s="18"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="74"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="125" t="s">
+      <c r="A11" s="63"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="125"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="40" t="s">
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="18"/>
-      <c r="S11" s="18"/>
-      <c r="T11" s="18"/>
-      <c r="U11" s="18"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="74"/>
-      <c r="B12" s="74"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="126" t="s">
+      <c r="A12" s="63"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="132" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="126"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="40" t="s">
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="18"/>
-      <c r="S12" s="18"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="127" t="s">
+      <c r="A13" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="127"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="5" t="s">
+      <c r="B13" s="133"/>
+      <c r="C13" s="133"/>
+      <c r="D13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="74" t="s">
+      <c r="E13" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="74"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="40" t="s">
+      <c r="F13" s="63"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="18"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="18"/>
-      <c r="T13" s="18"/>
-      <c r="U13" s="18"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="127"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="5" t="s">
+      <c r="A14" s="133"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="133"/>
+      <c r="D14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="74" t="s">
+      <c r="E14" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="74"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="7" t="s">
+      <c r="F14" s="63"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="18"/>
-      <c r="T14" s="18"/>
-      <c r="U14" s="18"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="128" t="s">
+      <c r="A15" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="128"/>
-      <c r="C15" s="128"/>
-      <c r="D15" s="74" t="s">
+      <c r="B15" s="134"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="18"/>
-      <c r="S15" s="18"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="18"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="124"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="7" t="s">
+      <c r="B16" s="130"/>
+      <c r="C16" s="130"/>
+      <c r="D16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="74" t="s">
+      <c r="E16" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="74"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="47" t="s">
+      <c r="F16" s="63"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="M16" s="47"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="18"/>
-      <c r="R16" s="18"/>
-      <c r="S16" s="18"/>
-      <c r="T16" s="18"/>
-      <c r="U16" s="18"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="46"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="124"/>
-      <c r="C17" s="124"/>
-      <c r="D17" s="7" t="s">
+      <c r="A17" s="130"/>
+      <c r="B17" s="130"/>
+      <c r="C17" s="130"/>
+      <c r="D17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="74" t="s">
+      <c r="E17" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="74"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="18"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="17"/>
       <c r="L17" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="M17" s="47" t="s">
+      <c r="M17" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="N17" s="47"/>
-      <c r="O17" s="47"/>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="18"/>
-      <c r="R17" s="18"/>
-      <c r="S17" s="18"/>
-      <c r="T17" s="18"/>
-      <c r="U17" s="18"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="17"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="124"/>
-      <c r="B18" s="124"/>
-      <c r="C18" s="124"/>
-      <c r="D18" s="7" t="s">
+      <c r="A18" s="130"/>
+      <c r="B18" s="130"/>
+      <c r="C18" s="130"/>
+      <c r="D18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="74" t="s">
+      <c r="E18" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="74"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="18"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="17"/>
       <c r="L18" s="56"/>
-      <c r="M18" s="22" t="s">
+      <c r="M18" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="N18" s="22" t="s">
+      <c r="N18" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="O18" s="22" t="s">
+      <c r="O18" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="P18" s="22" t="s">
+      <c r="P18" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="Q18" s="18"/>
-      <c r="R18" s="18"/>
-      <c r="S18" s="18"/>
-      <c r="T18" s="18"/>
-      <c r="U18" s="18"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="128" t="s">
+      <c r="A19" s="134" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="128"/>
-      <c r="C19" s="128"/>
-      <c r="D19" s="129" t="s">
+      <c r="B19" s="134"/>
+      <c r="C19" s="134"/>
+      <c r="D19" s="135" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="129"/>
-      <c r="F19" s="129"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="14" t="s">
+      <c r="E19" s="135"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="18"/>
-      <c r="R19" s="18"/>
-      <c r="S19" s="18"/>
-      <c r="T19" s="18"/>
-      <c r="U19" s="18"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="128" t="s">
+      <c r="A20" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="128"/>
-      <c r="C20" s="128"/>
-      <c r="D20" s="74" t="s">
+      <c r="B20" s="134"/>
+      <c r="C20" s="134"/>
+      <c r="D20" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="14" t="s">
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="18"/>
-      <c r="R20" s="18"/>
-      <c r="S20" s="18"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="18"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="128" t="s">
+      <c r="A21" s="134" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="128"/>
-      <c r="C21" s="128"/>
-      <c r="D21" s="74" t="s">
+      <c r="B21" s="134"/>
+      <c r="C21" s="134"/>
+      <c r="D21" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="14" t="s">
+      <c r="E21" s="63"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="18"/>
-      <c r="R21" s="18"/>
-      <c r="S21" s="18"/>
-      <c r="T21" s="18"/>
-      <c r="U21" s="18"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="128" t="s">
+      <c r="A22" s="134" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="128"/>
-      <c r="C22" s="128"/>
-      <c r="D22" s="129" t="s">
+      <c r="B22" s="134"/>
+      <c r="C22" s="134"/>
+      <c r="D22" s="135" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="129"/>
-      <c r="F22" s="129"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="14" t="s">
+      <c r="E22" s="135"/>
+      <c r="F22" s="135"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="18"/>
-      <c r="R22" s="18"/>
-      <c r="S22" s="18"/>
-      <c r="T22" s="18"/>
-      <c r="U22" s="18"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="131" t="s">
+      <c r="A23" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="131"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="7" t="s">
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
+      <c r="D23" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="74" t="s">
+      <c r="E23" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="74"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="14" t="s">
+      <c r="F23" s="63"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="18"/>
-      <c r="R23" s="18"/>
-      <c r="S23" s="18"/>
-      <c r="T23" s="18"/>
-      <c r="U23" s="18"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="17"/>
     </row>
     <row r="24" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="Q24" s="18"/>
-      <c r="R24" s="18"/>
-      <c r="S24" s="18"/>
-      <c r="T24" s="18"/>
-      <c r="U24" s="18"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="17"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="71" t="s">
+      <c r="A25" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="72"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
       <c r="J25" s="86"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="71" t="s">
+      <c r="K25" s="17"/>
+      <c r="L25" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="M25" s="72"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="72"/>
+      <c r="M25" s="75"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="75"/>
       <c r="P25" s="86"/>
-      <c r="Q25" s="18"/>
-      <c r="R25" s="18"/>
-      <c r="S25" s="18"/>
-      <c r="T25" s="18"/>
-      <c r="U25" s="18"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" s="48" t="s">
+      <c r="A26" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48" t="s">
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="18"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="17"/>
       <c r="L26" s="56" t="s">
         <v>71</v>
       </c>
@@ -2434,243 +2434,243 @@
       <c r="N26" s="104"/>
       <c r="O26" s="104"/>
       <c r="P26" s="105"/>
-      <c r="Q26" s="18"/>
-      <c r="R26" s="18"/>
-      <c r="S26" s="18"/>
-      <c r="T26" s="18"/>
-      <c r="U26" s="18"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="17"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="22" t="s">
+      <c r="A27" s="47"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="22" t="s">
+      <c r="H27" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I27" s="22" t="s">
+      <c r="I27" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="J27" s="22" t="s">
+      <c r="J27" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="K27" s="18"/>
+      <c r="K27" s="17"/>
       <c r="L27" s="56"/>
-      <c r="M27" s="22" t="s">
+      <c r="M27" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="N27" s="22" t="s">
+      <c r="N27" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="O27" s="22" t="s">
+      <c r="O27" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="P27" s="22" t="s">
+      <c r="P27" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="Q27" s="18"/>
-      <c r="R27" s="18"/>
-      <c r="S27" s="18"/>
-      <c r="T27" s="18"/>
-      <c r="U27" s="18"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="17"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="90" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="90"/>
-      <c r="C28" s="132" t="s">
+      <c r="C28" s="119" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="132"/>
-      <c r="E28" s="132"/>
-      <c r="F28" s="132"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="14" t="s">
+      <c r="D28" s="119"/>
+      <c r="E28" s="119"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="18"/>
-      <c r="R28" s="18"/>
-      <c r="S28" s="18"/>
-      <c r="T28" s="18"/>
-      <c r="U28" s="18"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="90"/>
-      <c r="C29" s="132" t="s">
+      <c r="C29" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="132"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="14" t="s">
+      <c r="D29" s="119"/>
+      <c r="E29" s="119"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="18"/>
-      <c r="R29" s="18"/>
-      <c r="S29" s="18"/>
-      <c r="T29" s="18"/>
-      <c r="U29" s="18"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="90"/>
       <c r="B30" s="90"/>
-      <c r="C30" s="133" t="s">
+      <c r="C30" s="120" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="133"/>
-      <c r="E30" s="133"/>
-      <c r="F30" s="133"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="14" t="s">
+      <c r="D30" s="120"/>
+      <c r="E30" s="120"/>
+      <c r="F30" s="120"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="20"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="18"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="18"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="17"/>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="134" t="s">
+      <c r="A31" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="134"/>
-      <c r="C31" s="134"/>
-      <c r="D31" s="134"/>
-      <c r="E31" s="134"/>
-      <c r="F31" s="134"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="14" t="s">
+      <c r="B31" s="121"/>
+      <c r="C31" s="121"/>
+      <c r="D31" s="121"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="18"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="18"/>
-      <c r="U31" s="18"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="17"/>
+      <c r="U31" s="17"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="130" t="s">
+      <c r="B32" s="25"/>
+      <c r="C32" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="130"/>
-      <c r="E32" s="130"/>
-      <c r="F32" s="130"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="14" t="s">
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="118"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="18"/>
-      <c r="R32" s="18"/>
-      <c r="S32" s="18"/>
-      <c r="T32" s="18"/>
-      <c r="U32" s="18"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="17"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="135" t="s">
+      <c r="A33" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="135"/>
-      <c r="C33" s="136" t="s">
+      <c r="B33" s="122"/>
+      <c r="C33" s="123" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="136"/>
-      <c r="E33" s="136"/>
-      <c r="F33" s="136"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="14" t="s">
+      <c r="D33" s="123"/>
+      <c r="E33" s="123"/>
+      <c r="F33" s="123"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="18"/>
-      <c r="R33" s="18"/>
-      <c r="S33" s="18"/>
-      <c r="T33" s="18"/>
-      <c r="U33" s="18"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" s="135"/>
-      <c r="B34" s="135"/>
-      <c r="C34" s="136" t="s">
+      <c r="A34" s="122"/>
+      <c r="B34" s="122"/>
+      <c r="C34" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="136"/>
-      <c r="E34" s="136"/>
-      <c r="F34" s="136"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="18"/>
-      <c r="P34" s="18"/>
-      <c r="Q34" s="18"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="18"/>
+      <c r="D34" s="123"/>
+      <c r="E34" s="123"/>
+      <c r="F34" s="123"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="90" t="s">
@@ -2683,21 +2683,21 @@
       <c r="D35" s="137"/>
       <c r="E35" s="137"/>
       <c r="F35" s="137"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
-      <c r="P35" s="18"/>
-      <c r="Q35" s="18"/>
-      <c r="R35" s="18"/>
-      <c r="S35" s="18"/>
-      <c r="T35" s="18"/>
-      <c r="U35" s="18"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="17"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="90"/>
@@ -2708,21 +2708,21 @@
       <c r="D36" s="138"/>
       <c r="E36" s="138"/>
       <c r="F36" s="138"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
-      <c r="M36" s="18"/>
-      <c r="N36" s="18"/>
-      <c r="O36" s="18"/>
-      <c r="P36" s="18"/>
-      <c r="Q36" s="18"/>
-      <c r="R36" s="18"/>
-      <c r="S36" s="18"/>
-      <c r="T36" s="18"/>
-      <c r="U36" s="18"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
@@ -2733,21 +2733,21 @@
       <c r="D37" s="138"/>
       <c r="E37" s="138"/>
       <c r="F37" s="138"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
-      <c r="N37" s="18"/>
-      <c r="O37" s="18"/>
-      <c r="P37" s="18"/>
-      <c r="Q37" s="18"/>
-      <c r="R37" s="18"/>
-      <c r="S37" s="18"/>
-      <c r="T37" s="18"/>
-      <c r="U37" s="18"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="90"/>
@@ -2758,177 +2758,177 @@
       <c r="D38" s="138"/>
       <c r="E38" s="138"/>
       <c r="F38" s="138"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="18"/>
-      <c r="N38" s="18"/>
-      <c r="O38" s="18"/>
-      <c r="P38" s="18"/>
-      <c r="Q38" s="18"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="18"/>
-      <c r="U38" s="18"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="17"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="90" t="s">
         <v>52</v>
       </c>
       <c r="B39" s="90"/>
-      <c r="C39" s="127" t="s">
+      <c r="C39" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="127"/>
-      <c r="E39" s="127"/>
-      <c r="F39" s="5" t="s">
+      <c r="D39" s="133"/>
+      <c r="E39" s="133"/>
+      <c r="F39" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
-      <c r="M39" s="18"/>
-      <c r="N39" s="18"/>
-      <c r="O39" s="18"/>
-      <c r="P39" s="18"/>
-      <c r="Q39" s="18"/>
-      <c r="R39" s="18"/>
-      <c r="S39" s="18"/>
-      <c r="T39" s="18"/>
-      <c r="U39" s="18"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="17"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="90"/>
       <c r="B40" s="90"/>
-      <c r="C40" s="127"/>
-      <c r="D40" s="127"/>
-      <c r="E40" s="127"/>
-      <c r="F40" s="5" t="s">
+      <c r="C40" s="133"/>
+      <c r="D40" s="133"/>
+      <c r="E40" s="133"/>
+      <c r="F40" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G40" s="27"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
-      <c r="M40" s="18"/>
-      <c r="N40" s="18"/>
-      <c r="O40" s="18"/>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="18"/>
-      <c r="R40" s="18"/>
-      <c r="S40" s="18"/>
-      <c r="T40" s="18"/>
-      <c r="U40" s="18"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="17"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="90"/>
-      <c r="C41" s="128" t="s">
+      <c r="C41" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="128"/>
-      <c r="E41" s="128"/>
-      <c r="F41" s="128"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
-      <c r="M41" s="18"/>
-      <c r="N41" s="18"/>
-      <c r="O41" s="18"/>
-      <c r="P41" s="18"/>
-      <c r="Q41" s="18"/>
-      <c r="R41" s="18"/>
-      <c r="S41" s="18"/>
-      <c r="T41" s="18"/>
-      <c r="U41" s="18"/>
+      <c r="D41" s="134"/>
+      <c r="E41" s="134"/>
+      <c r="F41" s="134"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="17"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="90"/>
       <c r="B42" s="90"/>
-      <c r="C42" s="124" t="s">
+      <c r="C42" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="D42" s="124"/>
-      <c r="E42" s="124"/>
-      <c r="F42" s="7" t="s">
+      <c r="D42" s="130"/>
+      <c r="E42" s="130"/>
+      <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G42" s="27"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
-      <c r="M42" s="18"/>
-      <c r="N42" s="18"/>
-      <c r="O42" s="18"/>
-      <c r="P42" s="18"/>
-      <c r="Q42" s="18"/>
-      <c r="R42" s="18"/>
-      <c r="S42" s="18"/>
-      <c r="T42" s="18"/>
-      <c r="U42" s="18"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="17"/>
+      <c r="U42" s="17"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="90"/>
-      <c r="C43" s="124"/>
-      <c r="D43" s="124"/>
-      <c r="E43" s="124"/>
-      <c r="F43" s="7" t="s">
+      <c r="C43" s="130"/>
+      <c r="D43" s="130"/>
+      <c r="E43" s="130"/>
+      <c r="F43" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G43" s="27"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="18"/>
-      <c r="L43" s="18"/>
-      <c r="M43" s="18"/>
-      <c r="N43" s="18"/>
-      <c r="O43" s="18"/>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="18"/>
-      <c r="R43" s="18"/>
-      <c r="S43" s="18"/>
-      <c r="T43" s="18"/>
-      <c r="U43" s="18"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="17"/>
+      <c r="T43" s="17"/>
+      <c r="U43" s="17"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="90"/>
       <c r="B44" s="90"/>
-      <c r="C44" s="124"/>
-      <c r="D44" s="124"/>
-      <c r="E44" s="124"/>
-      <c r="F44" s="7" t="s">
+      <c r="C44" s="130"/>
+      <c r="D44" s="130"/>
+      <c r="E44" s="130"/>
+      <c r="F44" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G44" s="27"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="18"/>
-      <c r="M44" s="18"/>
-      <c r="N44" s="18"/>
-      <c r="O44" s="18"/>
-      <c r="P44" s="18"/>
-      <c r="Q44" s="18"/>
-      <c r="R44" s="18"/>
-      <c r="S44" s="18"/>
-      <c r="T44" s="18"/>
-      <c r="U44" s="18"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="17"/>
+      <c r="U44" s="17"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
@@ -2939,134 +2939,134 @@
       <c r="D45" s="140"/>
       <c r="E45" s="140"/>
       <c r="F45" s="140"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="18"/>
-      <c r="L45" s="18"/>
-      <c r="M45" s="18"/>
-      <c r="N45" s="18"/>
-      <c r="O45" s="18"/>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="18"/>
-      <c r="R45" s="18"/>
-      <c r="S45" s="18"/>
-      <c r="T45" s="18"/>
-      <c r="U45" s="18"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="27"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="17"/>
+      <c r="U45" s="17"/>
     </row>
     <row r="46" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="18"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="18"/>
-      <c r="L46" s="18"/>
-      <c r="M46" s="18"/>
-      <c r="N46" s="18"/>
-      <c r="O46" s="18"/>
-      <c r="P46" s="18"/>
-      <c r="U46" s="18"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="U46" s="17"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="47" t="s">
+      <c r="A47" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="47"/>
-      <c r="C47" s="47"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="47"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="47"/>
-      <c r="I47" s="47"/>
-      <c r="J47" s="48" t="s">
+      <c r="B47" s="46"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="46"/>
+      <c r="I47" s="46"/>
+      <c r="J47" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="K47" s="48"/>
-      <c r="L47" s="48"/>
-      <c r="M47" s="48"/>
-      <c r="N47" s="18"/>
-      <c r="O47" s="18"/>
-      <c r="P47" s="18"/>
-      <c r="Q47" s="18"/>
-      <c r="R47" s="18"/>
-      <c r="S47" s="18"/>
-      <c r="T47" s="18"/>
-      <c r="U47" s="18"/>
+      <c r="K47" s="47"/>
+      <c r="L47" s="47"/>
+      <c r="M47" s="47"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+      <c r="R47" s="17"/>
+      <c r="S47" s="17"/>
+      <c r="T47" s="17"/>
+      <c r="U47" s="17"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="48" t="s">
+      <c r="A48" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="48"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48" t="s">
+      <c r="B48" s="47"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48"/>
-      <c r="J48" s="48" t="s">
+      <c r="G48" s="47"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="K48" s="48"/>
-      <c r="L48" s="48"/>
-      <c r="M48" s="48"/>
-      <c r="N48" s="18"/>
-      <c r="O48" s="18"/>
-      <c r="P48" s="18"/>
-      <c r="Q48" s="18"/>
-      <c r="R48" s="18"/>
-      <c r="S48" s="18"/>
-      <c r="T48" s="18"/>
-      <c r="U48" s="18"/>
+      <c r="K48" s="47"/>
+      <c r="L48" s="47"/>
+      <c r="M48" s="47"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="17"/>
+      <c r="U48" s="17"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="48"/>
-      <c r="B49" s="48"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="22" t="s">
+      <c r="A49" s="47"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G49" s="22" t="s">
+      <c r="G49" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="H49" s="22" t="s">
+      <c r="H49" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="I49" s="22" t="s">
+      <c r="I49" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="J49" s="22" t="s">
+      <c r="J49" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="K49" s="22" t="s">
+      <c r="K49" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="L49" s="22" t="s">
+      <c r="L49" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="M49" s="22" t="s">
+      <c r="M49" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="N49" s="18"/>
-      <c r="O49" s="18"/>
-      <c r="P49" s="18"/>
-      <c r="Q49" s="18"/>
-      <c r="R49" s="18"/>
-      <c r="S49" s="18"/>
-      <c r="T49" s="18"/>
-      <c r="U49" s="18"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="17"/>
+      <c r="T49" s="17"/>
+      <c r="U49" s="17"/>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="137" t="s">
@@ -3076,22 +3076,22 @@
       <c r="C50" s="137"/>
       <c r="D50" s="137"/>
       <c r="E50" s="137"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="12"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-      <c r="M50" s="12"/>
-      <c r="N50" s="18"/>
-      <c r="O50" s="18"/>
-      <c r="P50" s="18"/>
-      <c r="Q50" s="18"/>
-      <c r="R50" s="18"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="18"/>
-      <c r="U50" s="18"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+      <c r="R50" s="17"/>
+      <c r="S50" s="17"/>
+      <c r="T50" s="17"/>
+      <c r="U50" s="17"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="139" t="s">
@@ -3101,22 +3101,22 @@
       <c r="C51" s="139"/>
       <c r="D51" s="139"/>
       <c r="E51" s="139"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="12"/>
-      <c r="N51" s="18"/>
-      <c r="O51" s="18"/>
-      <c r="P51" s="18"/>
-      <c r="Q51" s="18"/>
-      <c r="R51" s="18"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="18"/>
-      <c r="U51" s="18"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17"/>
+      <c r="R51" s="17"/>
+      <c r="S51" s="17"/>
+      <c r="T51" s="17"/>
+      <c r="U51" s="17"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="137" t="s">
@@ -3126,72 +3126,72 @@
       <c r="C52" s="137"/>
       <c r="D52" s="137"/>
       <c r="E52" s="137"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="12"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-      <c r="M52" s="12"/>
-      <c r="N52" s="18"/>
-      <c r="O52" s="18"/>
-      <c r="P52" s="18"/>
-      <c r="Q52" s="18"/>
-      <c r="R52" s="18"/>
-      <c r="S52" s="18"/>
-      <c r="T52" s="18"/>
-      <c r="U52" s="18"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="17"/>
+      <c r="S52" s="17"/>
+      <c r="T52" s="17"/>
+      <c r="U52" s="17"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="143" t="s">
+      <c r="A53" s="141" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="143"/>
-      <c r="C53" s="143"/>
-      <c r="D53" s="143"/>
-      <c r="E53" s="143"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="12"/>
-      <c r="N53" s="18"/>
-      <c r="O53" s="18"/>
-      <c r="P53" s="18"/>
-      <c r="Q53" s="18"/>
-      <c r="R53" s="18"/>
-      <c r="S53" s="18"/>
-      <c r="T53" s="18"/>
-      <c r="U53" s="18"/>
+      <c r="B53" s="141"/>
+      <c r="C53" s="141"/>
+      <c r="D53" s="141"/>
+      <c r="E53" s="141"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="17"/>
+      <c r="P53" s="17"/>
+      <c r="Q53" s="17"/>
+      <c r="R53" s="17"/>
+      <c r="S53" s="17"/>
+      <c r="T53" s="17"/>
+      <c r="U53" s="17"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A54" s="145" t="s">
+      <c r="A54" s="142" t="s">
         <v>41</v>
       </c>
-      <c r="B54" s="145"/>
-      <c r="C54" s="145"/>
-      <c r="D54" s="145"/>
-      <c r="E54" s="145"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-      <c r="M54" s="9"/>
-      <c r="N54" s="18"/>
-      <c r="O54" s="18"/>
-      <c r="P54" s="18"/>
-      <c r="Q54" s="18"/>
-      <c r="R54" s="18"/>
-      <c r="S54" s="18"/>
-      <c r="T54" s="18"/>
-      <c r="U54" s="18"/>
+      <c r="B54" s="142"/>
+      <c r="C54" s="142"/>
+      <c r="D54" s="142"/>
+      <c r="E54" s="142"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+      <c r="R54" s="17"/>
+      <c r="S54" s="17"/>
+      <c r="T54" s="17"/>
+      <c r="U54" s="17"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="138" t="s">
@@ -3201,423 +3201,429 @@
       <c r="C55" s="138"/>
       <c r="D55" s="138"/>
       <c r="E55" s="138"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="12"/>
-      <c r="N55" s="18"/>
-      <c r="O55" s="18"/>
-      <c r="P55" s="18"/>
-      <c r="Q55" s="18"/>
-      <c r="R55" s="18"/>
-      <c r="S55" s="18"/>
-      <c r="T55" s="18"/>
-      <c r="U55" s="18"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="17"/>
+      <c r="O55" s="17"/>
+      <c r="P55" s="17"/>
+      <c r="Q55" s="17"/>
+      <c r="R55" s="17"/>
+      <c r="S55" s="17"/>
+      <c r="T55" s="17"/>
+      <c r="U55" s="17"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="90" t="s">
         <v>52</v>
       </c>
       <c r="B56" s="90"/>
-      <c r="C56" s="127" t="s">
+      <c r="C56" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="D56" s="127"/>
-      <c r="E56" s="5" t="s">
+      <c r="D56" s="133"/>
+      <c r="E56" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="12"/>
-      <c r="N56" s="18"/>
-      <c r="O56" s="18"/>
-      <c r="P56" s="18"/>
-      <c r="Q56" s="18"/>
-      <c r="R56" s="18"/>
-      <c r="S56" s="18"/>
-      <c r="T56" s="18"/>
-      <c r="U56" s="18"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="17"/>
+      <c r="S56" s="17"/>
+      <c r="T56" s="17"/>
+      <c r="U56" s="17"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="90"/>
-      <c r="C57" s="127"/>
-      <c r="D57" s="127"/>
-      <c r="E57" s="5" t="s">
+      <c r="C57" s="133"/>
+      <c r="D57" s="133"/>
+      <c r="E57" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="9"/>
-      <c r="K57" s="9"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="12"/>
-      <c r="N57" s="18"/>
-      <c r="O57" s="18"/>
-      <c r="P57" s="18"/>
-      <c r="Q57" s="18"/>
-      <c r="R57" s="18"/>
-      <c r="S57" s="18"/>
-      <c r="T57" s="18"/>
-      <c r="U57" s="18"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="17"/>
+      <c r="O57" s="17"/>
+      <c r="P57" s="17"/>
+      <c r="Q57" s="17"/>
+      <c r="R57" s="17"/>
+      <c r="S57" s="17"/>
+      <c r="T57" s="17"/>
+      <c r="U57" s="17"/>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="90"/>
       <c r="B58" s="90"/>
-      <c r="C58" s="128" t="s">
+      <c r="C58" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="D58" s="128"/>
-      <c r="E58" s="128"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="12"/>
-      <c r="N58" s="18"/>
-      <c r="O58" s="18"/>
-      <c r="P58" s="18"/>
-      <c r="Q58" s="18"/>
-      <c r="R58" s="18"/>
-      <c r="S58" s="18"/>
-      <c r="T58" s="18"/>
-      <c r="U58" s="18"/>
+      <c r="D58" s="134"/>
+      <c r="E58" s="134"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="17"/>
+      <c r="O58" s="17"/>
+      <c r="P58" s="17"/>
+      <c r="Q58" s="17"/>
+      <c r="R58" s="17"/>
+      <c r="S58" s="17"/>
+      <c r="T58" s="17"/>
+      <c r="U58" s="17"/>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="90"/>
-      <c r="C59" s="124" t="s">
+      <c r="C59" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="D59" s="124"/>
-      <c r="E59" s="7" t="s">
+      <c r="D59" s="130"/>
+      <c r="E59" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="19"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="12"/>
-      <c r="J59" s="19"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="12"/>
-      <c r="N59" s="18"/>
-      <c r="O59" s="18"/>
-      <c r="P59" s="18"/>
-      <c r="Q59" s="18"/>
-      <c r="R59" s="18"/>
-      <c r="S59" s="18"/>
-      <c r="T59" s="18"/>
-      <c r="U59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="17"/>
+      <c r="O59" s="17"/>
+      <c r="P59" s="17"/>
+      <c r="Q59" s="17"/>
+      <c r="R59" s="17"/>
+      <c r="S59" s="17"/>
+      <c r="T59" s="17"/>
+      <c r="U59" s="17"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="90"/>
       <c r="B60" s="90"/>
-      <c r="C60" s="124"/>
-      <c r="D60" s="124"/>
-      <c r="E60" s="7" t="s">
+      <c r="C60" s="130"/>
+      <c r="D60" s="130"/>
+      <c r="E60" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F60" s="19"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="12"/>
-      <c r="J60" s="19"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="12"/>
-      <c r="N60" s="18"/>
-      <c r="O60" s="18"/>
-      <c r="P60" s="18"/>
-      <c r="Q60" s="18"/>
-      <c r="R60" s="18"/>
-      <c r="S60" s="18"/>
-      <c r="T60" s="18"/>
-      <c r="U60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="17"/>
+      <c r="O60" s="17"/>
+      <c r="P60" s="17"/>
+      <c r="Q60" s="17"/>
+      <c r="R60" s="17"/>
+      <c r="S60" s="17"/>
+      <c r="T60" s="17"/>
+      <c r="U60" s="17"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="90"/>
-      <c r="C61" s="124"/>
-      <c r="D61" s="124"/>
-      <c r="E61" s="7" t="s">
+      <c r="C61" s="130"/>
+      <c r="D61" s="130"/>
+      <c r="E61" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F61" s="19"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="12"/>
-      <c r="J61" s="19"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="12"/>
-      <c r="N61" s="18"/>
-      <c r="O61" s="18"/>
-      <c r="P61" s="18"/>
-      <c r="Q61" s="18"/>
-      <c r="R61" s="18"/>
-      <c r="S61" s="18"/>
-      <c r="T61" s="18"/>
-      <c r="U61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="11"/>
+      <c r="N61" s="17"/>
+      <c r="O61" s="17"/>
+      <c r="P61" s="17"/>
+      <c r="Q61" s="17"/>
+      <c r="R61" s="17"/>
+      <c r="S61" s="17"/>
+      <c r="T61" s="17"/>
+      <c r="U61" s="17"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="90"/>
       <c r="B62" s="90"/>
-      <c r="C62" s="141" t="s">
+      <c r="C62" s="143" t="s">
         <v>62</v>
       </c>
-      <c r="D62" s="141"/>
-      <c r="E62" s="141"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="12"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="13"/>
-      <c r="M62" s="12"/>
-      <c r="N62" s="18"/>
-      <c r="O62" s="18"/>
-      <c r="P62" s="18"/>
-      <c r="Q62" s="18"/>
-      <c r="R62" s="18"/>
-      <c r="S62" s="18"/>
-      <c r="T62" s="18"/>
-      <c r="U62" s="18"/>
+      <c r="D62" s="143"/>
+      <c r="E62" s="143"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="17"/>
+      <c r="O62" s="17"/>
+      <c r="P62" s="17"/>
+      <c r="Q62" s="17"/>
+      <c r="R62" s="17"/>
+      <c r="S62" s="17"/>
+      <c r="T62" s="17"/>
+      <c r="U62" s="17"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="90"/>
-      <c r="C63" s="142" t="s">
+      <c r="C63" s="144" t="s">
         <v>54</v>
       </c>
-      <c r="D63" s="142"/>
-      <c r="E63" s="142"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="12"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="9"/>
-      <c r="L63" s="9"/>
-      <c r="M63" s="12"/>
-      <c r="N63" s="18"/>
-      <c r="O63" s="18"/>
-      <c r="P63" s="18"/>
-      <c r="Q63" s="18"/>
-      <c r="R63" s="18"/>
-      <c r="S63" s="18"/>
-      <c r="T63" s="18"/>
-      <c r="U63" s="18"/>
+      <c r="D63" s="144"/>
+      <c r="E63" s="144"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="8"/>
+      <c r="M63" s="11"/>
+      <c r="N63" s="17"/>
+      <c r="O63" s="17"/>
+      <c r="P63" s="17"/>
+      <c r="Q63" s="17"/>
+      <c r="R63" s="17"/>
+      <c r="S63" s="17"/>
+      <c r="T63" s="17"/>
+      <c r="U63" s="17"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="90"/>
       <c r="B64" s="90"/>
-      <c r="C64" s="132" t="s">
+      <c r="C64" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="D64" s="132"/>
-      <c r="E64" s="132"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="12"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="9"/>
-      <c r="L64" s="9"/>
-      <c r="M64" s="12"/>
-      <c r="N64" s="18"/>
-      <c r="O64" s="18"/>
-      <c r="P64" s="18"/>
-      <c r="Q64" s="18"/>
-      <c r="R64" s="18"/>
-      <c r="S64" s="18"/>
-      <c r="T64" s="18"/>
-      <c r="U64" s="18"/>
+      <c r="D64" s="119"/>
+      <c r="E64" s="119"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="8"/>
+      <c r="M64" s="11"/>
+      <c r="N64" s="17"/>
+      <c r="O64" s="17"/>
+      <c r="P64" s="17"/>
+      <c r="Q64" s="17"/>
+      <c r="R64" s="17"/>
+      <c r="S64" s="17"/>
+      <c r="T64" s="17"/>
+      <c r="U64" s="17"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="90"/>
-      <c r="C65" s="132" t="s">
+      <c r="C65" s="119" t="s">
         <v>64</v>
       </c>
-      <c r="D65" s="132"/>
-      <c r="E65" s="132"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="12"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="9"/>
-      <c r="L65" s="9"/>
-      <c r="M65" s="12"/>
-      <c r="N65" s="18"/>
-      <c r="O65" s="18"/>
-      <c r="P65" s="18"/>
-      <c r="Q65" s="18"/>
-      <c r="R65" s="18"/>
-      <c r="S65" s="18"/>
-      <c r="T65" s="18"/>
-      <c r="U65" s="18"/>
+      <c r="D65" s="119"/>
+      <c r="E65" s="119"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="17"/>
+      <c r="O65" s="17"/>
+      <c r="P65" s="17"/>
+      <c r="Q65" s="17"/>
+      <c r="R65" s="17"/>
+      <c r="S65" s="17"/>
+      <c r="T65" s="17"/>
+      <c r="U65" s="17"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="90"/>
       <c r="B66" s="90"/>
-      <c r="C66" s="132" t="s">
+      <c r="C66" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="D66" s="132"/>
-      <c r="E66" s="132"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="12"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="9"/>
-      <c r="L66" s="9"/>
-      <c r="M66" s="12"/>
-      <c r="N66" s="18"/>
-      <c r="O66" s="18"/>
-      <c r="P66" s="18"/>
-      <c r="Q66" s="18"/>
-      <c r="R66" s="18"/>
-      <c r="S66" s="18"/>
-      <c r="T66" s="18"/>
-      <c r="U66" s="18"/>
+      <c r="D66" s="119"/>
+      <c r="E66" s="119"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="8"/>
+      <c r="L66" s="8"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="17"/>
+      <c r="O66" s="17"/>
+      <c r="P66" s="17"/>
+      <c r="Q66" s="17"/>
+      <c r="R66" s="17"/>
+      <c r="S66" s="17"/>
+      <c r="T66" s="17"/>
+      <c r="U66" s="17"/>
     </row>
     <row r="67" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="18"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="18"/>
-      <c r="E67" s="18"/>
-      <c r="F67" s="18"/>
-      <c r="G67" s="18"/>
-      <c r="H67" s="18"/>
-      <c r="I67" s="18"/>
-      <c r="J67" s="18"/>
-      <c r="K67" s="18"/>
-      <c r="L67" s="18"/>
-      <c r="M67" s="18"/>
-      <c r="N67" s="18"/>
-      <c r="U67" s="18"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
+      <c r="M67" s="17"/>
+      <c r="N67" s="17"/>
+      <c r="O67" s="17"/>
+      <c r="P67" s="17"/>
+      <c r="Q67" s="17"/>
+      <c r="R67" s="17"/>
+      <c r="S67" s="17"/>
+      <c r="T67" s="17"/>
+      <c r="U67" s="17"/>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A68" s="47" t="s">
+      <c r="A68" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="47"/>
-      <c r="C68" s="47"/>
-      <c r="D68" s="47"/>
-      <c r="E68" s="47"/>
-      <c r="F68" s="47"/>
-      <c r="G68" s="47"/>
-      <c r="H68" s="47"/>
-      <c r="I68" s="47"/>
-      <c r="J68" s="48" t="s">
+      <c r="B68" s="46"/>
+      <c r="C68" s="46"/>
+      <c r="D68" s="46"/>
+      <c r="E68" s="46"/>
+      <c r="F68" s="46"/>
+      <c r="G68" s="46"/>
+      <c r="H68" s="46"/>
+      <c r="I68" s="46"/>
+      <c r="J68" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="K68" s="48"/>
-      <c r="L68" s="48"/>
-      <c r="M68" s="48"/>
-      <c r="N68" s="18"/>
-      <c r="O68" s="47" t="s">
+      <c r="K68" s="47"/>
+      <c r="L68" s="47"/>
+      <c r="M68" s="47"/>
+      <c r="N68" s="17"/>
+      <c r="O68" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="P68" s="47"/>
-      <c r="Q68" s="47"/>
-      <c r="R68" s="47"/>
-      <c r="S68" s="47"/>
-      <c r="T68" s="47"/>
-      <c r="U68" s="18"/>
+      <c r="P68" s="46"/>
+      <c r="Q68" s="46"/>
+      <c r="R68" s="46"/>
+      <c r="S68" s="46"/>
+      <c r="T68" s="46"/>
+      <c r="U68" s="17"/>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A69" s="48" t="s">
+      <c r="A69" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B69" s="48"/>
-      <c r="C69" s="48"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48" t="s">
+      <c r="B69" s="47"/>
+      <c r="C69" s="47"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="G69" s="48"/>
-      <c r="H69" s="48"/>
-      <c r="I69" s="48"/>
-      <c r="J69" s="48" t="s">
+      <c r="G69" s="47"/>
+      <c r="H69" s="47"/>
+      <c r="I69" s="47"/>
+      <c r="J69" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="K69" s="48"/>
-      <c r="L69" s="48"/>
-      <c r="M69" s="48"/>
-      <c r="N69" s="18"/>
-      <c r="O69" s="48" t="s">
+      <c r="K69" s="47"/>
+      <c r="L69" s="47"/>
+      <c r="M69" s="47"/>
+      <c r="N69" s="17"/>
+      <c r="O69" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="P69" s="48"/>
-      <c r="Q69" s="48"/>
-      <c r="R69" s="48"/>
-      <c r="S69" s="48"/>
-      <c r="T69" s="22" t="s">
+      <c r="P69" s="47"/>
+      <c r="Q69" s="47"/>
+      <c r="R69" s="47"/>
+      <c r="S69" s="47"/>
+      <c r="T69" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="U69" s="18"/>
+      <c r="U69" s="17"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A70" s="48"/>
-      <c r="B70" s="48"/>
-      <c r="C70" s="48"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="22" t="s">
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G70" s="22" t="s">
+      <c r="G70" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="H70" s="22" t="s">
+      <c r="H70" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="I70" s="22" t="s">
+      <c r="I70" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="J70" s="22" t="s">
+      <c r="J70" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="K70" s="22" t="s">
+      <c r="K70" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="L70" s="22" t="s">
+      <c r="L70" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="M70" s="22" t="s">
+      <c r="M70" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="N70" s="18"/>
-      <c r="O70" s="68" t="s">
+      <c r="N70" s="17"/>
+      <c r="O70" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="P70" s="68"/>
-      <c r="Q70" s="68"/>
-      <c r="R70" s="68"/>
-      <c r="S70" s="68"/>
-      <c r="T70" s="4"/>
-      <c r="U70" s="18"/>
+      <c r="P70" s="72"/>
+      <c r="Q70" s="72"/>
+      <c r="R70" s="72"/>
+      <c r="S70" s="72"/>
+      <c r="T70" s="3"/>
+      <c r="U70" s="17"/>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="137" t="s">
@@ -3627,24 +3633,24 @@
       <c r="C71" s="137"/>
       <c r="D71" s="137"/>
       <c r="E71" s="137"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="12"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="9"/>
-      <c r="L71" s="9"/>
-      <c r="M71" s="12"/>
-      <c r="N71" s="18"/>
-      <c r="O71" s="68" t="s">
+      <c r="F71" s="3"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+      <c r="M71" s="11"/>
+      <c r="N71" s="17"/>
+      <c r="O71" s="72" t="s">
         <v>162</v>
       </c>
-      <c r="P71" s="68"/>
-      <c r="Q71" s="68"/>
-      <c r="R71" s="68"/>
-      <c r="S71" s="68"/>
-      <c r="T71" s="4"/>
-      <c r="U71" s="18"/>
+      <c r="P71" s="72"/>
+      <c r="Q71" s="72"/>
+      <c r="R71" s="72"/>
+      <c r="S71" s="72"/>
+      <c r="T71" s="3"/>
+      <c r="U71" s="17"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="139" t="s">
@@ -3654,24 +3660,24 @@
       <c r="C72" s="139"/>
       <c r="D72" s="139"/>
       <c r="E72" s="139"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="12"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="9"/>
-      <c r="L72" s="9"/>
-      <c r="M72" s="12"/>
-      <c r="N72" s="18"/>
-      <c r="O72" s="68" t="s">
+      <c r="F72" s="3"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+      <c r="M72" s="11"/>
+      <c r="N72" s="17"/>
+      <c r="O72" s="72" t="s">
         <v>163</v>
       </c>
-      <c r="P72" s="68"/>
-      <c r="Q72" s="68"/>
-      <c r="R72" s="68"/>
-      <c r="S72" s="68"/>
-      <c r="T72" s="4"/>
-      <c r="U72" s="18"/>
+      <c r="P72" s="72"/>
+      <c r="Q72" s="72"/>
+      <c r="R72" s="72"/>
+      <c r="S72" s="72"/>
+      <c r="T72" s="3"/>
+      <c r="U72" s="17"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="137" t="s">
@@ -3681,51 +3687,51 @@
       <c r="C73" s="137"/>
       <c r="D73" s="137"/>
       <c r="E73" s="137"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="12"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="9"/>
-      <c r="L73" s="9"/>
-      <c r="M73" s="12"/>
-      <c r="N73" s="18"/>
-      <c r="O73" s="68" t="s">
+      <c r="F73" s="3"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+      <c r="M73" s="11"/>
+      <c r="N73" s="17"/>
+      <c r="O73" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="P73" s="68"/>
-      <c r="Q73" s="68"/>
-      <c r="R73" s="68"/>
-      <c r="S73" s="68"/>
-      <c r="T73" s="4"/>
-      <c r="U73" s="18"/>
+      <c r="P73" s="72"/>
+      <c r="Q73" s="72"/>
+      <c r="R73" s="72"/>
+      <c r="S73" s="72"/>
+      <c r="T73" s="3"/>
+      <c r="U73" s="17"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A74" s="143" t="s">
+      <c r="A74" s="141" t="s">
         <v>61</v>
       </c>
-      <c r="B74" s="143"/>
-      <c r="C74" s="143"/>
-      <c r="D74" s="143"/>
-      <c r="E74" s="143"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="12"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="12"/>
-      <c r="N74" s="18"/>
-      <c r="O74" s="68" t="s">
+      <c r="B74" s="141"/>
+      <c r="C74" s="141"/>
+      <c r="D74" s="141"/>
+      <c r="E74" s="141"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="11"/>
+      <c r="N74" s="17"/>
+      <c r="O74" s="72" t="s">
         <v>165</v>
       </c>
-      <c r="P74" s="68"/>
-      <c r="Q74" s="68"/>
-      <c r="R74" s="68"/>
-      <c r="S74" s="68"/>
-      <c r="T74" s="4"/>
-      <c r="U74" s="18"/>
+      <c r="P74" s="72"/>
+      <c r="Q74" s="72"/>
+      <c r="R74" s="72"/>
+      <c r="S74" s="72"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="17"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="138" t="s">
@@ -3735,244 +3741,244 @@
       <c r="C75" s="138"/>
       <c r="D75" s="138"/>
       <c r="E75" s="138"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="11"/>
-      <c r="I75" s="12"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="9"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="12"/>
-      <c r="N75" s="18"/>
-      <c r="O75" s="68" t="s">
+      <c r="F75" s="3"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="10"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="10"/>
+      <c r="M75" s="11"/>
+      <c r="N75" s="17"/>
+      <c r="O75" s="72" t="s">
         <v>166</v>
       </c>
-      <c r="P75" s="68"/>
-      <c r="Q75" s="68"/>
-      <c r="R75" s="68"/>
-      <c r="S75" s="68"/>
-      <c r="T75" s="4"/>
-      <c r="U75" s="18"/>
+      <c r="P75" s="72"/>
+      <c r="Q75" s="72"/>
+      <c r="R75" s="72"/>
+      <c r="S75" s="72"/>
+      <c r="T75" s="3"/>
+      <c r="U75" s="17"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="90" t="s">
         <v>52</v>
       </c>
       <c r="B76" s="90"/>
-      <c r="C76" s="127" t="s">
+      <c r="C76" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="D76" s="127"/>
-      <c r="E76" s="5" t="s">
+      <c r="D76" s="133"/>
+      <c r="E76" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="12"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
-      <c r="M76" s="12"/>
-      <c r="N76" s="18"/>
-      <c r="O76" s="68" t="s">
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="11"/>
+      <c r="N76" s="17"/>
+      <c r="O76" s="72" t="s">
         <v>167</v>
       </c>
-      <c r="P76" s="68"/>
-      <c r="Q76" s="68"/>
-      <c r="R76" s="68"/>
-      <c r="S76" s="68"/>
-      <c r="T76" s="4"/>
-      <c r="U76" s="18"/>
+      <c r="P76" s="72"/>
+      <c r="Q76" s="72"/>
+      <c r="R76" s="72"/>
+      <c r="S76" s="72"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="17"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="90"/>
       <c r="B77" s="90"/>
-      <c r="C77" s="127"/>
-      <c r="D77" s="127"/>
-      <c r="E77" s="5" t="s">
+      <c r="C77" s="133"/>
+      <c r="D77" s="133"/>
+      <c r="E77" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="12"/>
-      <c r="J77" s="9"/>
-      <c r="K77" s="9"/>
-      <c r="L77" s="4"/>
-      <c r="M77" s="12"/>
-      <c r="N77" s="18"/>
-      <c r="O77" s="68" t="s">
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="11"/>
+      <c r="N77" s="17"/>
+      <c r="O77" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="P77" s="68"/>
-      <c r="Q77" s="68"/>
-      <c r="R77" s="68"/>
-      <c r="S77" s="68"/>
-      <c r="T77" s="4"/>
-      <c r="U77" s="18"/>
+      <c r="P77" s="72"/>
+      <c r="Q77" s="72"/>
+      <c r="R77" s="72"/>
+      <c r="S77" s="72"/>
+      <c r="T77" s="3"/>
+      <c r="U77" s="17"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="90"/>
       <c r="B78" s="90"/>
-      <c r="C78" s="128" t="s">
+      <c r="C78" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="D78" s="128"/>
-      <c r="E78" s="128"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="12"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4"/>
-      <c r="M78" s="12"/>
-      <c r="N78" s="18"/>
-      <c r="O78" s="68" t="s">
+      <c r="D78" s="134"/>
+      <c r="E78" s="134"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="11"/>
+      <c r="N78" s="17"/>
+      <c r="O78" s="72" t="s">
         <v>169</v>
       </c>
-      <c r="P78" s="68"/>
-      <c r="Q78" s="68"/>
-      <c r="R78" s="68"/>
-      <c r="S78" s="68"/>
-      <c r="T78" s="4"/>
-      <c r="U78" s="18"/>
+      <c r="P78" s="72"/>
+      <c r="Q78" s="72"/>
+      <c r="R78" s="72"/>
+      <c r="S78" s="72"/>
+      <c r="T78" s="3"/>
+      <c r="U78" s="17"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="90"/>
       <c r="B79" s="90"/>
-      <c r="C79" s="124" t="s">
+      <c r="C79" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="D79" s="124"/>
-      <c r="E79" s="7" t="s">
+      <c r="D79" s="130"/>
+      <c r="E79" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F79" s="19"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="12"/>
-      <c r="J79" s="19"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
-      <c r="M79" s="12"/>
-      <c r="N79" s="18"/>
-      <c r="O79" s="68" t="s">
+      <c r="F79" s="18"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="18"/>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="11"/>
+      <c r="N79" s="17"/>
+      <c r="O79" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="P79" s="68"/>
-      <c r="Q79" s="68"/>
-      <c r="R79" s="68"/>
-      <c r="S79" s="68"/>
-      <c r="T79" s="4"/>
-      <c r="U79" s="18"/>
+      <c r="P79" s="72"/>
+      <c r="Q79" s="72"/>
+      <c r="R79" s="72"/>
+      <c r="S79" s="72"/>
+      <c r="T79" s="3"/>
+      <c r="U79" s="17"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="90"/>
       <c r="B80" s="90"/>
-      <c r="C80" s="124"/>
-      <c r="D80" s="124"/>
-      <c r="E80" s="7" t="s">
+      <c r="C80" s="130"/>
+      <c r="D80" s="130"/>
+      <c r="E80" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F80" s="19"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="12"/>
-      <c r="J80" s="19"/>
-      <c r="K80" s="4"/>
-      <c r="L80" s="4"/>
-      <c r="M80" s="12"/>
-      <c r="N80" s="18"/>
-      <c r="O80" s="68" t="s">
+      <c r="F80" s="18"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="18"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="11"/>
+      <c r="N80" s="17"/>
+      <c r="O80" s="72" t="s">
         <v>158</v>
       </c>
-      <c r="P80" s="68"/>
-      <c r="Q80" s="68"/>
-      <c r="R80" s="68"/>
-      <c r="S80" s="68"/>
-      <c r="T80" s="4"/>
-      <c r="U80" s="18"/>
+      <c r="P80" s="72"/>
+      <c r="Q80" s="72"/>
+      <c r="R80" s="72"/>
+      <c r="S80" s="72"/>
+      <c r="T80" s="3"/>
+      <c r="U80" s="17"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="90"/>
       <c r="B81" s="90"/>
-      <c r="C81" s="124"/>
-      <c r="D81" s="124"/>
-      <c r="E81" s="7" t="s">
+      <c r="C81" s="130"/>
+      <c r="D81" s="130"/>
+      <c r="E81" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F81" s="19"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="12"/>
-      <c r="J81" s="19"/>
-      <c r="K81" s="4"/>
-      <c r="L81" s="4"/>
-      <c r="M81" s="12"/>
-      <c r="N81" s="18"/>
-      <c r="O81" s="68" t="s">
+      <c r="F81" s="18"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="18"/>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3"/>
+      <c r="M81" s="11"/>
+      <c r="N81" s="17"/>
+      <c r="O81" s="72" t="s">
         <v>159</v>
       </c>
-      <c r="P81" s="68"/>
-      <c r="Q81" s="68"/>
-      <c r="R81" s="68"/>
-      <c r="S81" s="68"/>
-      <c r="T81" s="4"/>
-      <c r="U81" s="18"/>
+      <c r="P81" s="72"/>
+      <c r="Q81" s="72"/>
+      <c r="R81" s="72"/>
+      <c r="S81" s="72"/>
+      <c r="T81" s="3"/>
+      <c r="U81" s="17"/>
     </row>
     <row r="82" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="90"/>
       <c r="B82" s="90"/>
-      <c r="C82" s="144" t="s">
+      <c r="C82" s="148" t="s">
         <v>62</v>
       </c>
-      <c r="D82" s="144"/>
-      <c r="E82" s="144"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="13"/>
-      <c r="I82" s="12"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
-      <c r="L82" s="13"/>
-      <c r="M82" s="12"/>
-      <c r="N82" s="18"/>
-      <c r="O82" s="62" t="s">
+      <c r="D82" s="148"/>
+      <c r="E82" s="148"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="12"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+      <c r="L82" s="12"/>
+      <c r="M82" s="11"/>
+      <c r="N82" s="17"/>
+      <c r="O82" s="66" t="s">
         <v>160</v>
       </c>
-      <c r="P82" s="62"/>
-      <c r="Q82" s="62"/>
-      <c r="R82" s="62"/>
-      <c r="S82" s="62"/>
-      <c r="T82" s="66"/>
-      <c r="U82" s="18"/>
+      <c r="P82" s="66"/>
+      <c r="Q82" s="66"/>
+      <c r="R82" s="66"/>
+      <c r="S82" s="66"/>
+      <c r="T82" s="70"/>
+      <c r="U82" s="17"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="90"/>
       <c r="B83" s="90"/>
-      <c r="C83" s="146" t="s">
+      <c r="C83" s="145" t="s">
         <v>54</v>
       </c>
-      <c r="D83" s="146"/>
-      <c r="E83" s="146"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
-      <c r="I83" s="12"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="9"/>
-      <c r="L83" s="9"/>
-      <c r="M83" s="12"/>
-      <c r="N83" s="18"/>
-      <c r="O83" s="62"/>
-      <c r="P83" s="62"/>
-      <c r="Q83" s="62"/>
-      <c r="R83" s="62"/>
-      <c r="S83" s="62"/>
-      <c r="T83" s="67"/>
-      <c r="U83" s="18"/>
+      <c r="D83" s="145"/>
+      <c r="E83" s="145"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+      <c r="M83" s="11"/>
+      <c r="N83" s="17"/>
+      <c r="O83" s="66"/>
+      <c r="P83" s="66"/>
+      <c r="Q83" s="66"/>
+      <c r="R83" s="66"/>
+      <c r="S83" s="66"/>
+      <c r="T83" s="71"/>
+      <c r="U83" s="17"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="137" t="s">
@@ -3982,24 +3988,24 @@
       <c r="C84" s="137"/>
       <c r="D84" s="137"/>
       <c r="E84" s="137"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="12"/>
-      <c r="J84" s="13"/>
-      <c r="K84" s="13"/>
-      <c r="L84" s="9"/>
-      <c r="M84" s="12"/>
-      <c r="N84" s="18"/>
-      <c r="O84" s="68" t="s">
+      <c r="F84" s="3"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="12"/>
+      <c r="K84" s="12"/>
+      <c r="L84" s="8"/>
+      <c r="M84" s="11"/>
+      <c r="N84" s="17"/>
+      <c r="O84" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="P84" s="68"/>
-      <c r="Q84" s="68"/>
-      <c r="R84" s="68"/>
-      <c r="S84" s="68"/>
-      <c r="T84" s="1"/>
-      <c r="U84" s="18"/>
+      <c r="P84" s="72"/>
+      <c r="Q84" s="72"/>
+      <c r="R84" s="72"/>
+      <c r="S84" s="72"/>
+      <c r="T84" s="3"/>
+      <c r="U84" s="17"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="137" t="s">
@@ -4009,24 +4015,24 @@
       <c r="C85" s="137"/>
       <c r="D85" s="137"/>
       <c r="E85" s="137"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="9"/>
-      <c r="I85" s="12"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="9"/>
-      <c r="M85" s="12"/>
-      <c r="N85" s="18"/>
-      <c r="O85" s="63" t="s">
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3"/>
+      <c r="L85" s="8"/>
+      <c r="M85" s="11"/>
+      <c r="N85" s="17"/>
+      <c r="O85" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="P85" s="64"/>
-      <c r="Q85" s="64"/>
-      <c r="R85" s="64"/>
-      <c r="S85" s="65"/>
-      <c r="T85" s="41"/>
-      <c r="U85" s="18"/>
+      <c r="P85" s="68"/>
+      <c r="Q85" s="68"/>
+      <c r="R85" s="68"/>
+      <c r="S85" s="69"/>
+      <c r="T85" s="40"/>
+      <c r="U85" s="17"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="137" t="s">
@@ -4036,22 +4042,22 @@
       <c r="C86" s="137"/>
       <c r="D86" s="137"/>
       <c r="E86" s="137"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="9"/>
-      <c r="I86" s="12"/>
-      <c r="J86" s="9"/>
-      <c r="K86" s="9"/>
-      <c r="L86" s="9"/>
-      <c r="M86" s="9"/>
-      <c r="N86" s="18"/>
-      <c r="O86" s="18"/>
-      <c r="P86" s="18"/>
-      <c r="Q86" s="18"/>
-      <c r="R86" s="18"/>
-      <c r="S86" s="18"/>
-      <c r="T86" s="18"/>
-      <c r="U86" s="18"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+      <c r="M86" s="8"/>
+      <c r="N86" s="17"/>
+      <c r="O86" s="17"/>
+      <c r="P86" s="17"/>
+      <c r="Q86" s="17"/>
+      <c r="R86" s="17"/>
+      <c r="S86" s="17"/>
+      <c r="T86" s="17"/>
+      <c r="U86" s="17"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="137" t="s">
@@ -4061,40 +4067,40 @@
       <c r="C87" s="137"/>
       <c r="D87" s="137"/>
       <c r="E87" s="137"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="9"/>
-      <c r="I87" s="12"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="9"/>
-      <c r="L87" s="9"/>
-      <c r="M87" s="12"/>
-      <c r="N87" s="18"/>
-      <c r="O87" s="18"/>
-      <c r="P87" s="18"/>
-      <c r="Q87" s="18"/>
-      <c r="R87" s="18"/>
-      <c r="S87" s="18"/>
-      <c r="T87" s="18"/>
-      <c r="U87" s="18"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="11"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+      <c r="M87" s="11"/>
+      <c r="N87" s="17"/>
+      <c r="O87" s="17"/>
+      <c r="P87" s="17"/>
+      <c r="Q87" s="17"/>
+      <c r="R87" s="17"/>
+      <c r="S87" s="17"/>
+      <c r="T87" s="17"/>
+      <c r="U87" s="17"/>
     </row>
     <row r="88" spans="1:21" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="18"/>
-      <c r="B88" s="18"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="18"/>
-      <c r="E88" s="18"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="18"/>
-      <c r="H88" s="18"/>
-      <c r="I88" s="18"/>
-      <c r="J88" s="18"/>
-      <c r="K88" s="18"/>
-      <c r="L88" s="18"/>
-      <c r="M88" s="18"/>
-      <c r="N88" s="18"/>
-      <c r="T88" s="18"/>
-      <c r="U88" s="18"/>
+      <c r="A88" s="17"/>
+      <c r="B88" s="17"/>
+      <c r="C88" s="17"/>
+      <c r="D88" s="17"/>
+      <c r="E88" s="17"/>
+      <c r="F88" s="17"/>
+      <c r="G88" s="17"/>
+      <c r="H88" s="17"/>
+      <c r="I88" s="17"/>
+      <c r="J88" s="17"/>
+      <c r="K88" s="17"/>
+      <c r="L88" s="17"/>
+      <c r="M88" s="17"/>
+      <c r="N88" s="17"/>
+      <c r="T88" s="17"/>
+      <c r="U88" s="17"/>
     </row>
     <row r="89" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="106" t="s">
@@ -4104,7 +4110,7 @@
       <c r="C89" s="107"/>
       <c r="D89" s="107"/>
       <c r="E89" s="108"/>
-      <c r="F89" s="33"/>
+      <c r="F89" s="32"/>
       <c r="G89" s="87" t="s">
         <v>104</v>
       </c>
@@ -4112,18 +4118,18 @@
       <c r="I89" s="88"/>
       <c r="J89" s="88"/>
       <c r="K89" s="89"/>
-      <c r="L89" s="33"/>
-      <c r="M89" s="71" t="s">
+      <c r="L89" s="32"/>
+      <c r="M89" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="N89" s="72"/>
-      <c r="O89" s="72"/>
-      <c r="P89" s="72"/>
-      <c r="Q89" s="72"/>
-      <c r="R89" s="72"/>
+      <c r="N89" s="75"/>
+      <c r="O89" s="75"/>
+      <c r="P89" s="75"/>
+      <c r="Q89" s="75"/>
+      <c r="R89" s="75"/>
       <c r="S89" s="86"/>
-      <c r="T89" s="35"/>
-      <c r="U89" s="18"/>
+      <c r="T89" s="34"/>
+      <c r="U89" s="17"/>
     </row>
     <row r="90" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="109"/>
@@ -4131,32 +4137,32 @@
       <c r="C90" s="110"/>
       <c r="D90" s="110"/>
       <c r="E90" s="111"/>
-      <c r="F90" s="33"/>
-      <c r="G90" s="48" t="s">
+      <c r="F90" s="32"/>
+      <c r="G90" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="H90" s="48"/>
-      <c r="I90" s="48"/>
-      <c r="J90" s="48"/>
-      <c r="K90" s="48" t="s">
+      <c r="H90" s="47"/>
+      <c r="I90" s="47"/>
+      <c r="J90" s="47"/>
+      <c r="K90" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="L90" s="33"/>
+      <c r="L90" s="32"/>
       <c r="M90" s="56" t="s">
         <v>75</v>
       </c>
       <c r="N90" s="56"/>
-      <c r="O90" s="30"/>
-      <c r="P90" s="22" t="s">
+      <c r="O90" s="29"/>
+      <c r="P90" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="Q90" s="22"/>
+      <c r="Q90" s="21"/>
       <c r="R90" s="112" t="s">
         <v>10</v>
       </c>
       <c r="S90" s="114"/>
-      <c r="T90" s="33"/>
-      <c r="U90" s="18"/>
+      <c r="T90" s="32"/>
+      <c r="U90" s="17"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="112" t="s">
@@ -4165,39 +4171,39 @@
       <c r="B91" s="113"/>
       <c r="C91" s="113"/>
       <c r="D91" s="114"/>
-      <c r="E91" s="48" t="s">
+      <c r="E91" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="F91" s="33"/>
-      <c r="G91" s="48"/>
-      <c r="H91" s="48"/>
-      <c r="I91" s="48"/>
-      <c r="J91" s="48"/>
-      <c r="K91" s="48"/>
-      <c r="L91" s="33"/>
+      <c r="F91" s="32"/>
+      <c r="G91" s="47"/>
+      <c r="H91" s="47"/>
+      <c r="I91" s="47"/>
+      <c r="J91" s="47"/>
+      <c r="K91" s="47"/>
+      <c r="L91" s="32"/>
       <c r="M91" s="56"/>
       <c r="N91" s="56"/>
-      <c r="O91" s="22" t="s">
+      <c r="O91" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="P91" s="22" t="s">
+      <c r="P91" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="22" t="s">
+      <c r="Q91" s="21" t="s">
         <v>9</v>
       </c>
       <c r="R91" s="115"/>
       <c r="S91" s="117"/>
-      <c r="T91" s="33"/>
-      <c r="U91" s="18"/>
+      <c r="T91" s="32"/>
+      <c r="U91" s="17"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="115"/>
       <c r="B92" s="116"/>
       <c r="C92" s="116"/>
       <c r="D92" s="117"/>
-      <c r="E92" s="48"/>
-      <c r="F92" s="33"/>
+      <c r="E92" s="47"/>
+      <c r="F92" s="32"/>
       <c r="G92" s="90" t="s">
         <v>105</v>
       </c>
@@ -4206,21 +4212,21 @@
         <v>77</v>
       </c>
       <c r="J92" s="91"/>
-      <c r="K92" s="4"/>
-      <c r="L92" s="33"/>
-      <c r="M92" s="73" t="s">
+      <c r="K92" s="3"/>
+      <c r="L92" s="32"/>
+      <c r="M92" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="N92" s="73"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
-      <c r="Q92" s="4"/>
-      <c r="R92" s="69"/>
-      <c r="S92" s="70"/>
-      <c r="T92" s="34" t="s">
+      <c r="N92" s="62"/>
+      <c r="O92" s="3"/>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="3"/>
+      <c r="R92" s="64"/>
+      <c r="S92" s="65"/>
+      <c r="T92" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="U92" s="18"/>
+      <c r="U92" s="17"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="90" t="s">
@@ -4231,29 +4237,29 @@
         <v>77</v>
       </c>
       <c r="D93" s="98"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="33"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="32"/>
       <c r="G93" s="90"/>
       <c r="H93" s="90"/>
       <c r="I93" s="92" t="s">
         <v>78</v>
       </c>
       <c r="J93" s="92"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="33"/>
-      <c r="M93" s="74" t="s">
+      <c r="K93" s="3"/>
+      <c r="L93" s="32"/>
+      <c r="M93" s="63" t="s">
         <v>78</v>
       </c>
-      <c r="N93" s="74"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
-      <c r="R93" s="69"/>
-      <c r="S93" s="70"/>
-      <c r="T93" s="34" t="s">
+      <c r="N93" s="63"/>
+      <c r="O93" s="3"/>
+      <c r="P93" s="3"/>
+      <c r="Q93" s="3"/>
+      <c r="R93" s="64"/>
+      <c r="S93" s="65"/>
+      <c r="T93" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="U93" s="18"/>
+      <c r="U93" s="17"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="90"/>
@@ -4262,29 +4268,29 @@
         <v>78</v>
       </c>
       <c r="D94" s="102"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="33"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="32"/>
       <c r="G94" s="90"/>
       <c r="H94" s="90"/>
       <c r="I94" s="92" t="s">
         <v>79</v>
       </c>
       <c r="J94" s="92"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="33"/>
-      <c r="M94" s="74" t="s">
+      <c r="K94" s="3"/>
+      <c r="L94" s="32"/>
+      <c r="M94" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="N94" s="74"/>
-      <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
-      <c r="Q94" s="4"/>
-      <c r="R94" s="69"/>
-      <c r="S94" s="70"/>
-      <c r="T94" s="34" t="s">
+      <c r="N94" s="63"/>
+      <c r="O94" s="3"/>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="64"/>
+      <c r="S94" s="65"/>
+      <c r="T94" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="U94" s="18"/>
+      <c r="U94" s="17"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="90"/>
@@ -4293,29 +4299,29 @@
         <v>79</v>
       </c>
       <c r="D95" s="102"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="33"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="32"/>
       <c r="G95" s="90"/>
       <c r="H95" s="90"/>
       <c r="I95" s="92" t="s">
         <v>80</v>
       </c>
       <c r="J95" s="92"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="33"/>
-      <c r="M95" s="74" t="s">
+      <c r="K95" s="3"/>
+      <c r="L95" s="32"/>
+      <c r="M95" s="63" t="s">
         <v>115</v>
       </c>
-      <c r="N95" s="74"/>
-      <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
-      <c r="Q95" s="4"/>
-      <c r="R95" s="69"/>
-      <c r="S95" s="70"/>
-      <c r="T95" s="34" t="s">
+      <c r="N95" s="63"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="64"/>
+      <c r="S95" s="65"/>
+      <c r="T95" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="U95" s="18"/>
+      <c r="U95" s="17"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="90"/>
@@ -4324,31 +4330,31 @@
         <v>80</v>
       </c>
       <c r="D96" s="102"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="33"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="32"/>
       <c r="G96" s="90"/>
       <c r="H96" s="90"/>
       <c r="I96" s="93" t="s">
         <v>106</v>
       </c>
       <c r="J96" s="93"/>
-      <c r="K96" s="4"/>
-      <c r="L96" s="34" t="s">
+      <c r="K96" s="3"/>
+      <c r="L96" s="33" t="s">
         <v>85</v>
       </c>
       <c r="M96" s="61" t="s">
         <v>116</v>
       </c>
       <c r="N96" s="61"/>
-      <c r="O96" s="4"/>
-      <c r="P96" s="4"/>
-      <c r="Q96" s="4"/>
-      <c r="R96" s="69"/>
-      <c r="S96" s="70"/>
-      <c r="T96" s="34" t="s">
+      <c r="O96" s="3"/>
+      <c r="P96" s="3"/>
+      <c r="Q96" s="3"/>
+      <c r="R96" s="64"/>
+      <c r="S96" s="65"/>
+      <c r="T96" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="U96" s="18"/>
+      <c r="U96" s="17"/>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="90"/>
@@ -4357,29 +4363,29 @@
         <v>81</v>
       </c>
       <c r="D97" s="102"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="33"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="32"/>
       <c r="G97" s="77" t="s">
         <v>87</v>
       </c>
       <c r="H97" s="77"/>
       <c r="I97" s="77"/>
       <c r="J97" s="77"/>
-      <c r="K97" s="4"/>
-      <c r="L97" s="34" t="s">
+      <c r="K97" s="3"/>
+      <c r="L97" s="33" t="s">
         <v>85</v>
       </c>
       <c r="M97" s="79" t="s">
         <v>117</v>
       </c>
       <c r="N97" s="80"/>
-      <c r="O97" s="4"/>
-      <c r="P97" s="4"/>
-      <c r="Q97" s="4"/>
-      <c r="R97" s="69"/>
-      <c r="S97" s="70"/>
-      <c r="T97" s="35"/>
-      <c r="U97" s="18"/>
+      <c r="O97" s="3"/>
+      <c r="P97" s="3"/>
+      <c r="Q97" s="3"/>
+      <c r="R97" s="64"/>
+      <c r="S97" s="65"/>
+      <c r="T97" s="34"/>
+      <c r="U97" s="17"/>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="90" t="s">
@@ -4390,29 +4396,29 @@
         <v>77</v>
       </c>
       <c r="D98" s="98"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="33"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="32"/>
       <c r="G98" s="77" t="s">
         <v>107</v>
       </c>
       <c r="H98" s="77"/>
       <c r="I98" s="77"/>
       <c r="J98" s="77"/>
-      <c r="K98" s="4"/>
-      <c r="L98" s="34" t="s">
+      <c r="K98" s="3"/>
+      <c r="L98" s="33" t="s">
         <v>85</v>
       </c>
       <c r="M98" s="81" t="s">
         <v>141</v>
       </c>
       <c r="N98" s="82"/>
-      <c r="O98" s="4"/>
-      <c r="P98" s="4"/>
-      <c r="Q98" s="4"/>
-      <c r="R98" s="69"/>
-      <c r="S98" s="70"/>
-      <c r="T98" s="35"/>
-      <c r="U98" s="18"/>
+      <c r="O98" s="3"/>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3"/>
+      <c r="R98" s="64"/>
+      <c r="S98" s="65"/>
+      <c r="T98" s="34"/>
+      <c r="U98" s="17"/>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="90"/>
@@ -4421,29 +4427,29 @@
         <v>78</v>
       </c>
       <c r="D99" s="100"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="33"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="32"/>
       <c r="G99" s="77" t="s">
         <v>108</v>
       </c>
       <c r="H99" s="77"/>
       <c r="I99" s="77"/>
       <c r="J99" s="77"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="34" t="s">
+      <c r="K99" s="3"/>
+      <c r="L99" s="33" t="s">
         <v>85</v>
       </c>
       <c r="M99" s="78" t="s">
         <v>118</v>
       </c>
       <c r="N99" s="78"/>
-      <c r="O99" s="4"/>
-      <c r="P99" s="4"/>
-      <c r="Q99" s="4"/>
-      <c r="R99" s="69"/>
-      <c r="S99" s="70"/>
-      <c r="T99" s="46"/>
-      <c r="U99" s="18"/>
+      <c r="O99" s="3"/>
+      <c r="P99" s="3"/>
+      <c r="Q99" s="3"/>
+      <c r="R99" s="64"/>
+      <c r="S99" s="65"/>
+      <c r="T99" s="44"/>
+      <c r="U99" s="17"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="90"/>
@@ -4452,29 +4458,29 @@
         <v>79</v>
       </c>
       <c r="D100" s="100"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="33"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="32"/>
       <c r="G100" s="77" t="s">
         <v>109</v>
       </c>
       <c r="H100" s="77"/>
       <c r="I100" s="77"/>
       <c r="J100" s="77"/>
-      <c r="K100" s="4"/>
-      <c r="L100" s="34" t="s">
+      <c r="K100" s="3"/>
+      <c r="L100" s="33" t="s">
         <v>85</v>
       </c>
       <c r="M100" s="77" t="s">
         <v>84</v>
       </c>
       <c r="N100" s="77"/>
-      <c r="O100" s="4"/>
-      <c r="P100" s="4"/>
-      <c r="Q100" s="4"/>
-      <c r="R100" s="69"/>
-      <c r="S100" s="70"/>
-      <c r="T100" s="35"/>
-      <c r="U100" s="18"/>
+      <c r="O100" s="3"/>
+      <c r="P100" s="3"/>
+      <c r="Q100" s="3"/>
+      <c r="R100" s="64"/>
+      <c r="S100" s="65"/>
+      <c r="T100" s="34"/>
+      <c r="U100" s="17"/>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="90"/>
@@ -4483,29 +4489,29 @@
         <v>80</v>
       </c>
       <c r="D101" s="100"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="33"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="32"/>
       <c r="G101" s="77" t="s">
         <v>110</v>
       </c>
       <c r="H101" s="77"/>
       <c r="I101" s="77"/>
       <c r="J101" s="77"/>
-      <c r="K101" s="4"/>
-      <c r="L101" s="34" t="s">
+      <c r="K101" s="3"/>
+      <c r="L101" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="M101" s="36" t="s">
+      <c r="M101" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="N101" s="37"/>
-      <c r="O101" s="37"/>
-      <c r="P101" s="37"/>
-      <c r="Q101" s="37"/>
-      <c r="R101" s="37"/>
-      <c r="S101" s="37"/>
-      <c r="T101" s="37"/>
-      <c r="U101" s="18"/>
+      <c r="N101" s="36"/>
+      <c r="O101" s="36"/>
+      <c r="P101" s="36"/>
+      <c r="Q101" s="36"/>
+      <c r="R101" s="36"/>
+      <c r="S101" s="36"/>
+      <c r="T101" s="36"/>
+      <c r="U101" s="17"/>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="90"/>
@@ -4514,27 +4520,27 @@
         <v>81</v>
       </c>
       <c r="D102" s="100"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="33"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="32"/>
       <c r="G102" s="77" t="s">
         <v>111</v>
       </c>
       <c r="H102" s="77"/>
       <c r="I102" s="77"/>
       <c r="J102" s="77"/>
-      <c r="K102" s="4"/>
-      <c r="L102" s="34" t="s">
+      <c r="K102" s="3"/>
+      <c r="L102" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="M102" s="18"/>
-      <c r="N102" s="18"/>
-      <c r="O102" s="18"/>
-      <c r="P102" s="18"/>
-      <c r="Q102" s="18"/>
-      <c r="R102" s="18"/>
-      <c r="S102" s="18"/>
-      <c r="T102" s="18"/>
-      <c r="U102" s="18"/>
+      <c r="M102" s="17"/>
+      <c r="N102" s="17"/>
+      <c r="O102" s="17"/>
+      <c r="P102" s="17"/>
+      <c r="Q102" s="17"/>
+      <c r="R102" s="17"/>
+      <c r="S102" s="17"/>
+      <c r="T102" s="17"/>
+      <c r="U102" s="17"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="94" t="s">
@@ -4543,27 +4549,27 @@
       <c r="B103" s="95"/>
       <c r="C103" s="95"/>
       <c r="D103" s="96"/>
-      <c r="E103" s="4"/>
-      <c r="F103" s="33"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="32"/>
       <c r="G103" s="77" t="s">
         <v>112</v>
       </c>
       <c r="H103" s="77"/>
       <c r="I103" s="77"/>
       <c r="J103" s="77"/>
-      <c r="K103" s="4"/>
-      <c r="L103" s="34" t="s">
+      <c r="K103" s="3"/>
+      <c r="L103" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="M103" s="18"/>
-      <c r="N103" s="18"/>
-      <c r="O103" s="18"/>
-      <c r="P103" s="18"/>
-      <c r="Q103" s="18"/>
-      <c r="R103" s="18"/>
-      <c r="S103" s="18"/>
-      <c r="T103" s="18"/>
-      <c r="U103" s="18"/>
+      <c r="M103" s="17"/>
+      <c r="N103" s="17"/>
+      <c r="O103" s="17"/>
+      <c r="P103" s="17"/>
+      <c r="Q103" s="17"/>
+      <c r="R103" s="17"/>
+      <c r="S103" s="17"/>
+      <c r="T103" s="17"/>
+      <c r="U103" s="17"/>
     </row>
     <row r="104" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="83" t="s">
@@ -4572,8 +4578,8 @@
       <c r="B104" s="84"/>
       <c r="C104" s="84"/>
       <c r="D104" s="85"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="34" t="s">
+      <c r="E104" s="3"/>
+      <c r="F104" s="33" t="s">
         <v>85</v>
       </c>
       <c r="G104" s="77" t="s">
@@ -4582,17 +4588,17 @@
       <c r="H104" s="77"/>
       <c r="I104" s="77"/>
       <c r="J104" s="77"/>
-      <c r="K104" s="4"/>
-      <c r="L104" s="35"/>
-      <c r="M104" s="18"/>
-      <c r="N104" s="18"/>
-      <c r="O104" s="18"/>
-      <c r="P104" s="18"/>
-      <c r="Q104" s="18"/>
-      <c r="R104" s="18"/>
-      <c r="S104" s="18"/>
-      <c r="T104" s="18"/>
-      <c r="U104" s="18"/>
+      <c r="K104" s="3"/>
+      <c r="L104" s="34"/>
+      <c r="M104" s="17"/>
+      <c r="N104" s="17"/>
+      <c r="O104" s="17"/>
+      <c r="P104" s="17"/>
+      <c r="Q104" s="17"/>
+      <c r="R104" s="17"/>
+      <c r="S104" s="17"/>
+      <c r="T104" s="17"/>
+      <c r="U104" s="17"/>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="83" t="s">
@@ -4601,29 +4607,29 @@
       <c r="B105" s="84"/>
       <c r="C105" s="84"/>
       <c r="D105" s="85"/>
-      <c r="E105" s="4"/>
-      <c r="F105" s="34" t="s">
+      <c r="E105" s="3"/>
+      <c r="F105" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G105" s="23" t="s">
+      <c r="G105" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="H105" s="24"/>
-      <c r="I105" s="24"/>
-      <c r="J105" s="24"/>
-      <c r="K105" s="24"/>
-      <c r="L105" s="35"/>
-      <c r="M105" s="18"/>
-      <c r="N105" s="18"/>
-      <c r="O105" s="18"/>
-      <c r="P105" s="18"/>
-      <c r="Q105" s="71" t="s">
+      <c r="H105" s="23"/>
+      <c r="I105" s="23"/>
+      <c r="J105" s="23"/>
+      <c r="K105" s="23"/>
+      <c r="L105" s="34"/>
+      <c r="M105" s="17"/>
+      <c r="N105" s="17"/>
+      <c r="O105" s="17"/>
+      <c r="P105" s="17"/>
+      <c r="Q105" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="R105" s="72"/>
-      <c r="S105" s="72"/>
-      <c r="T105" s="72"/>
-      <c r="U105" s="18"/>
+      <c r="R105" s="75"/>
+      <c r="S105" s="75"/>
+      <c r="T105" s="75"/>
+      <c r="U105" s="17"/>
     </row>
     <row r="106" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="83" t="s">
@@ -4632,8 +4638,8 @@
       <c r="B106" s="84"/>
       <c r="C106" s="84"/>
       <c r="D106" s="85"/>
-      <c r="E106" s="4"/>
-      <c r="F106" s="34" t="s">
+      <c r="E106" s="3"/>
+      <c r="F106" s="33" t="s">
         <v>85</v>
       </c>
       <c r="G106" s="56" t="s">
@@ -4642,27 +4648,27 @@
       <c r="H106" s="56"/>
       <c r="I106" s="56"/>
       <c r="J106" s="56"/>
-      <c r="K106" s="44"/>
-      <c r="L106" s="18"/>
-      <c r="M106" s="47" t="s">
+      <c r="K106" s="42"/>
+      <c r="L106" s="17"/>
+      <c r="M106" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="N106" s="47"/>
-      <c r="O106" s="47"/>
-      <c r="P106" s="18"/>
-      <c r="Q106" s="22" t="s">
+      <c r="N106" s="46"/>
+      <c r="O106" s="46"/>
+      <c r="P106" s="17"/>
+      <c r="Q106" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="R106" s="22" t="s">
+      <c r="R106" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="S106" s="22" t="s">
+      <c r="S106" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="T106" s="22" t="s">
+      <c r="T106" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="U106" s="18"/>
+      <c r="U106" s="17"/>
     </row>
     <row r="107" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="83" t="s">
@@ -4671,29 +4677,29 @@
       <c r="B107" s="84"/>
       <c r="C107" s="84"/>
       <c r="D107" s="85"/>
-      <c r="E107" s="4"/>
-      <c r="F107" s="34" t="s">
+      <c r="E107" s="3"/>
+      <c r="F107" s="33" t="s">
         <v>85</v>
       </c>
       <c r="G107" s="56"/>
       <c r="H107" s="56"/>
       <c r="I107" s="56"/>
       <c r="J107" s="56"/>
-      <c r="K107" s="44"/>
-      <c r="L107" s="18"/>
-      <c r="M107" s="47" t="s">
+      <c r="K107" s="42"/>
+      <c r="L107" s="17"/>
+      <c r="M107" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="N107" s="47"/>
-      <c r="O107" s="47"/>
-      <c r="P107" s="18"/>
-      <c r="Q107" s="38" t="s">
+      <c r="N107" s="46"/>
+      <c r="O107" s="46"/>
+      <c r="P107" s="17"/>
+      <c r="Q107" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="R107" s="38"/>
-      <c r="S107" s="38"/>
-      <c r="T107" s="1"/>
-      <c r="U107" s="18"/>
+      <c r="R107" s="3"/>
+      <c r="S107" s="3"/>
+      <c r="T107" s="3"/>
+      <c r="U107" s="17"/>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="83" t="s">
@@ -4702,8 +4708,8 @@
       <c r="B108" s="84"/>
       <c r="C108" s="84"/>
       <c r="D108" s="85"/>
-      <c r="E108" s="4"/>
-      <c r="F108" s="34" t="s">
+      <c r="E108" s="3"/>
+      <c r="F108" s="33" t="s">
         <v>85</v>
       </c>
       <c r="G108" s="56" t="s">
@@ -4714,23 +4720,23 @@
         <v>121</v>
       </c>
       <c r="J108" s="76"/>
-      <c r="K108" s="31"/>
-      <c r="L108" s="18"/>
-      <c r="M108" s="48" t="s">
+      <c r="K108" s="30"/>
+      <c r="L108" s="17"/>
+      <c r="M108" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="N108" s="48"/>
-      <c r="O108" s="48" t="s">
+      <c r="N108" s="47"/>
+      <c r="O108" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="P108" s="18"/>
-      <c r="Q108" s="38" t="s">
+      <c r="P108" s="17"/>
+      <c r="Q108" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="R108" s="38"/>
-      <c r="S108" s="38"/>
-      <c r="T108" s="1"/>
-      <c r="U108" s="18"/>
+      <c r="R108" s="3"/>
+      <c r="S108" s="3"/>
+      <c r="T108" s="3"/>
+      <c r="U108" s="17"/>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="83" t="s">
@@ -4739,27 +4745,27 @@
       <c r="B109" s="84"/>
       <c r="C109" s="84"/>
       <c r="D109" s="85"/>
-      <c r="E109" s="4"/>
-      <c r="F109" s="34" t="s">
+      <c r="E109" s="3"/>
+      <c r="F109" s="33" t="s">
         <v>85</v>
       </c>
       <c r="G109" s="56"/>
       <c r="H109" s="56"/>
       <c r="I109" s="76"/>
       <c r="J109" s="76"/>
-      <c r="K109" s="31"/>
-      <c r="L109" s="18"/>
-      <c r="M109" s="48"/>
-      <c r="N109" s="48"/>
-      <c r="O109" s="48"/>
-      <c r="P109" s="18"/>
-      <c r="Q109" s="38" t="s">
+      <c r="K109" s="30"/>
+      <c r="L109" s="17"/>
+      <c r="M109" s="47"/>
+      <c r="N109" s="47"/>
+      <c r="O109" s="47"/>
+      <c r="P109" s="17"/>
+      <c r="Q109" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="R109" s="38"/>
-      <c r="S109" s="38"/>
-      <c r="T109" s="1"/>
-      <c r="U109" s="18"/>
+      <c r="R109" s="3"/>
+      <c r="S109" s="3"/>
+      <c r="T109" s="3"/>
+      <c r="U109" s="17"/>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="83" t="s">
@@ -4768,31 +4774,31 @@
       <c r="B110" s="84"/>
       <c r="C110" s="84"/>
       <c r="D110" s="85"/>
-      <c r="E110" s="4"/>
-      <c r="F110" s="34" t="s">
+      <c r="E110" s="3"/>
+      <c r="F110" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G110" s="73" t="s">
+      <c r="G110" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="H110" s="73"/>
-      <c r="I110" s="75"/>
-      <c r="J110" s="75"/>
-      <c r="K110" s="32"/>
-      <c r="L110" s="18"/>
-      <c r="M110" s="74" t="s">
+      <c r="H110" s="62"/>
+      <c r="I110" s="73"/>
+      <c r="J110" s="73"/>
+      <c r="K110" s="31"/>
+      <c r="L110" s="17"/>
+      <c r="M110" s="63" t="s">
         <v>78</v>
       </c>
-      <c r="N110" s="74"/>
-      <c r="O110" s="4"/>
-      <c r="P110" s="18"/>
-      <c r="Q110" s="38" t="s">
+      <c r="N110" s="63"/>
+      <c r="O110" s="3"/>
+      <c r="P110" s="17"/>
+      <c r="Q110" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="R110" s="38"/>
-      <c r="S110" s="38"/>
-      <c r="T110" s="1"/>
-      <c r="U110" s="18"/>
+      <c r="R110" s="3"/>
+      <c r="S110" s="3"/>
+      <c r="T110" s="3"/>
+      <c r="U110" s="17"/>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="83" t="s">
@@ -4801,31 +4807,31 @@
       <c r="B111" s="84"/>
       <c r="C111" s="84"/>
       <c r="D111" s="85"/>
-      <c r="E111" s="4"/>
-      <c r="F111" s="34" t="s">
+      <c r="E111" s="3"/>
+      <c r="F111" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G111" s="74" t="s">
+      <c r="G111" s="63" t="s">
         <v>78</v>
       </c>
-      <c r="H111" s="74"/>
-      <c r="I111" s="75"/>
-      <c r="J111" s="75"/>
-      <c r="K111" s="32"/>
-      <c r="L111" s="18"/>
-      <c r="M111" s="74" t="s">
+      <c r="H111" s="63"/>
+      <c r="I111" s="73"/>
+      <c r="J111" s="73"/>
+      <c r="K111" s="31"/>
+      <c r="L111" s="17"/>
+      <c r="M111" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="N111" s="74"/>
-      <c r="O111" s="4"/>
-      <c r="P111" s="18"/>
-      <c r="Q111" s="38" t="s">
+      <c r="N111" s="63"/>
+      <c r="O111" s="3"/>
+      <c r="P111" s="17"/>
+      <c r="Q111" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="R111" s="38"/>
-      <c r="S111" s="38"/>
-      <c r="T111" s="1"/>
-      <c r="U111" s="18"/>
+      <c r="R111" s="3"/>
+      <c r="S111" s="3"/>
+      <c r="T111" s="3"/>
+      <c r="U111" s="17"/>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="83" t="s">
@@ -4834,31 +4840,31 @@
       <c r="B112" s="84"/>
       <c r="C112" s="84"/>
       <c r="D112" s="85"/>
-      <c r="E112" s="4"/>
-      <c r="F112" s="34" t="s">
+      <c r="E112" s="3"/>
+      <c r="F112" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G112" s="74" t="s">
+      <c r="G112" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="H112" s="74"/>
-      <c r="I112" s="75"/>
-      <c r="J112" s="75"/>
-      <c r="K112" s="32"/>
-      <c r="L112" s="18"/>
-      <c r="M112" s="74" t="s">
+      <c r="H112" s="63"/>
+      <c r="I112" s="73"/>
+      <c r="J112" s="73"/>
+      <c r="K112" s="31"/>
+      <c r="L112" s="17"/>
+      <c r="M112" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="N112" s="74"/>
-      <c r="O112" s="4"/>
-      <c r="P112" s="18"/>
-      <c r="Q112" s="38" t="s">
+      <c r="N112" s="63"/>
+      <c r="O112" s="3"/>
+      <c r="P112" s="17"/>
+      <c r="Q112" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="R112" s="38"/>
-      <c r="S112" s="38"/>
-      <c r="T112" s="1"/>
-      <c r="U112" s="18"/>
+      <c r="R112" s="3"/>
+      <c r="S112" s="3"/>
+      <c r="T112" s="3"/>
+      <c r="U112" s="17"/>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="83" t="s">
@@ -4867,31 +4873,31 @@
       <c r="B113" s="84"/>
       <c r="C113" s="84"/>
       <c r="D113" s="85"/>
-      <c r="E113" s="4"/>
-      <c r="F113" s="34" t="s">
+      <c r="E113" s="3"/>
+      <c r="F113" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G113" s="74" t="s">
+      <c r="G113" s="63" t="s">
         <v>115</v>
       </c>
-      <c r="H113" s="74"/>
-      <c r="I113" s="75"/>
-      <c r="J113" s="75"/>
-      <c r="K113" s="32"/>
-      <c r="L113" s="18"/>
+      <c r="H113" s="63"/>
+      <c r="I113" s="73"/>
+      <c r="J113" s="73"/>
+      <c r="K113" s="31"/>
+      <c r="L113" s="17"/>
       <c r="M113" s="50" t="s">
         <v>126</v>
       </c>
       <c r="N113" s="50"/>
-      <c r="O113" s="4"/>
-      <c r="P113" s="18"/>
-      <c r="Q113" s="39" t="s">
+      <c r="O113" s="3"/>
+      <c r="P113" s="17"/>
+      <c r="Q113" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="R113" s="43"/>
-      <c r="S113" s="43"/>
-      <c r="T113" s="43"/>
-      <c r="U113" s="18"/>
+      <c r="R113" s="3"/>
+      <c r="S113" s="3"/>
+      <c r="T113" s="3"/>
+      <c r="U113" s="17"/>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="83" t="s">
@@ -4900,27 +4906,27 @@
       <c r="B114" s="84"/>
       <c r="C114" s="84"/>
       <c r="D114" s="85"/>
-      <c r="E114" s="4"/>
-      <c r="F114" s="34" t="s">
+      <c r="E114" s="3"/>
+      <c r="F114" s="33" t="s">
         <v>85</v>
       </c>
       <c r="G114" s="50" t="s">
         <v>122</v>
       </c>
       <c r="H114" s="50"/>
-      <c r="I114" s="75"/>
-      <c r="J114" s="75"/>
-      <c r="K114" s="32"/>
-      <c r="L114" s="18"/>
-      <c r="M114" s="18"/>
-      <c r="N114" s="18"/>
-      <c r="O114" s="18"/>
-      <c r="P114" s="18"/>
-      <c r="Q114" s="18"/>
-      <c r="R114" s="18"/>
-      <c r="S114" s="18"/>
-      <c r="T114" s="18"/>
-      <c r="U114" s="18"/>
+      <c r="I114" s="73"/>
+      <c r="J114" s="73"/>
+      <c r="K114" s="31"/>
+      <c r="L114" s="17"/>
+      <c r="M114" s="17"/>
+      <c r="N114" s="17"/>
+      <c r="O114" s="17"/>
+      <c r="P114" s="17"/>
+      <c r="Q114" s="17"/>
+      <c r="R114" s="17"/>
+      <c r="S114" s="17"/>
+      <c r="T114" s="17"/>
+      <c r="U114" s="17"/>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="83" t="s">
@@ -4929,25 +4935,25 @@
       <c r="B115" s="84"/>
       <c r="C115" s="84"/>
       <c r="D115" s="85"/>
-      <c r="E115" s="4"/>
-      <c r="F115" s="34" t="s">
+      <c r="E115" s="3"/>
+      <c r="F115" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G115" s="18"/>
-      <c r="H115" s="18"/>
-      <c r="I115" s="18"/>
-      <c r="J115" s="18"/>
-      <c r="K115" s="18"/>
-      <c r="L115" s="18"/>
-      <c r="M115" s="18"/>
-      <c r="N115" s="18"/>
-      <c r="O115" s="18"/>
-      <c r="P115" s="18"/>
-      <c r="Q115" s="18"/>
-      <c r="R115" s="18"/>
-      <c r="S115" s="18"/>
-      <c r="T115" s="18"/>
-      <c r="U115" s="18"/>
+      <c r="G115" s="17"/>
+      <c r="H115" s="17"/>
+      <c r="I115" s="17"/>
+      <c r="J115" s="17"/>
+      <c r="K115" s="17"/>
+      <c r="L115" s="17"/>
+      <c r="M115" s="17"/>
+      <c r="N115" s="17"/>
+      <c r="O115" s="17"/>
+      <c r="P115" s="17"/>
+      <c r="Q115" s="17"/>
+      <c r="R115" s="17"/>
+      <c r="S115" s="17"/>
+      <c r="T115" s="17"/>
+      <c r="U115" s="17"/>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="83" t="s">
@@ -4956,25 +4962,25 @@
       <c r="B116" s="84"/>
       <c r="C116" s="84"/>
       <c r="D116" s="85"/>
-      <c r="E116" s="4"/>
-      <c r="F116" s="34" t="s">
+      <c r="E116" s="3"/>
+      <c r="F116" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G116" s="18"/>
-      <c r="H116" s="18"/>
-      <c r="I116" s="18"/>
-      <c r="J116" s="18"/>
-      <c r="K116" s="18"/>
-      <c r="L116" s="18"/>
-      <c r="M116" s="18"/>
-      <c r="N116" s="18"/>
-      <c r="O116" s="18"/>
-      <c r="P116" s="18"/>
-      <c r="Q116" s="18"/>
-      <c r="R116" s="18"/>
-      <c r="S116" s="18"/>
-      <c r="T116" s="18"/>
-      <c r="U116" s="18"/>
+      <c r="G116" s="17"/>
+      <c r="H116" s="17"/>
+      <c r="I116" s="17"/>
+      <c r="J116" s="17"/>
+      <c r="K116" s="17"/>
+      <c r="L116" s="17"/>
+      <c r="M116" s="17"/>
+      <c r="N116" s="17"/>
+      <c r="O116" s="17"/>
+      <c r="P116" s="17"/>
+      <c r="Q116" s="17"/>
+      <c r="R116" s="17"/>
+      <c r="S116" s="17"/>
+      <c r="T116" s="17"/>
+      <c r="U116" s="17"/>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="83" t="s">
@@ -4983,25 +4989,25 @@
       <c r="B117" s="84"/>
       <c r="C117" s="84"/>
       <c r="D117" s="85"/>
-      <c r="E117" s="4"/>
-      <c r="F117" s="34" t="s">
+      <c r="E117" s="3"/>
+      <c r="F117" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G117" s="18"/>
-      <c r="H117" s="18"/>
-      <c r="I117" s="18"/>
-      <c r="J117" s="18"/>
-      <c r="K117" s="18"/>
-      <c r="L117" s="18"/>
-      <c r="M117" s="18"/>
-      <c r="N117" s="18"/>
-      <c r="O117" s="18"/>
-      <c r="P117" s="18"/>
-      <c r="Q117" s="18"/>
-      <c r="R117" s="18"/>
-      <c r="S117" s="18"/>
-      <c r="T117" s="18"/>
-      <c r="U117" s="18"/>
+      <c r="G117" s="17"/>
+      <c r="H117" s="17"/>
+      <c r="I117" s="17"/>
+      <c r="J117" s="17"/>
+      <c r="K117" s="17"/>
+      <c r="L117" s="17"/>
+      <c r="M117" s="17"/>
+      <c r="N117" s="17"/>
+      <c r="O117" s="17"/>
+      <c r="P117" s="17"/>
+      <c r="Q117" s="17"/>
+      <c r="R117" s="17"/>
+      <c r="S117" s="17"/>
+      <c r="T117" s="17"/>
+      <c r="U117" s="17"/>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="83" t="s">
@@ -5010,25 +5016,25 @@
       <c r="B118" s="84"/>
       <c r="C118" s="84"/>
       <c r="D118" s="85"/>
-      <c r="E118" s="4"/>
-      <c r="F118" s="34" t="s">
+      <c r="E118" s="3"/>
+      <c r="F118" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G118" s="18"/>
-      <c r="H118" s="18"/>
-      <c r="I118" s="18"/>
-      <c r="J118" s="18"/>
-      <c r="K118" s="18"/>
-      <c r="L118" s="18"/>
-      <c r="M118" s="18"/>
-      <c r="N118" s="18"/>
-      <c r="O118" s="18"/>
-      <c r="P118" s="18"/>
-      <c r="Q118" s="18"/>
-      <c r="R118" s="18"/>
-      <c r="S118" s="18"/>
-      <c r="T118" s="18"/>
-      <c r="U118" s="18"/>
+      <c r="G118" s="17"/>
+      <c r="H118" s="17"/>
+      <c r="I118" s="17"/>
+      <c r="J118" s="17"/>
+      <c r="K118" s="17"/>
+      <c r="L118" s="17"/>
+      <c r="M118" s="17"/>
+      <c r="N118" s="17"/>
+      <c r="O118" s="17"/>
+      <c r="P118" s="17"/>
+      <c r="Q118" s="17"/>
+      <c r="R118" s="17"/>
+      <c r="S118" s="17"/>
+      <c r="T118" s="17"/>
+      <c r="U118" s="17"/>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="83" t="s">
@@ -5037,25 +5043,25 @@
       <c r="B119" s="84"/>
       <c r="C119" s="84"/>
       <c r="D119" s="85"/>
-      <c r="E119" s="4"/>
-      <c r="F119" s="34" t="s">
+      <c r="E119" s="3"/>
+      <c r="F119" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G119" s="18"/>
-      <c r="H119" s="18"/>
-      <c r="I119" s="18"/>
-      <c r="J119" s="18"/>
-      <c r="K119" s="18"/>
-      <c r="L119" s="18"/>
-      <c r="M119" s="18"/>
-      <c r="N119" s="18"/>
-      <c r="O119" s="18"/>
-      <c r="P119" s="18"/>
-      <c r="Q119" s="18"/>
-      <c r="R119" s="18"/>
-      <c r="S119" s="18"/>
-      <c r="T119" s="18"/>
-      <c r="U119" s="18"/>
+      <c r="G119" s="17"/>
+      <c r="H119" s="17"/>
+      <c r="I119" s="17"/>
+      <c r="J119" s="17"/>
+      <c r="K119" s="17"/>
+      <c r="L119" s="17"/>
+      <c r="M119" s="17"/>
+      <c r="N119" s="17"/>
+      <c r="O119" s="17"/>
+      <c r="P119" s="17"/>
+      <c r="Q119" s="17"/>
+      <c r="R119" s="17"/>
+      <c r="S119" s="17"/>
+      <c r="T119" s="17"/>
+      <c r="U119" s="17"/>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="83" t="s">
@@ -5064,73 +5070,73 @@
       <c r="B120" s="84"/>
       <c r="C120" s="84"/>
       <c r="D120" s="85"/>
-      <c r="E120" s="4"/>
-      <c r="F120" s="34" t="s">
+      <c r="E120" s="3"/>
+      <c r="F120" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G120" s="18"/>
-      <c r="H120" s="18"/>
-      <c r="I120" s="18"/>
-      <c r="J120" s="18"/>
-      <c r="K120" s="18"/>
-      <c r="L120" s="18"/>
-      <c r="M120" s="18"/>
-      <c r="N120" s="18"/>
-      <c r="O120" s="18"/>
-      <c r="P120" s="18"/>
-      <c r="Q120" s="18"/>
-      <c r="R120" s="18"/>
-      <c r="S120" s="18"/>
-      <c r="T120" s="18"/>
-      <c r="U120" s="18"/>
+      <c r="G120" s="17"/>
+      <c r="H120" s="17"/>
+      <c r="I120" s="17"/>
+      <c r="J120" s="17"/>
+      <c r="K120" s="17"/>
+      <c r="L120" s="17"/>
+      <c r="M120" s="17"/>
+      <c r="N120" s="17"/>
+      <c r="O120" s="17"/>
+      <c r="P120" s="17"/>
+      <c r="Q120" s="17"/>
+      <c r="R120" s="17"/>
+      <c r="S120" s="17"/>
+      <c r="T120" s="17"/>
+      <c r="U120" s="17"/>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A121" s="36" t="s">
+      <c r="A121" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="B121" s="35"/>
-      <c r="C121" s="35"/>
-      <c r="D121" s="35"/>
-      <c r="E121" s="35"/>
-      <c r="F121" s="35"/>
-      <c r="G121" s="18"/>
-      <c r="H121" s="18"/>
-      <c r="I121" s="18"/>
-      <c r="J121" s="18"/>
-      <c r="K121" s="18"/>
-      <c r="L121" s="18"/>
-      <c r="M121" s="18"/>
-      <c r="N121" s="18"/>
-      <c r="O121" s="18"/>
-      <c r="P121" s="18"/>
-      <c r="Q121" s="18"/>
-      <c r="R121" s="18"/>
-      <c r="S121" s="18"/>
-      <c r="T121" s="18"/>
-      <c r="U121" s="18"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="34"/>
+      <c r="D121" s="34"/>
+      <c r="E121" s="34"/>
+      <c r="F121" s="34"/>
+      <c r="G121" s="17"/>
+      <c r="H121" s="17"/>
+      <c r="I121" s="17"/>
+      <c r="J121" s="17"/>
+      <c r="K121" s="17"/>
+      <c r="L121" s="17"/>
+      <c r="M121" s="17"/>
+      <c r="N121" s="17"/>
+      <c r="O121" s="17"/>
+      <c r="P121" s="17"/>
+      <c r="Q121" s="17"/>
+      <c r="R121" s="17"/>
+      <c r="S121" s="17"/>
+      <c r="T121" s="17"/>
+      <c r="U121" s="17"/>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A122" s="18"/>
-      <c r="B122" s="18"/>
-      <c r="C122" s="18"/>
-      <c r="D122" s="18"/>
-      <c r="E122" s="18"/>
-      <c r="F122" s="18"/>
-      <c r="G122" s="18"/>
-      <c r="H122" s="18"/>
-      <c r="I122" s="18"/>
-      <c r="J122" s="18"/>
-      <c r="K122" s="18"/>
-      <c r="L122" s="18"/>
-      <c r="M122" s="18"/>
-      <c r="N122" s="18"/>
-      <c r="O122" s="18"/>
-      <c r="P122" s="18"/>
-      <c r="Q122" s="18"/>
-      <c r="R122" s="18"/>
-      <c r="S122" s="18"/>
-      <c r="T122" s="18"/>
-      <c r="U122" s="18"/>
+      <c r="A122" s="17"/>
+      <c r="B122" s="17"/>
+      <c r="C122" s="17"/>
+      <c r="D122" s="17"/>
+      <c r="E122" s="17"/>
+      <c r="F122" s="17"/>
+      <c r="G122" s="17"/>
+      <c r="H122" s="17"/>
+      <c r="I122" s="17"/>
+      <c r="J122" s="17"/>
+      <c r="K122" s="17"/>
+      <c r="L122" s="17"/>
+      <c r="M122" s="17"/>
+      <c r="N122" s="17"/>
+      <c r="O122" s="17"/>
+      <c r="P122" s="17"/>
+      <c r="Q122" s="17"/>
+      <c r="R122" s="17"/>
+      <c r="S122" s="17"/>
+      <c r="T122" s="17"/>
+      <c r="U122" s="17"/>
     </row>
     <row r="123" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="60" t="s">
@@ -5138,7 +5144,7 @@
       </c>
       <c r="B123" s="60"/>
       <c r="C123" s="60"/>
-      <c r="D123" s="18"/>
+      <c r="D123" s="17"/>
       <c r="E123" s="55" t="s">
         <v>174</v>
       </c>
@@ -5147,507 +5153,507 @@
       <c r="H123" s="55"/>
       <c r="I123" s="55"/>
       <c r="J123" s="55"/>
-      <c r="K123" s="18"/>
-      <c r="L123" s="48" t="s">
+      <c r="K123" s="17"/>
+      <c r="L123" s="47" t="s">
         <v>182</v>
       </c>
-      <c r="M123" s="48"/>
-      <c r="N123" s="48"/>
-      <c r="O123" s="18"/>
-      <c r="P123" s="47" t="s">
+      <c r="M123" s="47"/>
+      <c r="N123" s="47"/>
+      <c r="O123" s="17"/>
+      <c r="P123" s="46" t="s">
         <v>188</v>
       </c>
-      <c r="Q123" s="47"/>
-      <c r="R123" s="47"/>
-      <c r="S123" s="47"/>
-      <c r="T123" s="47"/>
-      <c r="U123" s="18"/>
+      <c r="Q123" s="46"/>
+      <c r="R123" s="46"/>
+      <c r="S123" s="46"/>
+      <c r="T123" s="46"/>
+      <c r="U123" s="17"/>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="60"/>
       <c r="B124" s="60"/>
       <c r="C124" s="60"/>
-      <c r="D124" s="18"/>
-      <c r="E124" s="48" t="s">
+      <c r="D124" s="17"/>
+      <c r="E124" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="F124" s="48"/>
-      <c r="G124" s="48" t="s">
+      <c r="F124" s="47"/>
+      <c r="G124" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="H124" s="48"/>
-      <c r="I124" s="48"/>
-      <c r="J124" s="48"/>
-      <c r="K124" s="18"/>
-      <c r="L124" s="48" t="s">
+      <c r="H124" s="47"/>
+      <c r="I124" s="47"/>
+      <c r="J124" s="47"/>
+      <c r="K124" s="17"/>
+      <c r="L124" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="M124" s="48"/>
-      <c r="N124" s="22" t="s">
+      <c r="M124" s="47"/>
+      <c r="N124" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="O124" s="18"/>
-      <c r="P124" s="48" t="s">
+      <c r="O124" s="17"/>
+      <c r="P124" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="Q124" s="48"/>
-      <c r="R124" s="48"/>
-      <c r="S124" s="48" t="s">
+      <c r="Q124" s="47"/>
+      <c r="R124" s="47"/>
+      <c r="S124" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="T124" s="48"/>
-      <c r="U124" s="18"/>
+      <c r="T124" s="47"/>
+      <c r="U124" s="17"/>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="56" t="s">
         <v>173</v>
       </c>
       <c r="B125" s="56"/>
-      <c r="C125" s="21" t="s">
+      <c r="C125" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="D125" s="18"/>
-      <c r="E125" s="48"/>
-      <c r="F125" s="48"/>
-      <c r="G125" s="22" t="s">
+      <c r="D125" s="17"/>
+      <c r="E125" s="47"/>
+      <c r="F125" s="47"/>
+      <c r="G125" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="H125" s="42" t="s">
+      <c r="H125" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="I125" s="22" t="s">
+      <c r="I125" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="J125" s="22" t="s">
+      <c r="J125" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="K125" s="18"/>
+      <c r="K125" s="17"/>
       <c r="L125" s="53" t="s">
         <v>183</v>
       </c>
       <c r="M125" s="53"/>
-      <c r="N125" s="1"/>
-      <c r="O125" s="18"/>
+      <c r="N125" s="3"/>
+      <c r="O125" s="17"/>
       <c r="P125" s="51" t="s">
         <v>189</v>
       </c>
       <c r="Q125" s="51"/>
       <c r="R125" s="51"/>
-      <c r="S125" s="49"/>
+      <c r="S125" s="48"/>
       <c r="T125" s="49"/>
-      <c r="U125" s="18"/>
+      <c r="U125" s="17"/>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="61" t="s">
         <v>171</v>
       </c>
       <c r="B126" s="61"/>
-      <c r="C126" s="4"/>
-      <c r="D126" s="18"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="17"/>
       <c r="E126" s="59" t="s">
         <v>175</v>
       </c>
       <c r="F126" s="59"/>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
-      <c r="K126" s="18"/>
+      <c r="G126" s="3"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="3"/>
+      <c r="J126" s="3"/>
+      <c r="K126" s="17"/>
       <c r="L126" s="54" t="s">
         <v>184</v>
       </c>
       <c r="M126" s="54"/>
-      <c r="N126" s="1"/>
-      <c r="O126" s="18"/>
+      <c r="N126" s="3"/>
+      <c r="O126" s="17"/>
       <c r="P126" s="51" t="s">
         <v>190</v>
       </c>
       <c r="Q126" s="51"/>
       <c r="R126" s="51"/>
-      <c r="S126" s="49"/>
+      <c r="S126" s="48"/>
       <c r="T126" s="49"/>
-      <c r="U126" s="18"/>
+      <c r="U126" s="17"/>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="57" t="s">
         <v>78</v>
       </c>
       <c r="B127" s="57"/>
-      <c r="C127" s="4"/>
-      <c r="D127" s="18"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="17"/>
       <c r="E127" s="59" t="s">
         <v>176</v>
       </c>
       <c r="F127" s="59"/>
-      <c r="G127" s="1"/>
-      <c r="H127" s="1"/>
-      <c r="I127" s="1"/>
-      <c r="J127" s="1"/>
-      <c r="K127" s="18"/>
+      <c r="G127" s="3"/>
+      <c r="H127" s="3"/>
+      <c r="I127" s="3"/>
+      <c r="J127" s="3"/>
+      <c r="K127" s="17"/>
       <c r="L127" s="54" t="s">
         <v>185</v>
       </c>
       <c r="M127" s="54"/>
-      <c r="N127" s="1"/>
-      <c r="O127" s="18"/>
+      <c r="N127" s="3"/>
+      <c r="O127" s="17"/>
       <c r="P127" s="52" t="s">
         <v>191</v>
       </c>
       <c r="Q127" s="52"/>
       <c r="R127" s="52"/>
-      <c r="S127" s="49"/>
+      <c r="S127" s="48"/>
       <c r="T127" s="49"/>
-      <c r="U127" s="18"/>
+      <c r="U127" s="17"/>
     </row>
     <row r="128" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="57" t="s">
         <v>79</v>
       </c>
       <c r="B128" s="57"/>
-      <c r="C128" s="4"/>
-      <c r="D128" s="18"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="17"/>
       <c r="E128" s="59" t="s">
         <v>177</v>
       </c>
       <c r="F128" s="59"/>
-      <c r="G128" s="1"/>
-      <c r="H128" s="1"/>
-      <c r="I128" s="1"/>
-      <c r="J128" s="1"/>
-      <c r="K128" s="18"/>
+      <c r="G128" s="3"/>
+      <c r="H128" s="3"/>
+      <c r="I128" s="3"/>
+      <c r="J128" s="3"/>
+      <c r="K128" s="17"/>
       <c r="L128" s="54" t="s">
         <v>186</v>
       </c>
       <c r="M128" s="54"/>
-      <c r="N128" s="1"/>
-      <c r="O128" s="18"/>
+      <c r="N128" s="3"/>
+      <c r="O128" s="17"/>
       <c r="P128" s="50" t="s">
         <v>57</v>
       </c>
       <c r="Q128" s="50"/>
       <c r="R128" s="50"/>
-      <c r="S128" s="49"/>
+      <c r="S128" s="48"/>
       <c r="T128" s="49"/>
-      <c r="U128" s="18"/>
+      <c r="U128" s="17"/>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="57" t="s">
         <v>115</v>
       </c>
       <c r="B129" s="57"/>
-      <c r="C129" s="4"/>
-      <c r="D129" s="18"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="17"/>
       <c r="E129" s="59" t="s">
         <v>178</v>
       </c>
       <c r="F129" s="59"/>
-      <c r="G129" s="1"/>
-      <c r="H129" s="1"/>
-      <c r="I129" s="1"/>
-      <c r="J129" s="1"/>
-      <c r="K129" s="18"/>
+      <c r="G129" s="3"/>
+      <c r="H129" s="3"/>
+      <c r="I129" s="3"/>
+      <c r="J129" s="3"/>
+      <c r="K129" s="17"/>
       <c r="L129" s="54" t="s">
         <v>187</v>
       </c>
       <c r="M129" s="54"/>
-      <c r="N129" s="1"/>
-      <c r="O129" s="18"/>
-      <c r="P129" s="45"/>
-      <c r="Q129" s="45"/>
-      <c r="R129" s="18"/>
-      <c r="S129" s="18"/>
-      <c r="T129" s="18"/>
-      <c r="U129" s="18"/>
+      <c r="N129" s="3"/>
+      <c r="O129" s="17"/>
+      <c r="P129" s="43"/>
+      <c r="Q129" s="43"/>
+      <c r="R129" s="17"/>
+      <c r="S129" s="17"/>
+      <c r="T129" s="17"/>
+      <c r="U129" s="17"/>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="57" t="s">
         <v>172</v>
       </c>
       <c r="B130" s="57"/>
-      <c r="C130" s="4"/>
-      <c r="D130" s="18"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="17"/>
       <c r="E130" s="59" t="s">
         <v>179</v>
       </c>
       <c r="F130" s="59"/>
-      <c r="G130" s="1"/>
-      <c r="H130" s="1"/>
-      <c r="I130" s="1"/>
-      <c r="J130" s="1"/>
-      <c r="K130" s="18"/>
+      <c r="G130" s="3"/>
+      <c r="H130" s="3"/>
+      <c r="I130" s="3"/>
+      <c r="J130" s="3"/>
+      <c r="K130" s="17"/>
       <c r="L130" s="50" t="s">
         <v>57</v>
       </c>
       <c r="M130" s="50"/>
-      <c r="N130" s="1"/>
-      <c r="O130" s="18"/>
-      <c r="P130" s="18"/>
-      <c r="Q130" s="18"/>
-      <c r="R130" s="18"/>
-      <c r="S130" s="18"/>
-      <c r="T130" s="18"/>
-      <c r="U130" s="18"/>
+      <c r="N130" s="3"/>
+      <c r="O130" s="17"/>
+      <c r="P130" s="17"/>
+      <c r="Q130" s="17"/>
+      <c r="R130" s="17"/>
+      <c r="S130" s="17"/>
+      <c r="T130" s="17"/>
+      <c r="U130" s="17"/>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="50" t="s">
         <v>57</v>
       </c>
       <c r="B131" s="50"/>
-      <c r="C131" s="41"/>
-      <c r="D131" s="18"/>
+      <c r="C131" s="40"/>
+      <c r="D131" s="17"/>
       <c r="E131" s="59" t="s">
         <v>180</v>
       </c>
       <c r="F131" s="59"/>
-      <c r="G131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
-      <c r="K131" s="18"/>
-      <c r="L131" s="18"/>
-      <c r="M131" s="18"/>
-      <c r="N131" s="18"/>
-      <c r="O131" s="18"/>
-      <c r="P131" s="18"/>
-      <c r="Q131" s="18"/>
-      <c r="R131" s="18"/>
-      <c r="S131" s="18"/>
-      <c r="T131" s="18"/>
-      <c r="U131" s="18"/>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+      <c r="I131" s="3"/>
+      <c r="J131" s="3"/>
+      <c r="K131" s="17"/>
+      <c r="L131" s="17"/>
+      <c r="M131" s="17"/>
+      <c r="N131" s="17"/>
+      <c r="O131" s="17"/>
+      <c r="P131" s="17"/>
+      <c r="Q131" s="17"/>
+      <c r="R131" s="17"/>
+      <c r="S131" s="17"/>
+      <c r="T131" s="17"/>
+      <c r="U131" s="17"/>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A132" s="18"/>
-      <c r="B132" s="18"/>
-      <c r="C132" s="18"/>
-      <c r="D132" s="18"/>
+      <c r="A132" s="17"/>
+      <c r="B132" s="17"/>
+      <c r="C132" s="17"/>
+      <c r="D132" s="17"/>
       <c r="E132" s="58" t="s">
         <v>181</v>
       </c>
       <c r="F132" s="58"/>
-      <c r="G132" s="1"/>
-      <c r="H132" s="1"/>
-      <c r="I132" s="1"/>
-      <c r="J132" s="1"/>
-      <c r="K132" s="18"/>
-      <c r="L132" s="18"/>
-      <c r="M132" s="18"/>
-      <c r="N132" s="18"/>
-      <c r="O132" s="18"/>
-      <c r="P132" s="18"/>
-      <c r="Q132" s="18"/>
-      <c r="R132" s="18"/>
-      <c r="S132" s="18"/>
-      <c r="T132" s="18"/>
-      <c r="U132" s="18"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="3"/>
+      <c r="K132" s="17"/>
+      <c r="L132" s="17"/>
+      <c r="M132" s="17"/>
+      <c r="N132" s="17"/>
+      <c r="O132" s="17"/>
+      <c r="P132" s="17"/>
+      <c r="Q132" s="17"/>
+      <c r="R132" s="17"/>
+      <c r="S132" s="17"/>
+      <c r="T132" s="17"/>
+      <c r="U132" s="17"/>
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A133" s="18"/>
-      <c r="B133" s="18"/>
-      <c r="C133" s="18"/>
-      <c r="D133" s="18"/>
+      <c r="A133" s="17"/>
+      <c r="B133" s="17"/>
+      <c r="C133" s="17"/>
+      <c r="D133" s="17"/>
       <c r="E133" s="50" t="s">
         <v>10</v>
       </c>
       <c r="F133" s="50"/>
-      <c r="G133" s="1"/>
-      <c r="H133" s="1"/>
-      <c r="I133" s="1"/>
-      <c r="J133" s="1"/>
-      <c r="K133" s="18"/>
-      <c r="L133" s="18"/>
-      <c r="M133" s="18"/>
-      <c r="N133" s="18"/>
-      <c r="O133" s="18"/>
-      <c r="P133" s="18"/>
-      <c r="Q133" s="18"/>
-      <c r="R133" s="18"/>
-      <c r="S133" s="18"/>
-      <c r="T133" s="18"/>
-      <c r="U133" s="18"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+      <c r="I133" s="3"/>
+      <c r="J133" s="3"/>
+      <c r="K133" s="17"/>
+      <c r="L133" s="17"/>
+      <c r="M133" s="17"/>
+      <c r="N133" s="17"/>
+      <c r="O133" s="17"/>
+      <c r="P133" s="17"/>
+      <c r="Q133" s="17"/>
+      <c r="R133" s="17"/>
+      <c r="S133" s="17"/>
+      <c r="T133" s="17"/>
+      <c r="U133" s="17"/>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A134" s="18"/>
-      <c r="B134" s="18"/>
-      <c r="C134" s="18"/>
-      <c r="D134" s="18"/>
-      <c r="E134" s="18"/>
-      <c r="F134" s="18"/>
-      <c r="G134" s="18"/>
-      <c r="H134" s="18"/>
-      <c r="I134" s="18"/>
-      <c r="J134" s="18"/>
-      <c r="K134" s="18"/>
-      <c r="L134" s="18"/>
-      <c r="M134" s="18"/>
-      <c r="N134" s="18"/>
-      <c r="O134" s="18"/>
-      <c r="P134" s="18"/>
-      <c r="Q134" s="18"/>
-      <c r="R134" s="18"/>
-      <c r="S134" s="18"/>
-      <c r="T134" s="18"/>
-      <c r="U134" s="18"/>
+      <c r="A134" s="17"/>
+      <c r="B134" s="17"/>
+      <c r="C134" s="17"/>
+      <c r="D134" s="17"/>
+      <c r="E134" s="17"/>
+      <c r="F134" s="17"/>
+      <c r="G134" s="17"/>
+      <c r="H134" s="17"/>
+      <c r="I134" s="17"/>
+      <c r="J134" s="17"/>
+      <c r="K134" s="17"/>
+      <c r="L134" s="17"/>
+      <c r="M134" s="17"/>
+      <c r="N134" s="17"/>
+      <c r="O134" s="17"/>
+      <c r="P134" s="17"/>
+      <c r="Q134" s="17"/>
+      <c r="R134" s="17"/>
+      <c r="S134" s="17"/>
+      <c r="T134" s="17"/>
+      <c r="U134" s="17"/>
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A135" s="18"/>
-      <c r="B135" s="18"/>
-      <c r="C135" s="18"/>
-      <c r="D135" s="18"/>
-      <c r="E135" s="18"/>
-      <c r="F135" s="18"/>
-      <c r="G135" s="18"/>
-      <c r="H135" s="18"/>
-      <c r="I135" s="18"/>
-      <c r="J135" s="18"/>
-      <c r="K135" s="18"/>
-      <c r="L135" s="18"/>
-      <c r="M135" s="18"/>
-      <c r="N135" s="18"/>
-      <c r="O135" s="18"/>
-      <c r="P135" s="18"/>
-      <c r="Q135" s="18"/>
-      <c r="R135" s="18"/>
-      <c r="S135" s="18"/>
-      <c r="T135" s="18"/>
-      <c r="U135" s="18"/>
+      <c r="A135" s="17"/>
+      <c r="B135" s="17"/>
+      <c r="C135" s="17"/>
+      <c r="D135" s="17"/>
+      <c r="E135" s="17"/>
+      <c r="F135" s="17"/>
+      <c r="G135" s="17"/>
+      <c r="H135" s="17"/>
+      <c r="I135" s="17"/>
+      <c r="J135" s="17"/>
+      <c r="K135" s="17"/>
+      <c r="L135" s="17"/>
+      <c r="M135" s="17"/>
+      <c r="N135" s="17"/>
+      <c r="O135" s="17"/>
+      <c r="P135" s="17"/>
+      <c r="Q135" s="17"/>
+      <c r="R135" s="17"/>
+      <c r="S135" s="17"/>
+      <c r="T135" s="17"/>
+      <c r="U135" s="17"/>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A136" s="18"/>
-      <c r="B136" s="18"/>
-      <c r="C136" s="18"/>
-      <c r="D136" s="18"/>
-      <c r="E136" s="18"/>
-      <c r="F136" s="18"/>
-      <c r="G136" s="18"/>
-      <c r="H136" s="18"/>
-      <c r="I136" s="18"/>
-      <c r="J136" s="18"/>
-      <c r="K136" s="18"/>
-      <c r="L136" s="18"/>
-      <c r="M136" s="18"/>
-      <c r="N136" s="18"/>
-      <c r="O136" s="18"/>
-      <c r="P136" s="18"/>
-      <c r="Q136" s="18"/>
-      <c r="R136" s="18"/>
-      <c r="S136" s="18"/>
-      <c r="T136" s="18"/>
-      <c r="U136" s="18"/>
+      <c r="A136" s="17"/>
+      <c r="B136" s="17"/>
+      <c r="C136" s="17"/>
+      <c r="D136" s="17"/>
+      <c r="E136" s="17"/>
+      <c r="F136" s="17"/>
+      <c r="G136" s="17"/>
+      <c r="H136" s="17"/>
+      <c r="I136" s="17"/>
+      <c r="J136" s="17"/>
+      <c r="K136" s="17"/>
+      <c r="L136" s="17"/>
+      <c r="M136" s="17"/>
+      <c r="N136" s="17"/>
+      <c r="O136" s="17"/>
+      <c r="P136" s="17"/>
+      <c r="Q136" s="17"/>
+      <c r="R136" s="17"/>
+      <c r="S136" s="17"/>
+      <c r="T136" s="17"/>
+      <c r="U136" s="17"/>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A137" s="18"/>
-      <c r="B137" s="18"/>
-      <c r="C137" s="18"/>
-      <c r="D137" s="18"/>
-      <c r="E137" s="18"/>
-      <c r="F137" s="18"/>
-      <c r="G137" s="18"/>
-      <c r="H137" s="18"/>
-      <c r="I137" s="18"/>
-      <c r="J137" s="18"/>
-      <c r="K137" s="18"/>
-      <c r="L137" s="18"/>
-      <c r="M137" s="18"/>
-      <c r="N137" s="18"/>
-      <c r="O137" s="18"/>
-      <c r="P137" s="18"/>
-      <c r="Q137" s="18"/>
-      <c r="R137" s="18"/>
-      <c r="S137" s="18"/>
-      <c r="T137" s="18"/>
-      <c r="U137" s="18"/>
+      <c r="A137" s="17"/>
+      <c r="B137" s="17"/>
+      <c r="C137" s="17"/>
+      <c r="D137" s="17"/>
+      <c r="E137" s="17"/>
+      <c r="F137" s="17"/>
+      <c r="G137" s="17"/>
+      <c r="H137" s="17"/>
+      <c r="I137" s="17"/>
+      <c r="J137" s="17"/>
+      <c r="K137" s="17"/>
+      <c r="L137" s="17"/>
+      <c r="M137" s="17"/>
+      <c r="N137" s="17"/>
+      <c r="O137" s="17"/>
+      <c r="P137" s="17"/>
+      <c r="Q137" s="17"/>
+      <c r="R137" s="17"/>
+      <c r="S137" s="17"/>
+      <c r="T137" s="17"/>
+      <c r="U137" s="17"/>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A138" s="18"/>
-      <c r="B138" s="18"/>
-      <c r="C138" s="18"/>
-      <c r="D138" s="18"/>
-      <c r="E138" s="18"/>
-      <c r="F138" s="18"/>
-      <c r="G138" s="18"/>
-      <c r="H138" s="18"/>
-      <c r="I138" s="18"/>
-      <c r="J138" s="18"/>
-      <c r="K138" s="18"/>
-      <c r="L138" s="18"/>
-      <c r="M138" s="18"/>
-      <c r="N138" s="18"/>
-      <c r="O138" s="18"/>
-      <c r="P138" s="18"/>
-      <c r="Q138" s="18"/>
-      <c r="R138" s="18"/>
-      <c r="S138" s="18"/>
-      <c r="T138" s="18"/>
-      <c r="U138" s="18"/>
+      <c r="A138" s="17"/>
+      <c r="B138" s="17"/>
+      <c r="C138" s="17"/>
+      <c r="D138" s="17"/>
+      <c r="E138" s="17"/>
+      <c r="F138" s="17"/>
+      <c r="G138" s="17"/>
+      <c r="H138" s="17"/>
+      <c r="I138" s="17"/>
+      <c r="J138" s="17"/>
+      <c r="K138" s="17"/>
+      <c r="L138" s="17"/>
+      <c r="M138" s="17"/>
+      <c r="N138" s="17"/>
+      <c r="O138" s="17"/>
+      <c r="P138" s="17"/>
+      <c r="Q138" s="17"/>
+      <c r="R138" s="17"/>
+      <c r="S138" s="17"/>
+      <c r="T138" s="17"/>
+      <c r="U138" s="17"/>
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A139" s="18"/>
-      <c r="B139" s="18"/>
-      <c r="C139" s="18"/>
-      <c r="D139" s="18"/>
-      <c r="E139" s="18"/>
-      <c r="F139" s="18"/>
-      <c r="G139" s="18"/>
-      <c r="H139" s="18"/>
-      <c r="I139" s="18"/>
-      <c r="J139" s="18"/>
-      <c r="K139" s="18"/>
-      <c r="L139" s="18"/>
-      <c r="M139" s="18"/>
-      <c r="N139" s="18"/>
-      <c r="O139" s="18"/>
-      <c r="P139" s="18"/>
-      <c r="Q139" s="18"/>
-      <c r="R139" s="18"/>
-      <c r="S139" s="18"/>
-      <c r="T139" s="18"/>
-      <c r="U139" s="18"/>
+      <c r="A139" s="17"/>
+      <c r="B139" s="17"/>
+      <c r="C139" s="17"/>
+      <c r="D139" s="17"/>
+      <c r="E139" s="17"/>
+      <c r="F139" s="17"/>
+      <c r="G139" s="17"/>
+      <c r="H139" s="17"/>
+      <c r="I139" s="17"/>
+      <c r="J139" s="17"/>
+      <c r="K139" s="17"/>
+      <c r="L139" s="17"/>
+      <c r="M139" s="17"/>
+      <c r="N139" s="17"/>
+      <c r="O139" s="17"/>
+      <c r="P139" s="17"/>
+      <c r="Q139" s="17"/>
+      <c r="R139" s="17"/>
+      <c r="S139" s="17"/>
+      <c r="T139" s="17"/>
+      <c r="U139" s="17"/>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A140" s="18"/>
-      <c r="B140" s="18"/>
-      <c r="C140" s="18"/>
-      <c r="D140" s="18"/>
-      <c r="E140" s="18"/>
-      <c r="F140" s="18"/>
-      <c r="G140" s="18"/>
-      <c r="H140" s="18"/>
-      <c r="I140" s="18"/>
-      <c r="J140" s="18"/>
-      <c r="K140" s="18"/>
-      <c r="L140" s="18"/>
-      <c r="M140" s="18"/>
-      <c r="N140" s="18"/>
-      <c r="O140" s="18"/>
-      <c r="P140" s="18"/>
-      <c r="Q140" s="18"/>
-      <c r="R140" s="18"/>
-      <c r="S140" s="18"/>
-      <c r="T140" s="18"/>
-      <c r="U140" s="18"/>
+      <c r="A140" s="17"/>
+      <c r="B140" s="17"/>
+      <c r="C140" s="17"/>
+      <c r="D140" s="17"/>
+      <c r="E140" s="17"/>
+      <c r="F140" s="17"/>
+      <c r="G140" s="17"/>
+      <c r="H140" s="17"/>
+      <c r="I140" s="17"/>
+      <c r="J140" s="17"/>
+      <c r="K140" s="17"/>
+      <c r="L140" s="17"/>
+      <c r="M140" s="17"/>
+      <c r="N140" s="17"/>
+      <c r="O140" s="17"/>
+      <c r="P140" s="17"/>
+      <c r="Q140" s="17"/>
+      <c r="R140" s="17"/>
+      <c r="S140" s="17"/>
+      <c r="T140" s="17"/>
+      <c r="U140" s="17"/>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A141" s="18"/>
-      <c r="B141" s="18"/>
-      <c r="C141" s="18"/>
-      <c r="D141" s="18"/>
-      <c r="E141" s="18"/>
-      <c r="F141" s="18"/>
-      <c r="G141" s="18"/>
-      <c r="H141" s="18"/>
-      <c r="I141" s="18"/>
-      <c r="J141" s="18"/>
-      <c r="K141" s="18"/>
-      <c r="L141" s="18"/>
-      <c r="M141" s="18"/>
-      <c r="N141" s="18"/>
-      <c r="O141" s="18"/>
-      <c r="P141" s="18"/>
-      <c r="Q141" s="18"/>
-      <c r="R141" s="18"/>
-      <c r="S141" s="18"/>
-      <c r="T141" s="18"/>
-      <c r="U141" s="18"/>
+      <c r="A141" s="17"/>
+      <c r="B141" s="17"/>
+      <c r="C141" s="17"/>
+      <c r="D141" s="17"/>
+      <c r="E141" s="17"/>
+      <c r="F141" s="17"/>
+      <c r="G141" s="17"/>
+      <c r="H141" s="17"/>
+      <c r="I141" s="17"/>
+      <c r="J141" s="17"/>
+      <c r="K141" s="17"/>
+      <c r="L141" s="17"/>
+      <c r="M141" s="17"/>
+      <c r="N141" s="17"/>
+      <c r="O141" s="17"/>
+      <c r="P141" s="17"/>
+      <c r="Q141" s="17"/>
+      <c r="R141" s="17"/>
+      <c r="S141" s="17"/>
+      <c r="T141" s="17"/>
+      <c r="U141" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="255">
@@ -5907,8 +5913,8 @@
     <mergeCell ref="L128:M128"/>
     <mergeCell ref="L129:M129"/>
   </mergeCells>
-  <pageMargins left="7.874015748031496E-2" right="7.874015748031496E-2" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="78" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.11811023622047245" right="7.874015748031496E-2" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="78" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="67" max="16383" man="1"/>
   </rowBreaks>

--- a/uploads/Plantilla.xlsx
+++ b/uploads/Plantilla.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jhon\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MARCO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DF0940-F840-4E25-8409-38A59ED67CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BF5D45-E4DE-41C2-A71C-CEA3843CE817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="195">
   <si>
     <t xml:space="preserve">OPERACIONAL DE INMUNIZACIONES (ESNI) </t>
   </si>
@@ -612,6 +612,15 @@
   </si>
   <si>
     <t>Trabajador de Salud</t>
+  </si>
+  <si>
+    <t>Anticuerpo Monoclonal</t>
+  </si>
+  <si>
+    <t>0 a 12 Meses</t>
+  </si>
+  <si>
+    <t>U.-VSR-VIRUS SINCITIAL RESPIRATORIO</t>
   </si>
 </sst>
 </file>
@@ -622,7 +631,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -724,6 +733,12 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -811,7 +826,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -959,13 +974,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1088,6 +1112,10 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1180,8 +1208,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="1" fontId="14" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1392,6 +1420,48 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1696,24 +1766,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="126"/>
+      <c r="P1" s="126"/>
       <c r="Q1" s="17"/>
       <c r="R1" s="17"/>
       <c r="S1" s="17"/>
@@ -1721,25 +1791,25 @@
       <c r="U1" s="17"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="125" t="s">
+      <c r="A2" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="125"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="129"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="131"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="146"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="148"/>
+      <c r="J2" s="148"/>
       <c r="K2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
       <c r="N2" s="17"/>
       <c r="O2" s="17"/>
       <c r="P2" s="17"/>
@@ -1773,26 +1843,26 @@
       <c r="U3" s="17"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
       <c r="K4" s="17"/>
-      <c r="L4" s="60" t="s">
+      <c r="L4" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
       <c r="S4" s="17"/>
@@ -1800,26 +1870,26 @@
       <c r="U4" s="17"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="126" t="s">
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="126"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
       <c r="K5" s="17"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="60"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
       <c r="S5" s="17"/>
@@ -1827,12 +1897,12 @@
       <c r="U5" s="17"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="47"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
       <c r="G6" s="21" t="s">
         <v>7</v>
       </c>
@@ -1846,15 +1916,15 @@
         <v>10</v>
       </c>
       <c r="K6" s="17"/>
-      <c r="L6" s="56" t="s">
+      <c r="L6" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="M6" s="47" t="s">
+      <c r="M6" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
       <c r="Q6" s="17"/>
       <c r="R6" s="17"/>
       <c r="S6" s="17"/>
@@ -1862,22 +1932,22 @@
       <c r="U6" s="17"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="131" t="s">
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="133" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
+      <c r="E7" s="133"/>
+      <c r="F7" s="133"/>
       <c r="G7" s="3"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="11"/>
       <c r="K7" s="17"/>
-      <c r="L7" s="56"/>
+      <c r="L7" s="58"/>
       <c r="M7" s="21" t="s">
         <v>7</v>
       </c>
@@ -1897,14 +1967,14 @@
       <c r="U7" s="17"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="63"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="131" t="s">
+      <c r="A8" s="65"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="131"/>
-      <c r="F8" s="131"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
       <c r="G8" s="3"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -1924,14 +1994,14 @@
       <c r="U8" s="17"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="63"/>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="131" t="s">
+      <c r="A9" s="65"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="133" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="131"/>
-      <c r="F9" s="131"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
       <c r="G9" s="3"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -1951,16 +2021,16 @@
       <c r="U9" s="17"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="63" t="s">
+      <c r="A10" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="63"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="131" t="s">
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
       <c r="G10" s="3"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -1980,14 +2050,14 @@
       <c r="U10" s="17"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="63"/>
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="131" t="s">
+      <c r="A11" s="65"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="133" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="133"/>
       <c r="G11" s="3"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -2007,14 +2077,14 @@
       <c r="U11" s="17"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="63"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="132" t="s">
+      <c r="A12" s="65"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="134" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="132"/>
-      <c r="F12" s="132"/>
+      <c r="E12" s="134"/>
+      <c r="F12" s="134"/>
       <c r="G12" s="3"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -2034,18 +2104,18 @@
       <c r="U12" s="17"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="133" t="s">
+      <c r="A13" s="135" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="133"/>
-      <c r="C13" s="133"/>
+      <c r="B13" s="135"/>
+      <c r="C13" s="135"/>
       <c r="D13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="63" t="s">
+      <c r="E13" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="63"/>
+      <c r="F13" s="65"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -2065,16 +2135,16 @@
       <c r="U13" s="17"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="133"/>
-      <c r="B14" s="133"/>
-      <c r="C14" s="133"/>
+      <c r="A14" s="135"/>
+      <c r="B14" s="135"/>
+      <c r="C14" s="135"/>
       <c r="D14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="63" t="s">
+      <c r="E14" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="63"/>
+      <c r="F14" s="65"/>
       <c r="G14" s="28"/>
       <c r="H14" s="5"/>
       <c r="I14" s="3"/>
@@ -2094,16 +2164,16 @@
       <c r="U14" s="17"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="134" t="s">
+      <c r="A15" s="136" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="134"/>
-      <c r="C15" s="134"/>
-      <c r="D15" s="63" t="s">
+      <c r="B15" s="136"/>
+      <c r="C15" s="136"/>
+      <c r="D15" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -2120,31 +2190,31 @@
       <c r="T15" s="17"/>
       <c r="U15" s="17"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="130" t="s">
+    <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="151" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="130"/>
-      <c r="C16" s="130"/>
+      <c r="B16" s="152"/>
+      <c r="C16" s="153"/>
       <c r="D16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="63" t="s">
+      <c r="E16" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="63"/>
+      <c r="F16" s="65"/>
       <c r="G16" s="9"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="11"/>
       <c r="K16" s="17"/>
-      <c r="L16" s="46" t="s">
+      <c r="L16" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="M16" s="46"/>
-      <c r="N16" s="46"/>
-      <c r="O16" s="46"/>
-      <c r="P16" s="46"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="48"/>
+      <c r="O16" s="48"/>
+      <c r="P16" s="48"/>
       <c r="Q16" s="17"/>
       <c r="R16" s="17"/>
       <c r="S16" s="17"/>
@@ -2152,53 +2222,53 @@
       <c r="U16" s="17"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="130"/>
-      <c r="B17" s="130"/>
-      <c r="C17" s="130"/>
+      <c r="A17" s="154"/>
+      <c r="B17" s="155"/>
+      <c r="C17" s="156"/>
       <c r="D17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="63" t="s">
+      <c r="E17" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="63"/>
+      <c r="F17" s="65"/>
       <c r="G17" s="9"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="11"/>
       <c r="K17" s="17"/>
-      <c r="L17" s="56" t="s">
+      <c r="L17" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="M17" s="46" t="s">
+      <c r="M17" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="N17" s="46"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="46"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="48"/>
+      <c r="P17" s="48"/>
       <c r="Q17" s="17"/>
       <c r="R17" s="17"/>
       <c r="S17" s="17"/>
       <c r="T17" s="17"/>
       <c r="U17" s="17"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="130"/>
-      <c r="B18" s="130"/>
-      <c r="C18" s="130"/>
-      <c r="D18" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="63"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+    <row r="18" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="136" t="s">
+        <v>192</v>
+      </c>
+      <c r="B18" s="136"/>
+      <c r="C18" s="136"/>
+      <c r="D18" s="101" t="s">
+        <v>193</v>
+      </c>
+      <c r="E18" s="157"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
       <c r="J18" s="11"/>
       <c r="K18" s="17"/>
-      <c r="L18" s="56"/>
+      <c r="L18" s="58"/>
       <c r="M18" s="21" t="s">
         <v>7</v>
       </c>
@@ -2218,16 +2288,16 @@
       <c r="U18" s="17"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="134" t="s">
+      <c r="A19" s="136" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="134"/>
-      <c r="C19" s="134"/>
-      <c r="D19" s="135" t="s">
+      <c r="B19" s="136"/>
+      <c r="C19" s="136"/>
+      <c r="D19" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="135"/>
-      <c r="F19" s="135"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
       <c r="G19" s="3"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -2247,16 +2317,16 @@
       <c r="U19" s="17"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="134" t="s">
+      <c r="A20" s="136" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="134"/>
-      <c r="C20" s="134"/>
-      <c r="D20" s="63" t="s">
+      <c r="B20" s="136"/>
+      <c r="C20" s="136"/>
+      <c r="D20" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="7"/>
@@ -2276,16 +2346,16 @@
       <c r="U20" s="17"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="134" t="s">
+      <c r="A21" s="136" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="134"/>
-      <c r="C21" s="134"/>
-      <c r="D21" s="63" t="s">
+      <c r="B21" s="136"/>
+      <c r="C21" s="136"/>
+      <c r="D21" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="63"/>
-      <c r="F21" s="63"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="7"/>
@@ -2305,16 +2375,16 @@
       <c r="U21" s="17"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="134" t="s">
+      <c r="A22" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="134"/>
-      <c r="C22" s="134"/>
-      <c r="D22" s="135" t="s">
+      <c r="B22" s="136"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="135"/>
-      <c r="F22" s="135"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="137"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="7"/>
@@ -2334,18 +2404,18 @@
       <c r="U22" s="17"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="138"/>
+      <c r="C23" s="138"/>
       <c r="D23" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="63" t="s">
+      <c r="E23" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="63"/>
+      <c r="F23" s="65"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -2383,26 +2453,26 @@
       <c r="U24" s="17"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="74" t="s">
+      <c r="A25" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="75"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
-      <c r="J25" s="86"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="88"/>
       <c r="K25" s="17"/>
-      <c r="L25" s="74" t="s">
+      <c r="L25" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="M25" s="75"/>
-      <c r="N25" s="75"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="86"/>
+      <c r="M25" s="77"/>
+      <c r="N25" s="77"/>
+      <c r="O25" s="77"/>
+      <c r="P25" s="88"/>
       <c r="Q25" s="17"/>
       <c r="R25" s="17"/>
       <c r="S25" s="17"/>
@@ -2410,30 +2480,30 @@
       <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" s="47" t="s">
+      <c r="A26" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47" t="s">
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
       <c r="K26" s="17"/>
-      <c r="L26" s="56" t="s">
+      <c r="L26" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="M26" s="103" t="s">
+      <c r="M26" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="N26" s="104"/>
-      <c r="O26" s="104"/>
-      <c r="P26" s="105"/>
+      <c r="N26" s="106"/>
+      <c r="O26" s="106"/>
+      <c r="P26" s="107"/>
       <c r="Q26" s="17"/>
       <c r="R26" s="17"/>
       <c r="S26" s="17"/>
@@ -2441,12 +2511,12 @@
       <c r="U26" s="17"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="47"/>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
       <c r="G27" s="21" t="s">
         <v>7</v>
       </c>
@@ -2460,7 +2530,7 @@
         <v>10</v>
       </c>
       <c r="K27" s="17"/>
-      <c r="L27" s="56"/>
+      <c r="L27" s="58"/>
       <c r="M27" s="21" t="s">
         <v>7</v>
       </c>
@@ -2480,16 +2550,16 @@
       <c r="U27" s="17"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="90" t="s">
+      <c r="A28" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="90"/>
-      <c r="C28" s="119" t="s">
+      <c r="B28" s="92"/>
+      <c r="C28" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="119"/>
+      <c r="D28" s="121"/>
+      <c r="E28" s="121"/>
+      <c r="F28" s="121"/>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
       <c r="I28" s="3"/>
@@ -2509,14 +2579,14 @@
       <c r="U28" s="17"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="90"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="119" t="s">
+      <c r="A29" s="92"/>
+      <c r="B29" s="92"/>
+      <c r="C29" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="119"/>
+      <c r="D29" s="121"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="121"/>
       <c r="G29" s="3"/>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
@@ -2536,14 +2606,14 @@
       <c r="U29" s="17"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" s="90"/>
-      <c r="B30" s="90"/>
-      <c r="C30" s="120" t="s">
+      <c r="A30" s="92"/>
+      <c r="B30" s="92"/>
+      <c r="C30" s="122" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="120"/>
-      <c r="E30" s="120"/>
-      <c r="F30" s="120"/>
+      <c r="D30" s="122"/>
+      <c r="E30" s="122"/>
+      <c r="F30" s="122"/>
       <c r="G30" s="3"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
@@ -2563,14 +2633,14 @@
       <c r="U30" s="17"/>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="121" t="s">
+      <c r="A31" s="123" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="121"/>
-      <c r="C31" s="121"/>
-      <c r="D31" s="121"/>
-      <c r="E31" s="121"/>
-      <c r="F31" s="121"/>
+      <c r="B31" s="123"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="123"/>
+      <c r="E31" s="123"/>
+      <c r="F31" s="123"/>
       <c r="G31" s="3"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
@@ -2594,12 +2664,12 @@
         <v>42</v>
       </c>
       <c r="B32" s="25"/>
-      <c r="C32" s="118" t="s">
+      <c r="C32" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="118"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="118"/>
+      <c r="D32" s="120"/>
+      <c r="E32" s="120"/>
+      <c r="F32" s="120"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="8"/>
@@ -2619,16 +2689,16 @@
       <c r="U32" s="17"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="122" t="s">
+      <c r="A33" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="122"/>
-      <c r="C33" s="123" t="s">
+      <c r="B33" s="124"/>
+      <c r="C33" s="125" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="123"/>
-      <c r="E33" s="123"/>
-      <c r="F33" s="123"/>
+      <c r="D33" s="125"/>
+      <c r="E33" s="125"/>
+      <c r="F33" s="125"/>
       <c r="G33" s="3"/>
       <c r="H33" s="9"/>
       <c r="I33" s="10"/>
@@ -2648,14 +2718,14 @@
       <c r="U33" s="17"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" s="122"/>
-      <c r="B34" s="122"/>
-      <c r="C34" s="123" t="s">
+      <c r="A34" s="124"/>
+      <c r="B34" s="124"/>
+      <c r="C34" s="125" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="123"/>
-      <c r="E34" s="123"/>
-      <c r="F34" s="123"/>
+      <c r="D34" s="125"/>
+      <c r="E34" s="125"/>
+      <c r="F34" s="125"/>
       <c r="G34" s="3"/>
       <c r="H34" s="9"/>
       <c r="I34" s="10"/>
@@ -2673,16 +2743,16 @@
       <c r="U34" s="17"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" s="90" t="s">
+      <c r="A35" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="90"/>
-      <c r="C35" s="137" t="s">
+      <c r="B35" s="92"/>
+      <c r="C35" s="139" t="s">
         <v>48</v>
       </c>
-      <c r="D35" s="137"/>
-      <c r="E35" s="137"/>
-      <c r="F35" s="137"/>
+      <c r="D35" s="139"/>
+      <c r="E35" s="139"/>
+      <c r="F35" s="139"/>
       <c r="G35" s="26"/>
       <c r="H35" s="3"/>
       <c r="I35" s="8"/>
@@ -2700,14 +2770,14 @@
       <c r="U35" s="17"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="90"/>
-      <c r="B36" s="90"/>
-      <c r="C36" s="138" t="s">
+      <c r="A36" s="92"/>
+      <c r="B36" s="92"/>
+      <c r="C36" s="140" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="138"/>
-      <c r="E36" s="138"/>
-      <c r="F36" s="138"/>
+      <c r="D36" s="140"/>
+      <c r="E36" s="140"/>
+      <c r="F36" s="140"/>
       <c r="G36" s="3"/>
       <c r="H36" s="8"/>
       <c r="I36" s="10"/>
@@ -2725,14 +2795,14 @@
       <c r="U36" s="17"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="90"/>
-      <c r="B37" s="90"/>
-      <c r="C37" s="138" t="s">
+      <c r="A37" s="92"/>
+      <c r="B37" s="92"/>
+      <c r="C37" s="140" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="138"/>
-      <c r="E37" s="138"/>
-      <c r="F37" s="138"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="140"/>
       <c r="G37" s="3"/>
       <c r="H37" s="8"/>
       <c r="I37" s="10"/>
@@ -2750,14 +2820,14 @@
       <c r="U37" s="17"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" s="90"/>
-      <c r="B38" s="90"/>
-      <c r="C38" s="138" t="s">
+      <c r="A38" s="92"/>
+      <c r="B38" s="92"/>
+      <c r="C38" s="140" t="s">
         <v>51</v>
       </c>
-      <c r="D38" s="138"/>
-      <c r="E38" s="138"/>
-      <c r="F38" s="138"/>
+      <c r="D38" s="140"/>
+      <c r="E38" s="140"/>
+      <c r="F38" s="140"/>
       <c r="G38" s="3"/>
       <c r="H38" s="8"/>
       <c r="I38" s="10"/>
@@ -2775,15 +2845,15 @@
       <c r="U38" s="17"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="90" t="s">
+      <c r="A39" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="90"/>
-      <c r="C39" s="133" t="s">
+      <c r="B39" s="92"/>
+      <c r="C39" s="135" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="133"/>
-      <c r="E39" s="133"/>
+      <c r="D39" s="135"/>
+      <c r="E39" s="135"/>
       <c r="F39" s="4" t="s">
         <v>19</v>
       </c>
@@ -2804,11 +2874,11 @@
       <c r="U39" s="17"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A40" s="90"/>
-      <c r="B40" s="90"/>
-      <c r="C40" s="133"/>
-      <c r="D40" s="133"/>
-      <c r="E40" s="133"/>
+      <c r="A40" s="92"/>
+      <c r="B40" s="92"/>
+      <c r="C40" s="135"/>
+      <c r="D40" s="135"/>
+      <c r="E40" s="135"/>
       <c r="F40" s="4" t="s">
         <v>21</v>
       </c>
@@ -2829,14 +2899,14 @@
       <c r="U40" s="17"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="90"/>
-      <c r="B41" s="90"/>
-      <c r="C41" s="134" t="s">
+      <c r="A41" s="92"/>
+      <c r="B41" s="92"/>
+      <c r="C41" s="136" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="134"/>
-      <c r="E41" s="134"/>
-      <c r="F41" s="134"/>
+      <c r="D41" s="136"/>
+      <c r="E41" s="136"/>
+      <c r="F41" s="136"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -2854,13 +2924,13 @@
       <c r="U41" s="17"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="90"/>
-      <c r="B42" s="90"/>
-      <c r="C42" s="130" t="s">
+      <c r="A42" s="92"/>
+      <c r="B42" s="92"/>
+      <c r="C42" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="D42" s="130"/>
-      <c r="E42" s="130"/>
+      <c r="D42" s="132"/>
+      <c r="E42" s="132"/>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
@@ -2881,11 +2951,11 @@
       <c r="U42" s="17"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="90"/>
-      <c r="B43" s="90"/>
-      <c r="C43" s="130"/>
-      <c r="D43" s="130"/>
-      <c r="E43" s="130"/>
+      <c r="A43" s="92"/>
+      <c r="B43" s="92"/>
+      <c r="C43" s="132"/>
+      <c r="D43" s="132"/>
+      <c r="E43" s="132"/>
       <c r="F43" s="6" t="s">
         <v>28</v>
       </c>
@@ -2906,11 +2976,11 @@
       <c r="U43" s="17"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="90"/>
-      <c r="B44" s="90"/>
-      <c r="C44" s="130"/>
-      <c r="D44" s="130"/>
-      <c r="E44" s="130"/>
+      <c r="A44" s="92"/>
+      <c r="B44" s="92"/>
+      <c r="C44" s="132"/>
+      <c r="D44" s="132"/>
+      <c r="E44" s="132"/>
       <c r="F44" s="6" t="s">
         <v>29</v>
       </c>
@@ -2931,14 +3001,14 @@
       <c r="U44" s="17"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="90"/>
-      <c r="B45" s="90"/>
-      <c r="C45" s="140" t="s">
+      <c r="A45" s="92"/>
+      <c r="B45" s="92"/>
+      <c r="C45" s="142" t="s">
         <v>54</v>
       </c>
-      <c r="D45" s="140"/>
-      <c r="E45" s="140"/>
-      <c r="F45" s="140"/>
+      <c r="D45" s="142"/>
+      <c r="E45" s="142"/>
+      <c r="F45" s="142"/>
       <c r="G45" s="3"/>
       <c r="H45" s="27"/>
       <c r="I45" s="12"/>
@@ -2974,23 +3044,23 @@
       <c r="U46" s="17"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="46" t="s">
+      <c r="A47" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="46"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="47" t="s">
+      <c r="B47" s="48"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="48"/>
+      <c r="J47" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="K47" s="47"/>
-      <c r="L47" s="47"/>
-      <c r="M47" s="47"/>
+      <c r="K47" s="49"/>
+      <c r="L47" s="49"/>
+      <c r="M47" s="49"/>
       <c r="N47" s="17"/>
       <c r="O47" s="17"/>
       <c r="P47" s="17"/>
@@ -3001,25 +3071,25 @@
       <c r="U47" s="17"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="47" t="s">
+      <c r="A48" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="47"/>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47" t="s">
+      <c r="B48" s="49"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="G48" s="47"/>
-      <c r="H48" s="47"/>
-      <c r="I48" s="47"/>
-      <c r="J48" s="47" t="s">
+      <c r="G48" s="49"/>
+      <c r="H48" s="49"/>
+      <c r="I48" s="49"/>
+      <c r="J48" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="K48" s="47"/>
-      <c r="L48" s="47"/>
-      <c r="M48" s="47"/>
+      <c r="K48" s="49"/>
+      <c r="L48" s="49"/>
+      <c r="M48" s="49"/>
       <c r="N48" s="17"/>
       <c r="O48" s="17"/>
       <c r="P48" s="17"/>
@@ -3030,11 +3100,11 @@
       <c r="U48" s="17"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="47"/>
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
+      <c r="A49" s="49"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
       <c r="F49" s="21" t="s">
         <v>7</v>
       </c>
@@ -3069,13 +3139,13 @@
       <c r="U49" s="17"/>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A50" s="137" t="s">
+      <c r="A50" s="139" t="s">
         <v>58</v>
       </c>
-      <c r="B50" s="137"/>
-      <c r="C50" s="137"/>
-      <c r="D50" s="137"/>
-      <c r="E50" s="137"/>
+      <c r="B50" s="139"/>
+      <c r="C50" s="139"/>
+      <c r="D50" s="139"/>
+      <c r="E50" s="139"/>
       <c r="F50" s="3"/>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
@@ -3094,13 +3164,13 @@
       <c r="U50" s="17"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="139" t="s">
+      <c r="A51" s="141" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="139"/>
-      <c r="C51" s="139"/>
-      <c r="D51" s="139"/>
-      <c r="E51" s="139"/>
+      <c r="B51" s="141"/>
+      <c r="C51" s="141"/>
+      <c r="D51" s="141"/>
+      <c r="E51" s="141"/>
       <c r="F51" s="3"/>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
@@ -3119,13 +3189,13 @@
       <c r="U51" s="17"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A52" s="137" t="s">
+      <c r="A52" s="139" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="137"/>
-      <c r="C52" s="137"/>
-      <c r="D52" s="137"/>
-      <c r="E52" s="137"/>
+      <c r="B52" s="139"/>
+      <c r="C52" s="139"/>
+      <c r="D52" s="139"/>
+      <c r="E52" s="139"/>
       <c r="F52" s="3"/>
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
@@ -3144,13 +3214,13 @@
       <c r="U52" s="17"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="141" t="s">
+      <c r="A53" s="143" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="141"/>
-      <c r="C53" s="141"/>
-      <c r="D53" s="141"/>
-      <c r="E53" s="141"/>
+      <c r="B53" s="143"/>
+      <c r="C53" s="143"/>
+      <c r="D53" s="143"/>
+      <c r="E53" s="143"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
@@ -3169,13 +3239,13 @@
       <c r="U53" s="17"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A54" s="142" t="s">
+      <c r="A54" s="144" t="s">
         <v>41</v>
       </c>
-      <c r="B54" s="142"/>
-      <c r="C54" s="142"/>
-      <c r="D54" s="142"/>
-      <c r="E54" s="142"/>
+      <c r="B54" s="144"/>
+      <c r="C54" s="144"/>
+      <c r="D54" s="144"/>
+      <c r="E54" s="144"/>
       <c r="F54" s="3"/>
       <c r="G54" s="8"/>
       <c r="H54" s="10"/>
@@ -3194,13 +3264,13 @@
       <c r="U54" s="17"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="138" t="s">
+      <c r="A55" s="140" t="s">
         <v>45</v>
       </c>
-      <c r="B55" s="138"/>
-      <c r="C55" s="138"/>
-      <c r="D55" s="138"/>
-      <c r="E55" s="138"/>
+      <c r="B55" s="140"/>
+      <c r="C55" s="140"/>
+      <c r="D55" s="140"/>
+      <c r="E55" s="140"/>
       <c r="F55" s="3"/>
       <c r="G55" s="8"/>
       <c r="H55" s="10"/>
@@ -3219,14 +3289,14 @@
       <c r="U55" s="17"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A56" s="90" t="s">
+      <c r="A56" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="90"/>
-      <c r="C56" s="133" t="s">
+      <c r="B56" s="92"/>
+      <c r="C56" s="135" t="s">
         <v>18</v>
       </c>
-      <c r="D56" s="133"/>
+      <c r="D56" s="135"/>
       <c r="E56" s="4" t="s">
         <v>19</v>
       </c>
@@ -3248,10 +3318,10 @@
       <c r="U56" s="17"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="90"/>
-      <c r="B57" s="90"/>
-      <c r="C57" s="133"/>
-      <c r="D57" s="133"/>
+      <c r="A57" s="92"/>
+      <c r="B57" s="92"/>
+      <c r="C57" s="135"/>
+      <c r="D57" s="135"/>
       <c r="E57" s="4" t="s">
         <v>21</v>
       </c>
@@ -3273,13 +3343,13 @@
       <c r="U57" s="17"/>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A58" s="90"/>
-      <c r="B58" s="90"/>
-      <c r="C58" s="134" t="s">
+      <c r="A58" s="92"/>
+      <c r="B58" s="92"/>
+      <c r="C58" s="136" t="s">
         <v>23</v>
       </c>
-      <c r="D58" s="134"/>
-      <c r="E58" s="134"/>
+      <c r="D58" s="136"/>
+      <c r="E58" s="136"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
@@ -3298,12 +3368,12 @@
       <c r="U58" s="17"/>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="90"/>
-      <c r="B59" s="90"/>
-      <c r="C59" s="130" t="s">
+      <c r="A59" s="92"/>
+      <c r="B59" s="92"/>
+      <c r="C59" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="D59" s="130"/>
+      <c r="D59" s="132"/>
       <c r="E59" s="6" t="s">
         <v>26</v>
       </c>
@@ -3325,10 +3395,10 @@
       <c r="U59" s="17"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A60" s="90"/>
-      <c r="B60" s="90"/>
-      <c r="C60" s="130"/>
-      <c r="D60" s="130"/>
+      <c r="A60" s="92"/>
+      <c r="B60" s="92"/>
+      <c r="C60" s="132"/>
+      <c r="D60" s="132"/>
       <c r="E60" s="6" t="s">
         <v>28</v>
       </c>
@@ -3350,10 +3420,10 @@
       <c r="U60" s="17"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="90"/>
-      <c r="B61" s="90"/>
-      <c r="C61" s="130"/>
-      <c r="D61" s="130"/>
+      <c r="A61" s="92"/>
+      <c r="B61" s="92"/>
+      <c r="C61" s="132"/>
+      <c r="D61" s="132"/>
       <c r="E61" s="6" t="s">
         <v>29</v>
       </c>
@@ -3375,13 +3445,13 @@
       <c r="U61" s="17"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A62" s="90"/>
-      <c r="B62" s="90"/>
-      <c r="C62" s="143" t="s">
+      <c r="A62" s="92"/>
+      <c r="B62" s="92"/>
+      <c r="C62" s="145" t="s">
         <v>62</v>
       </c>
-      <c r="D62" s="143"/>
-      <c r="E62" s="143"/>
+      <c r="D62" s="145"/>
+      <c r="E62" s="145"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="12"/>
@@ -3400,13 +3470,13 @@
       <c r="U62" s="17"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" s="90"/>
-      <c r="B63" s="90"/>
-      <c r="C63" s="144" t="s">
+      <c r="A63" s="92"/>
+      <c r="B63" s="92"/>
+      <c r="C63" s="146" t="s">
         <v>54</v>
       </c>
-      <c r="D63" s="144"/>
-      <c r="E63" s="144"/>
+      <c r="D63" s="146"/>
+      <c r="E63" s="146"/>
       <c r="F63" s="3"/>
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
@@ -3425,13 +3495,13 @@
       <c r="U63" s="17"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A64" s="90"/>
-      <c r="B64" s="90"/>
-      <c r="C64" s="119" t="s">
+      <c r="A64" s="92"/>
+      <c r="B64" s="92"/>
+      <c r="C64" s="121" t="s">
         <v>63</v>
       </c>
-      <c r="D64" s="119"/>
-      <c r="E64" s="119"/>
+      <c r="D64" s="121"/>
+      <c r="E64" s="121"/>
       <c r="F64" s="3"/>
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
@@ -3450,13 +3520,13 @@
       <c r="U64" s="17"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A65" s="90"/>
-      <c r="B65" s="90"/>
-      <c r="C65" s="119" t="s">
+      <c r="A65" s="92"/>
+      <c r="B65" s="92"/>
+      <c r="C65" s="121" t="s">
         <v>64</v>
       </c>
-      <c r="D65" s="119"/>
-      <c r="E65" s="119"/>
+      <c r="D65" s="121"/>
+      <c r="E65" s="121"/>
       <c r="F65" s="3"/>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
@@ -3475,13 +3545,13 @@
       <c r="U65" s="17"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A66" s="90"/>
-      <c r="B66" s="90"/>
-      <c r="C66" s="119" t="s">
+      <c r="A66" s="92"/>
+      <c r="B66" s="92"/>
+      <c r="C66" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="D66" s="119"/>
-      <c r="E66" s="119"/>
+      <c r="D66" s="121"/>
+      <c r="E66" s="121"/>
       <c r="F66" s="3"/>
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
@@ -3523,73 +3593,73 @@
       <c r="U67" s="17"/>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A68" s="46" t="s">
+      <c r="A68" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="46"/>
-      <c r="C68" s="46"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="46"/>
-      <c r="F68" s="46"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
-      <c r="I68" s="46"/>
-      <c r="J68" s="47" t="s">
+      <c r="B68" s="48"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="48"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="48"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="48"/>
+      <c r="I68" s="48"/>
+      <c r="J68" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="K68" s="47"/>
-      <c r="L68" s="47"/>
-      <c r="M68" s="47"/>
+      <c r="K68" s="49"/>
+      <c r="L68" s="49"/>
+      <c r="M68" s="49"/>
       <c r="N68" s="17"/>
-      <c r="O68" s="46" t="s">
+      <c r="O68" s="48" t="s">
         <v>155</v>
       </c>
-      <c r="P68" s="46"/>
-      <c r="Q68" s="46"/>
-      <c r="R68" s="46"/>
-      <c r="S68" s="46"/>
-      <c r="T68" s="46"/>
+      <c r="P68" s="48"/>
+      <c r="Q68" s="48"/>
+      <c r="R68" s="48"/>
+      <c r="S68" s="48"/>
+      <c r="T68" s="48"/>
       <c r="U68" s="17"/>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A69" s="47" t="s">
+      <c r="A69" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B69" s="47"/>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47" t="s">
+      <c r="B69" s="49"/>
+      <c r="C69" s="49"/>
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="G69" s="47"/>
-      <c r="H69" s="47"/>
-      <c r="I69" s="47"/>
-      <c r="J69" s="47" t="s">
+      <c r="G69" s="49"/>
+      <c r="H69" s="49"/>
+      <c r="I69" s="49"/>
+      <c r="J69" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="K69" s="47"/>
-      <c r="L69" s="47"/>
-      <c r="M69" s="47"/>
+      <c r="K69" s="49"/>
+      <c r="L69" s="49"/>
+      <c r="M69" s="49"/>
       <c r="N69" s="17"/>
-      <c r="O69" s="47" t="s">
+      <c r="O69" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="P69" s="47"/>
-      <c r="Q69" s="47"/>
-      <c r="R69" s="47"/>
-      <c r="S69" s="47"/>
+      <c r="P69" s="49"/>
+      <c r="Q69" s="49"/>
+      <c r="R69" s="49"/>
+      <c r="S69" s="49"/>
       <c r="T69" s="21" t="s">
         <v>125</v>
       </c>
       <c r="U69" s="17"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A70" s="47"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="47"/>
+      <c r="A70" s="49"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="49"/>
+      <c r="D70" s="49"/>
+      <c r="E70" s="49"/>
       <c r="F70" s="21" t="s">
         <v>7</v>
       </c>
@@ -3615,24 +3685,24 @@
         <v>10</v>
       </c>
       <c r="N70" s="17"/>
-      <c r="O70" s="72" t="s">
+      <c r="O70" s="74" t="s">
         <v>156</v>
       </c>
-      <c r="P70" s="72"/>
-      <c r="Q70" s="72"/>
-      <c r="R70" s="72"/>
-      <c r="S70" s="72"/>
+      <c r="P70" s="74"/>
+      <c r="Q70" s="74"/>
+      <c r="R70" s="74"/>
+      <c r="S70" s="74"/>
       <c r="T70" s="3"/>
       <c r="U70" s="17"/>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A71" s="137" t="s">
+      <c r="A71" s="139" t="s">
         <v>58</v>
       </c>
-      <c r="B71" s="137"/>
-      <c r="C71" s="137"/>
-      <c r="D71" s="137"/>
-      <c r="E71" s="137"/>
+      <c r="B71" s="139"/>
+      <c r="C71" s="139"/>
+      <c r="D71" s="139"/>
+      <c r="E71" s="139"/>
       <c r="F71" s="3"/>
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
@@ -3642,24 +3712,24 @@
       <c r="L71" s="8"/>
       <c r="M71" s="11"/>
       <c r="N71" s="17"/>
-      <c r="O71" s="72" t="s">
+      <c r="O71" s="74" t="s">
         <v>162</v>
       </c>
-      <c r="P71" s="72"/>
-      <c r="Q71" s="72"/>
-      <c r="R71" s="72"/>
-      <c r="S71" s="72"/>
+      <c r="P71" s="74"/>
+      <c r="Q71" s="74"/>
+      <c r="R71" s="74"/>
+      <c r="S71" s="74"/>
       <c r="T71" s="3"/>
       <c r="U71" s="17"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A72" s="139" t="s">
+      <c r="A72" s="141" t="s">
         <v>59</v>
       </c>
-      <c r="B72" s="139"/>
-      <c r="C72" s="139"/>
-      <c r="D72" s="139"/>
-      <c r="E72" s="139"/>
+      <c r="B72" s="141"/>
+      <c r="C72" s="141"/>
+      <c r="D72" s="141"/>
+      <c r="E72" s="141"/>
       <c r="F72" s="3"/>
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
@@ -3669,24 +3739,24 @@
       <c r="L72" s="8"/>
       <c r="M72" s="11"/>
       <c r="N72" s="17"/>
-      <c r="O72" s="72" t="s">
+      <c r="O72" s="74" t="s">
         <v>163</v>
       </c>
-      <c r="P72" s="72"/>
-      <c r="Q72" s="72"/>
-      <c r="R72" s="72"/>
-      <c r="S72" s="72"/>
+      <c r="P72" s="74"/>
+      <c r="Q72" s="74"/>
+      <c r="R72" s="74"/>
+      <c r="S72" s="74"/>
       <c r="T72" s="3"/>
       <c r="U72" s="17"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A73" s="137" t="s">
+      <c r="A73" s="139" t="s">
         <v>60</v>
       </c>
-      <c r="B73" s="137"/>
-      <c r="C73" s="137"/>
-      <c r="D73" s="137"/>
-      <c r="E73" s="137"/>
+      <c r="B73" s="139"/>
+      <c r="C73" s="139"/>
+      <c r="D73" s="139"/>
+      <c r="E73" s="139"/>
       <c r="F73" s="3"/>
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
@@ -3696,24 +3766,24 @@
       <c r="L73" s="8"/>
       <c r="M73" s="11"/>
       <c r="N73" s="17"/>
-      <c r="O73" s="72" t="s">
+      <c r="O73" s="74" t="s">
         <v>164</v>
       </c>
-      <c r="P73" s="72"/>
-      <c r="Q73" s="72"/>
-      <c r="R73" s="72"/>
-      <c r="S73" s="72"/>
+      <c r="P73" s="74"/>
+      <c r="Q73" s="74"/>
+      <c r="R73" s="74"/>
+      <c r="S73" s="74"/>
       <c r="T73" s="3"/>
       <c r="U73" s="17"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A74" s="141" t="s">
+      <c r="A74" s="143" t="s">
         <v>61</v>
       </c>
-      <c r="B74" s="141"/>
-      <c r="C74" s="141"/>
-      <c r="D74" s="141"/>
-      <c r="E74" s="141"/>
+      <c r="B74" s="143"/>
+      <c r="C74" s="143"/>
+      <c r="D74" s="143"/>
+      <c r="E74" s="143"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
@@ -3723,24 +3793,24 @@
       <c r="L74" s="3"/>
       <c r="M74" s="11"/>
       <c r="N74" s="17"/>
-      <c r="O74" s="72" t="s">
+      <c r="O74" s="74" t="s">
         <v>165</v>
       </c>
-      <c r="P74" s="72"/>
-      <c r="Q74" s="72"/>
-      <c r="R74" s="72"/>
-      <c r="S74" s="72"/>
+      <c r="P74" s="74"/>
+      <c r="Q74" s="74"/>
+      <c r="R74" s="74"/>
+      <c r="S74" s="74"/>
       <c r="T74" s="3"/>
       <c r="U74" s="17"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" s="138" t="s">
+      <c r="A75" s="140" t="s">
         <v>45</v>
       </c>
-      <c r="B75" s="138"/>
-      <c r="C75" s="138"/>
-      <c r="D75" s="138"/>
-      <c r="E75" s="138"/>
+      <c r="B75" s="140"/>
+      <c r="C75" s="140"/>
+      <c r="D75" s="140"/>
+      <c r="E75" s="140"/>
       <c r="F75" s="3"/>
       <c r="G75" s="8"/>
       <c r="H75" s="10"/>
@@ -3750,25 +3820,25 @@
       <c r="L75" s="10"/>
       <c r="M75" s="11"/>
       <c r="N75" s="17"/>
-      <c r="O75" s="72" t="s">
+      <c r="O75" s="74" t="s">
         <v>166</v>
       </c>
-      <c r="P75" s="72"/>
-      <c r="Q75" s="72"/>
-      <c r="R75" s="72"/>
-      <c r="S75" s="72"/>
+      <c r="P75" s="74"/>
+      <c r="Q75" s="74"/>
+      <c r="R75" s="74"/>
+      <c r="S75" s="74"/>
       <c r="T75" s="3"/>
       <c r="U75" s="17"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A76" s="90" t="s">
+      <c r="A76" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="B76" s="90"/>
-      <c r="C76" s="133" t="s">
+      <c r="B76" s="92"/>
+      <c r="C76" s="135" t="s">
         <v>18</v>
       </c>
-      <c r="D76" s="133"/>
+      <c r="D76" s="135"/>
       <c r="E76" s="4" t="s">
         <v>19</v>
       </c>
@@ -3781,21 +3851,21 @@
       <c r="L76" s="3"/>
       <c r="M76" s="11"/>
       <c r="N76" s="17"/>
-      <c r="O76" s="72" t="s">
+      <c r="O76" s="74" t="s">
         <v>167</v>
       </c>
-      <c r="P76" s="72"/>
-      <c r="Q76" s="72"/>
-      <c r="R76" s="72"/>
-      <c r="S76" s="72"/>
+      <c r="P76" s="74"/>
+      <c r="Q76" s="74"/>
+      <c r="R76" s="74"/>
+      <c r="S76" s="74"/>
       <c r="T76" s="3"/>
       <c r="U76" s="17"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A77" s="90"/>
-      <c r="B77" s="90"/>
-      <c r="C77" s="133"/>
-      <c r="D77" s="133"/>
+      <c r="A77" s="92"/>
+      <c r="B77" s="92"/>
+      <c r="C77" s="135"/>
+      <c r="D77" s="135"/>
       <c r="E77" s="4" t="s">
         <v>21</v>
       </c>
@@ -3808,24 +3878,24 @@
       <c r="L77" s="3"/>
       <c r="M77" s="11"/>
       <c r="N77" s="17"/>
-      <c r="O77" s="72" t="s">
+      <c r="O77" s="74" t="s">
         <v>168</v>
       </c>
-      <c r="P77" s="72"/>
-      <c r="Q77" s="72"/>
-      <c r="R77" s="72"/>
-      <c r="S77" s="72"/>
+      <c r="P77" s="74"/>
+      <c r="Q77" s="74"/>
+      <c r="R77" s="74"/>
+      <c r="S77" s="74"/>
       <c r="T77" s="3"/>
       <c r="U77" s="17"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A78" s="90"/>
-      <c r="B78" s="90"/>
-      <c r="C78" s="134" t="s">
+      <c r="A78" s="92"/>
+      <c r="B78" s="92"/>
+      <c r="C78" s="136" t="s">
         <v>23</v>
       </c>
-      <c r="D78" s="134"/>
-      <c r="E78" s="134"/>
+      <c r="D78" s="136"/>
+      <c r="E78" s="136"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
@@ -3835,23 +3905,23 @@
       <c r="L78" s="3"/>
       <c r="M78" s="11"/>
       <c r="N78" s="17"/>
-      <c r="O78" s="72" t="s">
+      <c r="O78" s="74" t="s">
         <v>169</v>
       </c>
-      <c r="P78" s="72"/>
-      <c r="Q78" s="72"/>
-      <c r="R78" s="72"/>
-      <c r="S78" s="72"/>
+      <c r="P78" s="74"/>
+      <c r="Q78" s="74"/>
+      <c r="R78" s="74"/>
+      <c r="S78" s="74"/>
       <c r="T78" s="3"/>
       <c r="U78" s="17"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="90"/>
-      <c r="B79" s="90"/>
-      <c r="C79" s="130" t="s">
+      <c r="A79" s="92"/>
+      <c r="B79" s="92"/>
+      <c r="C79" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="D79" s="130"/>
+      <c r="D79" s="132"/>
       <c r="E79" s="6" t="s">
         <v>26</v>
       </c>
@@ -3864,21 +3934,21 @@
       <c r="L79" s="3"/>
       <c r="M79" s="11"/>
       <c r="N79" s="17"/>
-      <c r="O79" s="72" t="s">
+      <c r="O79" s="74" t="s">
         <v>157</v>
       </c>
-      <c r="P79" s="72"/>
-      <c r="Q79" s="72"/>
-      <c r="R79" s="72"/>
-      <c r="S79" s="72"/>
+      <c r="P79" s="74"/>
+      <c r="Q79" s="74"/>
+      <c r="R79" s="74"/>
+      <c r="S79" s="74"/>
       <c r="T79" s="3"/>
       <c r="U79" s="17"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A80" s="90"/>
-      <c r="B80" s="90"/>
-      <c r="C80" s="130"/>
-      <c r="D80" s="130"/>
+      <c r="A80" s="92"/>
+      <c r="B80" s="92"/>
+      <c r="C80" s="132"/>
+      <c r="D80" s="132"/>
       <c r="E80" s="6" t="s">
         <v>28</v>
       </c>
@@ -3891,21 +3961,21 @@
       <c r="L80" s="3"/>
       <c r="M80" s="11"/>
       <c r="N80" s="17"/>
-      <c r="O80" s="72" t="s">
+      <c r="O80" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="P80" s="72"/>
-      <c r="Q80" s="72"/>
-      <c r="R80" s="72"/>
-      <c r="S80" s="72"/>
+      <c r="P80" s="74"/>
+      <c r="Q80" s="74"/>
+      <c r="R80" s="74"/>
+      <c r="S80" s="74"/>
       <c r="T80" s="3"/>
       <c r="U80" s="17"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="90"/>
-      <c r="B81" s="90"/>
-      <c r="C81" s="130"/>
-      <c r="D81" s="130"/>
+      <c r="A81" s="92"/>
+      <c r="B81" s="92"/>
+      <c r="C81" s="132"/>
+      <c r="D81" s="132"/>
       <c r="E81" s="6" t="s">
         <v>29</v>
       </c>
@@ -3918,24 +3988,24 @@
       <c r="L81" s="3"/>
       <c r="M81" s="11"/>
       <c r="N81" s="17"/>
-      <c r="O81" s="72" t="s">
+      <c r="O81" s="74" t="s">
         <v>159</v>
       </c>
-      <c r="P81" s="72"/>
-      <c r="Q81" s="72"/>
-      <c r="R81" s="72"/>
-      <c r="S81" s="72"/>
+      <c r="P81" s="74"/>
+      <c r="Q81" s="74"/>
+      <c r="R81" s="74"/>
+      <c r="S81" s="74"/>
       <c r="T81" s="3"/>
       <c r="U81" s="17"/>
     </row>
     <row r="82" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="90"/>
-      <c r="B82" s="90"/>
-      <c r="C82" s="148" t="s">
+      <c r="A82" s="92"/>
+      <c r="B82" s="92"/>
+      <c r="C82" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="D82" s="148"/>
-      <c r="E82" s="148"/>
+      <c r="D82" s="150"/>
+      <c r="E82" s="150"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
       <c r="H82" s="12"/>
@@ -3945,24 +4015,24 @@
       <c r="L82" s="12"/>
       <c r="M82" s="11"/>
       <c r="N82" s="17"/>
-      <c r="O82" s="66" t="s">
+      <c r="O82" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="P82" s="66"/>
-      <c r="Q82" s="66"/>
-      <c r="R82" s="66"/>
-      <c r="S82" s="66"/>
-      <c r="T82" s="70"/>
+      <c r="P82" s="68"/>
+      <c r="Q82" s="68"/>
+      <c r="R82" s="68"/>
+      <c r="S82" s="68"/>
+      <c r="T82" s="72"/>
       <c r="U82" s="17"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A83" s="90"/>
-      <c r="B83" s="90"/>
-      <c r="C83" s="145" t="s">
+      <c r="A83" s="92"/>
+      <c r="B83" s="92"/>
+      <c r="C83" s="147" t="s">
         <v>54</v>
       </c>
-      <c r="D83" s="145"/>
-      <c r="E83" s="145"/>
+      <c r="D83" s="147"/>
+      <c r="E83" s="147"/>
       <c r="F83" s="3"/>
       <c r="G83" s="8"/>
       <c r="H83" s="8"/>
@@ -3972,22 +4042,22 @@
       <c r="L83" s="8"/>
       <c r="M83" s="11"/>
       <c r="N83" s="17"/>
-      <c r="O83" s="66"/>
-      <c r="P83" s="66"/>
-      <c r="Q83" s="66"/>
-      <c r="R83" s="66"/>
-      <c r="S83" s="66"/>
-      <c r="T83" s="71"/>
+      <c r="O83" s="68"/>
+      <c r="P83" s="68"/>
+      <c r="Q83" s="68"/>
+      <c r="R83" s="68"/>
+      <c r="S83" s="68"/>
+      <c r="T83" s="73"/>
       <c r="U83" s="17"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A84" s="137" t="s">
+      <c r="A84" s="139" t="s">
         <v>64</v>
       </c>
-      <c r="B84" s="137"/>
-      <c r="C84" s="137"/>
-      <c r="D84" s="137"/>
-      <c r="E84" s="137"/>
+      <c r="B84" s="139"/>
+      <c r="C84" s="139"/>
+      <c r="D84" s="139"/>
+      <c r="E84" s="139"/>
       <c r="F84" s="3"/>
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
@@ -3997,24 +4067,24 @@
       <c r="L84" s="8"/>
       <c r="M84" s="11"/>
       <c r="N84" s="17"/>
-      <c r="O84" s="72" t="s">
+      <c r="O84" s="74" t="s">
         <v>161</v>
       </c>
-      <c r="P84" s="72"/>
-      <c r="Q84" s="72"/>
-      <c r="R84" s="72"/>
-      <c r="S84" s="72"/>
+      <c r="P84" s="74"/>
+      <c r="Q84" s="74"/>
+      <c r="R84" s="74"/>
+      <c r="S84" s="74"/>
       <c r="T84" s="3"/>
       <c r="U84" s="17"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A85" s="137" t="s">
+      <c r="A85" s="139" t="s">
         <v>63</v>
       </c>
-      <c r="B85" s="137"/>
-      <c r="C85" s="137"/>
-      <c r="D85" s="137"/>
-      <c r="E85" s="137"/>
+      <c r="B85" s="139"/>
+      <c r="C85" s="139"/>
+      <c r="D85" s="139"/>
+      <c r="E85" s="139"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
       <c r="H85" s="8"/>
@@ -4024,24 +4094,24 @@
       <c r="L85" s="8"/>
       <c r="M85" s="11"/>
       <c r="N85" s="17"/>
-      <c r="O85" s="67" t="s">
+      <c r="O85" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="P85" s="68"/>
-      <c r="Q85" s="68"/>
-      <c r="R85" s="68"/>
-      <c r="S85" s="69"/>
+      <c r="P85" s="70"/>
+      <c r="Q85" s="70"/>
+      <c r="R85" s="70"/>
+      <c r="S85" s="71"/>
       <c r="T85" s="40"/>
       <c r="U85" s="17"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A86" s="137" t="s">
+      <c r="A86" s="139" t="s">
         <v>68</v>
       </c>
-      <c r="B86" s="137"/>
-      <c r="C86" s="137"/>
-      <c r="D86" s="137"/>
-      <c r="E86" s="137"/>
+      <c r="B86" s="139"/>
+      <c r="C86" s="139"/>
+      <c r="D86" s="139"/>
+      <c r="E86" s="139"/>
       <c r="F86" s="8"/>
       <c r="G86" s="3"/>
       <c r="H86" s="8"/>
@@ -4060,13 +4130,13 @@
       <c r="U86" s="17"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A87" s="137" t="s">
+      <c r="A87" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="B87" s="137"/>
-      <c r="C87" s="137"/>
-      <c r="D87" s="137"/>
-      <c r="E87" s="137"/>
+      <c r="B87" s="139"/>
+      <c r="C87" s="139"/>
+      <c r="D87" s="139"/>
+      <c r="E87" s="139"/>
       <c r="F87" s="3"/>
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
@@ -4103,86 +4173,86 @@
       <c r="U88" s="17"/>
     </row>
     <row r="89" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="106" t="s">
+      <c r="A89" s="108" t="s">
         <v>103</v>
       </c>
-      <c r="B89" s="107"/>
-      <c r="C89" s="107"/>
-      <c r="D89" s="107"/>
-      <c r="E89" s="108"/>
+      <c r="B89" s="109"/>
+      <c r="C89" s="109"/>
+      <c r="D89" s="109"/>
+      <c r="E89" s="110"/>
       <c r="F89" s="32"/>
-      <c r="G89" s="87" t="s">
+      <c r="G89" s="89" t="s">
         <v>104</v>
       </c>
-      <c r="H89" s="88"/>
-      <c r="I89" s="88"/>
-      <c r="J89" s="88"/>
-      <c r="K89" s="89"/>
+      <c r="H89" s="90"/>
+      <c r="I89" s="90"/>
+      <c r="J89" s="90"/>
+      <c r="K89" s="91"/>
       <c r="L89" s="32"/>
-      <c r="M89" s="74" t="s">
+      <c r="M89" s="76" t="s">
         <v>114</v>
       </c>
-      <c r="N89" s="75"/>
-      <c r="O89" s="75"/>
-      <c r="P89" s="75"/>
-      <c r="Q89" s="75"/>
-      <c r="R89" s="75"/>
-      <c r="S89" s="86"/>
+      <c r="N89" s="77"/>
+      <c r="O89" s="77"/>
+      <c r="P89" s="77"/>
+      <c r="Q89" s="77"/>
+      <c r="R89" s="77"/>
+      <c r="S89" s="88"/>
       <c r="T89" s="34"/>
       <c r="U89" s="17"/>
     </row>
     <row r="90" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="109"/>
-      <c r="B90" s="110"/>
-      <c r="C90" s="110"/>
-      <c r="D90" s="110"/>
-      <c r="E90" s="111"/>
+      <c r="A90" s="111"/>
+      <c r="B90" s="112"/>
+      <c r="C90" s="112"/>
+      <c r="D90" s="112"/>
+      <c r="E90" s="113"/>
       <c r="F90" s="32"/>
-      <c r="G90" s="47" t="s">
+      <c r="G90" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="H90" s="47"/>
-      <c r="I90" s="47"/>
-      <c r="J90" s="47"/>
-      <c r="K90" s="47" t="s">
+      <c r="H90" s="49"/>
+      <c r="I90" s="49"/>
+      <c r="J90" s="49"/>
+      <c r="K90" s="49" t="s">
         <v>10</v>
       </c>
       <c r="L90" s="32"/>
-      <c r="M90" s="56" t="s">
+      <c r="M90" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="N90" s="56"/>
+      <c r="N90" s="58"/>
       <c r="O90" s="29"/>
       <c r="P90" s="21" t="s">
         <v>38</v>
       </c>
       <c r="Q90" s="21"/>
-      <c r="R90" s="112" t="s">
+      <c r="R90" s="114" t="s">
         <v>10</v>
       </c>
-      <c r="S90" s="114"/>
+      <c r="S90" s="116"/>
       <c r="T90" s="32"/>
       <c r="U90" s="17"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A91" s="112" t="s">
+      <c r="A91" s="114" t="s">
         <v>75</v>
       </c>
-      <c r="B91" s="113"/>
-      <c r="C91" s="113"/>
-      <c r="D91" s="114"/>
-      <c r="E91" s="47" t="s">
+      <c r="B91" s="115"/>
+      <c r="C91" s="115"/>
+      <c r="D91" s="116"/>
+      <c r="E91" s="49" t="s">
         <v>10</v>
       </c>
       <c r="F91" s="32"/>
-      <c r="G91" s="47"/>
-      <c r="H91" s="47"/>
-      <c r="I91" s="47"/>
-      <c r="J91" s="47"/>
-      <c r="K91" s="47"/>
+      <c r="G91" s="49"/>
+      <c r="H91" s="49"/>
+      <c r="I91" s="49"/>
+      <c r="J91" s="49"/>
+      <c r="K91" s="49"/>
       <c r="L91" s="32"/>
-      <c r="M91" s="56"/>
-      <c r="N91" s="56"/>
+      <c r="M91" s="58"/>
+      <c r="N91" s="58"/>
       <c r="O91" s="21" t="s">
         <v>7</v>
       </c>
@@ -4192,311 +4262,311 @@
       <c r="Q91" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="R91" s="115"/>
-      <c r="S91" s="117"/>
+      <c r="R91" s="117"/>
+      <c r="S91" s="119"/>
       <c r="T91" s="32"/>
       <c r="U91" s="17"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A92" s="115"/>
-      <c r="B92" s="116"/>
-      <c r="C92" s="116"/>
-      <c r="D92" s="117"/>
-      <c r="E92" s="47"/>
+      <c r="A92" s="117"/>
+      <c r="B92" s="118"/>
+      <c r="C92" s="118"/>
+      <c r="D92" s="119"/>
+      <c r="E92" s="49"/>
       <c r="F92" s="32"/>
-      <c r="G92" s="90" t="s">
+      <c r="G92" s="92" t="s">
         <v>105</v>
       </c>
-      <c r="H92" s="90"/>
-      <c r="I92" s="91" t="s">
+      <c r="H92" s="92"/>
+      <c r="I92" s="93" t="s">
         <v>77</v>
       </c>
-      <c r="J92" s="91"/>
+      <c r="J92" s="93"/>
       <c r="K92" s="3"/>
       <c r="L92" s="32"/>
-      <c r="M92" s="62" t="s">
+      <c r="M92" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="N92" s="62"/>
+      <c r="N92" s="64"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
       <c r="Q92" s="3"/>
-      <c r="R92" s="64"/>
-      <c r="S92" s="65"/>
+      <c r="R92" s="66"/>
+      <c r="S92" s="67"/>
       <c r="T92" s="33" t="s">
         <v>85</v>
       </c>
       <c r="U92" s="17"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A93" s="90" t="s">
+      <c r="A93" s="92" t="s">
         <v>76</v>
       </c>
-      <c r="B93" s="90"/>
-      <c r="C93" s="97" t="s">
+      <c r="B93" s="92"/>
+      <c r="C93" s="99" t="s">
         <v>77</v>
       </c>
-      <c r="D93" s="98"/>
+      <c r="D93" s="100"/>
       <c r="E93" s="3"/>
       <c r="F93" s="32"/>
-      <c r="G93" s="90"/>
-      <c r="H93" s="90"/>
-      <c r="I93" s="92" t="s">
+      <c r="G93" s="92"/>
+      <c r="H93" s="92"/>
+      <c r="I93" s="94" t="s">
         <v>78</v>
       </c>
-      <c r="J93" s="92"/>
+      <c r="J93" s="94"/>
       <c r="K93" s="3"/>
       <c r="L93" s="32"/>
-      <c r="M93" s="63" t="s">
+      <c r="M93" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="N93" s="63"/>
+      <c r="N93" s="65"/>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
       <c r="Q93" s="3"/>
-      <c r="R93" s="64"/>
-      <c r="S93" s="65"/>
+      <c r="R93" s="66"/>
+      <c r="S93" s="67"/>
       <c r="T93" s="33" t="s">
         <v>85</v>
       </c>
       <c r="U93" s="17"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A94" s="90"/>
-      <c r="B94" s="90"/>
-      <c r="C94" s="101" t="s">
+      <c r="A94" s="92"/>
+      <c r="B94" s="92"/>
+      <c r="C94" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="D94" s="102"/>
+      <c r="D94" s="104"/>
       <c r="E94" s="3"/>
       <c r="F94" s="32"/>
-      <c r="G94" s="90"/>
-      <c r="H94" s="90"/>
-      <c r="I94" s="92" t="s">
+      <c r="G94" s="92"/>
+      <c r="H94" s="92"/>
+      <c r="I94" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="J94" s="92"/>
+      <c r="J94" s="94"/>
       <c r="K94" s="3"/>
       <c r="L94" s="32"/>
-      <c r="M94" s="63" t="s">
+      <c r="M94" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="N94" s="63"/>
+      <c r="N94" s="65"/>
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
       <c r="Q94" s="3"/>
-      <c r="R94" s="64"/>
-      <c r="S94" s="65"/>
+      <c r="R94" s="66"/>
+      <c r="S94" s="67"/>
       <c r="T94" s="33" t="s">
         <v>85</v>
       </c>
       <c r="U94" s="17"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A95" s="90"/>
-      <c r="B95" s="90"/>
-      <c r="C95" s="101" t="s">
+      <c r="A95" s="92"/>
+      <c r="B95" s="92"/>
+      <c r="C95" s="103" t="s">
         <v>79</v>
       </c>
-      <c r="D95" s="102"/>
+      <c r="D95" s="104"/>
       <c r="E95" s="3"/>
       <c r="F95" s="32"/>
-      <c r="G95" s="90"/>
-      <c r="H95" s="90"/>
-      <c r="I95" s="92" t="s">
+      <c r="G95" s="92"/>
+      <c r="H95" s="92"/>
+      <c r="I95" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="J95" s="92"/>
+      <c r="J95" s="94"/>
       <c r="K95" s="3"/>
       <c r="L95" s="32"/>
-      <c r="M95" s="63" t="s">
+      <c r="M95" s="65" t="s">
         <v>115</v>
       </c>
-      <c r="N95" s="63"/>
+      <c r="N95" s="65"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-      <c r="R95" s="64"/>
-      <c r="S95" s="65"/>
+      <c r="R95" s="66"/>
+      <c r="S95" s="67"/>
       <c r="T95" s="33" t="s">
         <v>85</v>
       </c>
       <c r="U95" s="17"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A96" s="90"/>
-      <c r="B96" s="90"/>
-      <c r="C96" s="101" t="s">
+      <c r="A96" s="92"/>
+      <c r="B96" s="92"/>
+      <c r="C96" s="103" t="s">
         <v>80</v>
       </c>
-      <c r="D96" s="102"/>
+      <c r="D96" s="104"/>
       <c r="E96" s="3"/>
       <c r="F96" s="32"/>
-      <c r="G96" s="90"/>
-      <c r="H96" s="90"/>
-      <c r="I96" s="93" t="s">
+      <c r="G96" s="92"/>
+      <c r="H96" s="92"/>
+      <c r="I96" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="J96" s="93"/>
+      <c r="J96" s="95"/>
       <c r="K96" s="3"/>
       <c r="L96" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="M96" s="61" t="s">
+      <c r="M96" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="N96" s="61"/>
+      <c r="N96" s="63"/>
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
-      <c r="R96" s="64"/>
-      <c r="S96" s="65"/>
+      <c r="R96" s="66"/>
+      <c r="S96" s="67"/>
       <c r="T96" s="33" t="s">
         <v>85</v>
       </c>
       <c r="U96" s="17"/>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A97" s="90"/>
-      <c r="B97" s="90"/>
-      <c r="C97" s="101" t="s">
+      <c r="A97" s="92"/>
+      <c r="B97" s="92"/>
+      <c r="C97" s="103" t="s">
         <v>81</v>
       </c>
-      <c r="D97" s="102"/>
+      <c r="D97" s="104"/>
       <c r="E97" s="3"/>
       <c r="F97" s="32"/>
-      <c r="G97" s="77" t="s">
+      <c r="G97" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="H97" s="77"/>
-      <c r="I97" s="77"/>
-      <c r="J97" s="77"/>
+      <c r="H97" s="79"/>
+      <c r="I97" s="79"/>
+      <c r="J97" s="79"/>
       <c r="K97" s="3"/>
       <c r="L97" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="M97" s="79" t="s">
+      <c r="M97" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="N97" s="80"/>
+      <c r="N97" s="82"/>
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
       <c r="Q97" s="3"/>
-      <c r="R97" s="64"/>
-      <c r="S97" s="65"/>
+      <c r="R97" s="66"/>
+      <c r="S97" s="67"/>
       <c r="T97" s="34"/>
       <c r="U97" s="17"/>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A98" s="90" t="s">
+      <c r="A98" s="92" t="s">
         <v>82</v>
       </c>
-      <c r="B98" s="90"/>
-      <c r="C98" s="97" t="s">
+      <c r="B98" s="92"/>
+      <c r="C98" s="99" t="s">
         <v>77</v>
       </c>
-      <c r="D98" s="98"/>
+      <c r="D98" s="100"/>
       <c r="E98" s="3"/>
       <c r="F98" s="32"/>
-      <c r="G98" s="77" t="s">
+      <c r="G98" s="79" t="s">
         <v>107</v>
       </c>
-      <c r="H98" s="77"/>
-      <c r="I98" s="77"/>
-      <c r="J98" s="77"/>
+      <c r="H98" s="79"/>
+      <c r="I98" s="79"/>
+      <c r="J98" s="79"/>
       <c r="K98" s="3"/>
       <c r="L98" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="M98" s="81" t="s">
+      <c r="M98" s="83" t="s">
         <v>141</v>
       </c>
-      <c r="N98" s="82"/>
+      <c r="N98" s="84"/>
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
-      <c r="R98" s="64"/>
-      <c r="S98" s="65"/>
+      <c r="R98" s="66"/>
+      <c r="S98" s="67"/>
       <c r="T98" s="34"/>
       <c r="U98" s="17"/>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A99" s="90"/>
-      <c r="B99" s="90"/>
-      <c r="C99" s="99" t="s">
+    <row r="99" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="92"/>
+      <c r="B99" s="92"/>
+      <c r="C99" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="D99" s="100"/>
+      <c r="D99" s="102"/>
       <c r="E99" s="3"/>
       <c r="F99" s="32"/>
-      <c r="G99" s="77" t="s">
+      <c r="G99" s="79" t="s">
         <v>108</v>
       </c>
-      <c r="H99" s="77"/>
-      <c r="I99" s="77"/>
-      <c r="J99" s="77"/>
+      <c r="H99" s="79"/>
+      <c r="I99" s="79"/>
+      <c r="J99" s="79"/>
       <c r="K99" s="3"/>
       <c r="L99" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="M99" s="78" t="s">
+      <c r="M99" s="80" t="s">
         <v>118</v>
       </c>
-      <c r="N99" s="78"/>
+      <c r="N99" s="80"/>
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
       <c r="Q99" s="3"/>
-      <c r="R99" s="64"/>
-      <c r="S99" s="65"/>
+      <c r="R99" s="66"/>
+      <c r="S99" s="67"/>
       <c r="T99" s="44"/>
       <c r="U99" s="17"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A100" s="90"/>
-      <c r="B100" s="90"/>
-      <c r="C100" s="99" t="s">
+      <c r="A100" s="92"/>
+      <c r="B100" s="92"/>
+      <c r="C100" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="D100" s="100"/>
+      <c r="D100" s="102"/>
       <c r="E100" s="3"/>
       <c r="F100" s="32"/>
-      <c r="G100" s="77" t="s">
+      <c r="G100" s="79" t="s">
         <v>109</v>
       </c>
-      <c r="H100" s="77"/>
-      <c r="I100" s="77"/>
-      <c r="J100" s="77"/>
+      <c r="H100" s="79"/>
+      <c r="I100" s="79"/>
+      <c r="J100" s="79"/>
       <c r="K100" s="3"/>
       <c r="L100" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="M100" s="77" t="s">
+      <c r="M100" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="N100" s="77"/>
+      <c r="N100" s="79"/>
       <c r="O100" s="3"/>
       <c r="P100" s="3"/>
       <c r="Q100" s="3"/>
-      <c r="R100" s="64"/>
-      <c r="S100" s="65"/>
+      <c r="R100" s="66"/>
+      <c r="S100" s="67"/>
       <c r="T100" s="34"/>
       <c r="U100" s="17"/>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A101" s="90"/>
-      <c r="B101" s="90"/>
-      <c r="C101" s="99" t="s">
+      <c r="A101" s="92"/>
+      <c r="B101" s="92"/>
+      <c r="C101" s="101" t="s">
         <v>80</v>
       </c>
-      <c r="D101" s="100"/>
+      <c r="D101" s="102"/>
       <c r="E101" s="3"/>
       <c r="F101" s="32"/>
-      <c r="G101" s="77" t="s">
+      <c r="G101" s="79" t="s">
         <v>110</v>
       </c>
-      <c r="H101" s="77"/>
-      <c r="I101" s="77"/>
-      <c r="J101" s="77"/>
+      <c r="H101" s="79"/>
+      <c r="I101" s="79"/>
+      <c r="J101" s="79"/>
       <c r="K101" s="3"/>
       <c r="L101" s="33" t="s">
         <v>85</v>
@@ -4514,20 +4584,20 @@
       <c r="U101" s="17"/>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A102" s="90"/>
-      <c r="B102" s="90"/>
-      <c r="C102" s="99" t="s">
+      <c r="A102" s="92"/>
+      <c r="B102" s="92"/>
+      <c r="C102" s="101" t="s">
         <v>81</v>
       </c>
-      <c r="D102" s="100"/>
+      <c r="D102" s="102"/>
       <c r="E102" s="3"/>
       <c r="F102" s="32"/>
-      <c r="G102" s="77" t="s">
+      <c r="G102" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="H102" s="77"/>
-      <c r="I102" s="77"/>
-      <c r="J102" s="77"/>
+      <c r="H102" s="79"/>
+      <c r="I102" s="79"/>
+      <c r="J102" s="79"/>
       <c r="K102" s="3"/>
       <c r="L102" s="33" t="s">
         <v>85</v>
@@ -4543,20 +4613,20 @@
       <c r="U102" s="17"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A103" s="94" t="s">
+      <c r="A103" s="96" t="s">
         <v>83</v>
       </c>
-      <c r="B103" s="95"/>
-      <c r="C103" s="95"/>
-      <c r="D103" s="96"/>
+      <c r="B103" s="97"/>
+      <c r="C103" s="97"/>
+      <c r="D103" s="98"/>
       <c r="E103" s="3"/>
       <c r="F103" s="32"/>
-      <c r="G103" s="77" t="s">
+      <c r="G103" s="79" t="s">
         <v>112</v>
       </c>
-      <c r="H103" s="77"/>
-      <c r="I103" s="77"/>
-      <c r="J103" s="77"/>
+      <c r="H103" s="79"/>
+      <c r="I103" s="79"/>
+      <c r="J103" s="79"/>
       <c r="K103" s="3"/>
       <c r="L103" s="33" t="s">
         <v>85</v>
@@ -4572,22 +4642,22 @@
       <c r="U103" s="17"/>
     </row>
     <row r="104" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="83" t="s">
+      <c r="A104" s="85" t="s">
         <v>84</v>
       </c>
-      <c r="B104" s="84"/>
-      <c r="C104" s="84"/>
-      <c r="D104" s="85"/>
+      <c r="B104" s="86"/>
+      <c r="C104" s="86"/>
+      <c r="D104" s="87"/>
       <c r="E104" s="3"/>
       <c r="F104" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G104" s="77" t="s">
+      <c r="G104" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="H104" s="77"/>
-      <c r="I104" s="77"/>
-      <c r="J104" s="77"/>
+      <c r="H104" s="79"/>
+      <c r="I104" s="79"/>
+      <c r="J104" s="79"/>
       <c r="K104" s="3"/>
       <c r="L104" s="34"/>
       <c r="M104" s="17"/>
@@ -4601,12 +4671,12 @@
       <c r="U104" s="17"/>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A105" s="83" t="s">
+      <c r="A105" s="85" t="s">
         <v>86</v>
       </c>
-      <c r="B105" s="84"/>
-      <c r="C105" s="84"/>
-      <c r="D105" s="85"/>
+      <c r="B105" s="86"/>
+      <c r="C105" s="86"/>
+      <c r="D105" s="87"/>
       <c r="E105" s="3"/>
       <c r="F105" s="33" t="s">
         <v>85</v>
@@ -4623,38 +4693,38 @@
       <c r="N105" s="17"/>
       <c r="O105" s="17"/>
       <c r="P105" s="17"/>
-      <c r="Q105" s="74" t="s">
+      <c r="Q105" s="76" t="s">
         <v>127</v>
       </c>
-      <c r="R105" s="75"/>
-      <c r="S105" s="75"/>
-      <c r="T105" s="75"/>
+      <c r="R105" s="77"/>
+      <c r="S105" s="77"/>
+      <c r="T105" s="77"/>
       <c r="U105" s="17"/>
     </row>
     <row r="106" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="83" t="s">
+      <c r="A106" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="B106" s="84"/>
-      <c r="C106" s="84"/>
-      <c r="D106" s="85"/>
+      <c r="B106" s="86"/>
+      <c r="C106" s="86"/>
+      <c r="D106" s="87"/>
       <c r="E106" s="3"/>
       <c r="F106" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G106" s="56" t="s">
+      <c r="G106" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="H106" s="56"/>
-      <c r="I106" s="56"/>
-      <c r="J106" s="56"/>
+      <c r="H106" s="58"/>
+      <c r="I106" s="58"/>
+      <c r="J106" s="58"/>
       <c r="K106" s="42"/>
       <c r="L106" s="17"/>
-      <c r="M106" s="46" t="s">
+      <c r="M106" s="48" t="s">
         <v>123</v>
       </c>
-      <c r="N106" s="46"/>
-      <c r="O106" s="46"/>
+      <c r="N106" s="48"/>
+      <c r="O106" s="48"/>
       <c r="P106" s="17"/>
       <c r="Q106" s="21" t="s">
         <v>128</v>
@@ -4671,27 +4741,27 @@
       <c r="U106" s="17"/>
     </row>
     <row r="107" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="83" t="s">
+      <c r="A107" s="85" t="s">
         <v>88</v>
       </c>
-      <c r="B107" s="84"/>
-      <c r="C107" s="84"/>
-      <c r="D107" s="85"/>
+      <c r="B107" s="86"/>
+      <c r="C107" s="86"/>
+      <c r="D107" s="87"/>
       <c r="E107" s="3"/>
       <c r="F107" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G107" s="56"/>
-      <c r="H107" s="56"/>
-      <c r="I107" s="56"/>
-      <c r="J107" s="56"/>
+      <c r="G107" s="58"/>
+      <c r="H107" s="58"/>
+      <c r="I107" s="58"/>
+      <c r="J107" s="58"/>
       <c r="K107" s="42"/>
       <c r="L107" s="17"/>
-      <c r="M107" s="46" t="s">
+      <c r="M107" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="N107" s="46"/>
-      <c r="O107" s="46"/>
+      <c r="N107" s="48"/>
+      <c r="O107" s="48"/>
       <c r="P107" s="17"/>
       <c r="Q107" s="37" t="s">
         <v>135</v>
@@ -4702,31 +4772,31 @@
       <c r="U107" s="17"/>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A108" s="83" t="s">
+      <c r="A108" s="85" t="s">
         <v>89</v>
       </c>
-      <c r="B108" s="84"/>
-      <c r="C108" s="84"/>
-      <c r="D108" s="85"/>
+      <c r="B108" s="86"/>
+      <c r="C108" s="86"/>
+      <c r="D108" s="87"/>
       <c r="E108" s="3"/>
       <c r="F108" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G108" s="56" t="s">
+      <c r="G108" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="H108" s="56"/>
-      <c r="I108" s="76" t="s">
+      <c r="H108" s="58"/>
+      <c r="I108" s="78" t="s">
         <v>121</v>
       </c>
-      <c r="J108" s="76"/>
+      <c r="J108" s="78"/>
       <c r="K108" s="30"/>
       <c r="L108" s="17"/>
-      <c r="M108" s="47" t="s">
+      <c r="M108" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="N108" s="47"/>
-      <c r="O108" s="47" t="s">
+      <c r="N108" s="49"/>
+      <c r="O108" s="49" t="s">
         <v>125</v>
       </c>
       <c r="P108" s="17"/>
@@ -4739,25 +4809,25 @@
       <c r="U108" s="17"/>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A109" s="83" t="s">
+      <c r="A109" s="85" t="s">
         <v>90</v>
       </c>
-      <c r="B109" s="84"/>
-      <c r="C109" s="84"/>
-      <c r="D109" s="85"/>
+      <c r="B109" s="86"/>
+      <c r="C109" s="86"/>
+      <c r="D109" s="87"/>
       <c r="E109" s="3"/>
       <c r="F109" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G109" s="56"/>
-      <c r="H109" s="56"/>
-      <c r="I109" s="76"/>
-      <c r="J109" s="76"/>
+      <c r="G109" s="58"/>
+      <c r="H109" s="58"/>
+      <c r="I109" s="78"/>
+      <c r="J109" s="78"/>
       <c r="K109" s="30"/>
       <c r="L109" s="17"/>
-      <c r="M109" s="47"/>
-      <c r="N109" s="47"/>
-      <c r="O109" s="47"/>
+      <c r="M109" s="49"/>
+      <c r="N109" s="49"/>
+      <c r="O109" s="49"/>
       <c r="P109" s="17"/>
       <c r="Q109" s="37" t="s">
         <v>137</v>
@@ -4768,28 +4838,28 @@
       <c r="U109" s="17"/>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A110" s="83" t="s">
+      <c r="A110" s="85" t="s">
         <v>91</v>
       </c>
-      <c r="B110" s="84"/>
-      <c r="C110" s="84"/>
-      <c r="D110" s="85"/>
+      <c r="B110" s="86"/>
+      <c r="C110" s="86"/>
+      <c r="D110" s="87"/>
       <c r="E110" s="3"/>
       <c r="F110" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G110" s="62" t="s">
+      <c r="G110" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="H110" s="62"/>
-      <c r="I110" s="73"/>
-      <c r="J110" s="73"/>
+      <c r="H110" s="64"/>
+      <c r="I110" s="75"/>
+      <c r="J110" s="75"/>
       <c r="K110" s="31"/>
       <c r="L110" s="17"/>
-      <c r="M110" s="63" t="s">
+      <c r="M110" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="N110" s="63"/>
+      <c r="N110" s="65"/>
       <c r="O110" s="3"/>
       <c r="P110" s="17"/>
       <c r="Q110" s="37" t="s">
@@ -4801,28 +4871,28 @@
       <c r="U110" s="17"/>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A111" s="83" t="s">
+      <c r="A111" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="B111" s="84"/>
-      <c r="C111" s="84"/>
-      <c r="D111" s="85"/>
+      <c r="B111" s="86"/>
+      <c r="C111" s="86"/>
+      <c r="D111" s="87"/>
       <c r="E111" s="3"/>
       <c r="F111" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G111" s="63" t="s">
+      <c r="G111" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="H111" s="63"/>
-      <c r="I111" s="73"/>
-      <c r="J111" s="73"/>
+      <c r="H111" s="65"/>
+      <c r="I111" s="75"/>
+      <c r="J111" s="75"/>
       <c r="K111" s="31"/>
       <c r="L111" s="17"/>
-      <c r="M111" s="63" t="s">
+      <c r="M111" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="N111" s="63"/>
+      <c r="N111" s="65"/>
       <c r="O111" s="3"/>
       <c r="P111" s="17"/>
       <c r="Q111" s="37" t="s">
@@ -4834,28 +4904,28 @@
       <c r="U111" s="17"/>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A112" s="83" t="s">
+      <c r="A112" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="B112" s="84"/>
-      <c r="C112" s="84"/>
-      <c r="D112" s="85"/>
+      <c r="B112" s="86"/>
+      <c r="C112" s="86"/>
+      <c r="D112" s="87"/>
       <c r="E112" s="3"/>
       <c r="F112" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G112" s="63" t="s">
+      <c r="G112" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="H112" s="63"/>
-      <c r="I112" s="73"/>
-      <c r="J112" s="73"/>
+      <c r="H112" s="65"/>
+      <c r="I112" s="75"/>
+      <c r="J112" s="75"/>
       <c r="K112" s="31"/>
       <c r="L112" s="17"/>
-      <c r="M112" s="63" t="s">
+      <c r="M112" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="N112" s="63"/>
+      <c r="N112" s="65"/>
       <c r="O112" s="3"/>
       <c r="P112" s="17"/>
       <c r="Q112" s="37" t="s">
@@ -4867,28 +4937,28 @@
       <c r="U112" s="17"/>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A113" s="83" t="s">
+      <c r="A113" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="B113" s="84"/>
-      <c r="C113" s="84"/>
-      <c r="D113" s="85"/>
+      <c r="B113" s="86"/>
+      <c r="C113" s="86"/>
+      <c r="D113" s="87"/>
       <c r="E113" s="3"/>
       <c r="F113" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G113" s="63" t="s">
+      <c r="G113" s="65" t="s">
         <v>115</v>
       </c>
-      <c r="H113" s="63"/>
-      <c r="I113" s="73"/>
-      <c r="J113" s="73"/>
+      <c r="H113" s="65"/>
+      <c r="I113" s="75"/>
+      <c r="J113" s="75"/>
       <c r="K113" s="31"/>
       <c r="L113" s="17"/>
-      <c r="M113" s="50" t="s">
+      <c r="M113" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="N113" s="50"/>
+      <c r="N113" s="52"/>
       <c r="O113" s="3"/>
       <c r="P113" s="17"/>
       <c r="Q113" s="38" t="s">
@@ -4900,22 +4970,22 @@
       <c r="U113" s="17"/>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A114" s="83" t="s">
+      <c r="A114" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="B114" s="84"/>
-      <c r="C114" s="84"/>
-      <c r="D114" s="85"/>
+      <c r="B114" s="86"/>
+      <c r="C114" s="86"/>
+      <c r="D114" s="87"/>
       <c r="E114" s="3"/>
       <c r="F114" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G114" s="50" t="s">
+      <c r="G114" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="H114" s="50"/>
-      <c r="I114" s="73"/>
-      <c r="J114" s="73"/>
+      <c r="H114" s="52"/>
+      <c r="I114" s="75"/>
+      <c r="J114" s="75"/>
       <c r="K114" s="31"/>
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
@@ -4928,13 +4998,13 @@
       <c r="T114" s="17"/>
       <c r="U114" s="17"/>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A115" s="83" t="s">
+    <row r="115" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="B115" s="84"/>
-      <c r="C115" s="84"/>
-      <c r="D115" s="85"/>
+      <c r="B115" s="86"/>
+      <c r="C115" s="86"/>
+      <c r="D115" s="87"/>
       <c r="E115" s="3"/>
       <c r="F115" s="33" t="s">
         <v>85</v>
@@ -4945,9 +5015,11 @@
       <c r="J115" s="17"/>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
-      <c r="M115" s="17"/>
-      <c r="N115" s="17"/>
-      <c r="O115" s="17"/>
+      <c r="M115" s="159" t="s">
+        <v>194</v>
+      </c>
+      <c r="N115" s="160"/>
+      <c r="O115" s="161"/>
       <c r="P115" s="17"/>
       <c r="Q115" s="17"/>
       <c r="R115" s="17"/>
@@ -4956,12 +5028,12 @@
       <c r="U115" s="17"/>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A116" s="83" t="s">
+      <c r="A116" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="B116" s="84"/>
-      <c r="C116" s="84"/>
-      <c r="D116" s="85"/>
+      <c r="B116" s="86"/>
+      <c r="C116" s="86"/>
+      <c r="D116" s="87"/>
       <c r="E116" s="3"/>
       <c r="F116" s="33" t="s">
         <v>85</v>
@@ -4972,9 +5044,9 @@
       <c r="J116" s="17"/>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
-      <c r="M116" s="17"/>
-      <c r="N116" s="17"/>
-      <c r="O116" s="17"/>
+      <c r="M116" s="162"/>
+      <c r="N116" s="163"/>
+      <c r="O116" s="164"/>
       <c r="P116" s="17"/>
       <c r="Q116" s="17"/>
       <c r="R116" s="17"/>
@@ -4983,12 +5055,12 @@
       <c r="U116" s="17"/>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A117" s="83" t="s">
+      <c r="A117" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="B117" s="84"/>
-      <c r="C117" s="84"/>
-      <c r="D117" s="85"/>
+      <c r="B117" s="86"/>
+      <c r="C117" s="86"/>
+      <c r="D117" s="87"/>
       <c r="E117" s="3"/>
       <c r="F117" s="33" t="s">
         <v>85</v>
@@ -4998,10 +5070,14 @@
       <c r="I117" s="17"/>
       <c r="J117" s="17"/>
       <c r="K117" s="17"/>
-      <c r="L117" s="17"/>
-      <c r="M117" s="17"/>
-      <c r="N117" s="17"/>
-      <c r="O117" s="17"/>
+      <c r="L117" s="46"/>
+      <c r="M117" s="63" t="s">
+        <v>120</v>
+      </c>
+      <c r="N117" s="63"/>
+      <c r="O117" s="47" t="s">
+        <v>125</v>
+      </c>
       <c r="P117" s="17"/>
       <c r="Q117" s="17"/>
       <c r="R117" s="17"/>
@@ -5010,12 +5086,12 @@
       <c r="U117" s="17"/>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A118" s="83" t="s">
+      <c r="A118" s="85" t="s">
         <v>99</v>
       </c>
-      <c r="B118" s="84"/>
-      <c r="C118" s="84"/>
-      <c r="D118" s="85"/>
+      <c r="B118" s="86"/>
+      <c r="C118" s="86"/>
+      <c r="D118" s="87"/>
       <c r="E118" s="3"/>
       <c r="F118" s="33" t="s">
         <v>85</v>
@@ -5026,9 +5102,11 @@
       <c r="J118" s="17"/>
       <c r="K118" s="17"/>
       <c r="L118" s="17"/>
-      <c r="M118" s="17"/>
-      <c r="N118" s="17"/>
-      <c r="O118" s="17"/>
+      <c r="M118" s="158" t="s">
+        <v>78</v>
+      </c>
+      <c r="N118" s="158"/>
+      <c r="O118" s="3"/>
       <c r="P118" s="17"/>
       <c r="Q118" s="17"/>
       <c r="R118" s="17"/>
@@ -5037,12 +5115,12 @@
       <c r="U118" s="17"/>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A119" s="83" t="s">
+      <c r="A119" s="85" t="s">
         <v>100</v>
       </c>
-      <c r="B119" s="84"/>
-      <c r="C119" s="84"/>
-      <c r="D119" s="85"/>
+      <c r="B119" s="86"/>
+      <c r="C119" s="86"/>
+      <c r="D119" s="87"/>
       <c r="E119" s="3"/>
       <c r="F119" s="33" t="s">
         <v>85</v>
@@ -5053,9 +5131,11 @@
       <c r="J119" s="17"/>
       <c r="K119" s="17"/>
       <c r="L119" s="17"/>
-      <c r="M119" s="17"/>
-      <c r="N119" s="17"/>
-      <c r="O119" s="17"/>
+      <c r="M119" s="158" t="s">
+        <v>79</v>
+      </c>
+      <c r="N119" s="158"/>
+      <c r="O119" s="3"/>
       <c r="P119" s="17"/>
       <c r="Q119" s="17"/>
       <c r="R119" s="17"/>
@@ -5064,12 +5144,12 @@
       <c r="U119" s="17"/>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A120" s="83" t="s">
+      <c r="A120" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="B120" s="84"/>
-      <c r="C120" s="84"/>
-      <c r="D120" s="85"/>
+      <c r="B120" s="86"/>
+      <c r="C120" s="86"/>
+      <c r="D120" s="87"/>
       <c r="E120" s="3"/>
       <c r="F120" s="33" t="s">
         <v>85</v>
@@ -5080,9 +5160,11 @@
       <c r="J120" s="17"/>
       <c r="K120" s="17"/>
       <c r="L120" s="17"/>
-      <c r="M120" s="17"/>
-      <c r="N120" s="17"/>
-      <c r="O120" s="17"/>
+      <c r="M120" s="158" t="s">
+        <v>80</v>
+      </c>
+      <c r="N120" s="158"/>
+      <c r="O120" s="3"/>
       <c r="P120" s="17"/>
       <c r="Q120" s="17"/>
       <c r="R120" s="17"/>
@@ -5105,9 +5187,11 @@
       <c r="J121" s="17"/>
       <c r="K121" s="17"/>
       <c r="L121" s="17"/>
-      <c r="M121" s="17"/>
-      <c r="N121" s="17"/>
-      <c r="O121" s="17"/>
+      <c r="M121" s="63" t="s">
+        <v>126</v>
+      </c>
+      <c r="N121" s="63"/>
+      <c r="O121" s="3"/>
       <c r="P121" s="17"/>
       <c r="Q121" s="17"/>
       <c r="R121" s="17"/>
@@ -5139,82 +5223,82 @@
       <c r="U122" s="17"/>
     </row>
     <row r="123" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="60" t="s">
+      <c r="A123" s="62" t="s">
         <v>170</v>
       </c>
-      <c r="B123" s="60"/>
-      <c r="C123" s="60"/>
+      <c r="B123" s="62"/>
+      <c r="C123" s="62"/>
       <c r="D123" s="17"/>
-      <c r="E123" s="55" t="s">
+      <c r="E123" s="57" t="s">
         <v>174</v>
       </c>
-      <c r="F123" s="55"/>
-      <c r="G123" s="55"/>
-      <c r="H123" s="55"/>
-      <c r="I123" s="55"/>
-      <c r="J123" s="55"/>
+      <c r="F123" s="57"/>
+      <c r="G123" s="57"/>
+      <c r="H123" s="57"/>
+      <c r="I123" s="57"/>
+      <c r="J123" s="57"/>
       <c r="K123" s="17"/>
-      <c r="L123" s="47" t="s">
+      <c r="L123" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="M123" s="47"/>
-      <c r="N123" s="47"/>
+      <c r="M123" s="49"/>
+      <c r="N123" s="49"/>
       <c r="O123" s="17"/>
-      <c r="P123" s="46" t="s">
+      <c r="P123" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="Q123" s="46"/>
-      <c r="R123" s="46"/>
-      <c r="S123" s="46"/>
-      <c r="T123" s="46"/>
+      <c r="Q123" s="48"/>
+      <c r="R123" s="48"/>
+      <c r="S123" s="48"/>
+      <c r="T123" s="48"/>
       <c r="U123" s="17"/>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A124" s="60"/>
-      <c r="B124" s="60"/>
-      <c r="C124" s="60"/>
+      <c r="A124" s="62"/>
+      <c r="B124" s="62"/>
+      <c r="C124" s="62"/>
       <c r="D124" s="17"/>
-      <c r="E124" s="47" t="s">
+      <c r="E124" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="F124" s="47"/>
-      <c r="G124" s="47" t="s">
+      <c r="F124" s="49"/>
+      <c r="G124" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="H124" s="47"/>
-      <c r="I124" s="47"/>
-      <c r="J124" s="47"/>
+      <c r="H124" s="49"/>
+      <c r="I124" s="49"/>
+      <c r="J124" s="49"/>
       <c r="K124" s="17"/>
-      <c r="L124" s="47" t="s">
+      <c r="L124" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="M124" s="47"/>
+      <c r="M124" s="49"/>
       <c r="N124" s="21" t="s">
         <v>125</v>
       </c>
       <c r="O124" s="17"/>
-      <c r="P124" s="47" t="s">
+      <c r="P124" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="Q124" s="47"/>
-      <c r="R124" s="47"/>
-      <c r="S124" s="47" t="s">
+      <c r="Q124" s="49"/>
+      <c r="R124" s="49"/>
+      <c r="S124" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="T124" s="47"/>
+      <c r="T124" s="49"/>
       <c r="U124" s="17"/>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A125" s="56" t="s">
+      <c r="A125" s="58" t="s">
         <v>173</v>
       </c>
-      <c r="B125" s="56"/>
+      <c r="B125" s="58"/>
       <c r="C125" s="20" t="s">
         <v>10</v>
       </c>
       <c r="D125" s="17"/>
-      <c r="E125" s="47"/>
-      <c r="F125" s="47"/>
+      <c r="E125" s="49"/>
+      <c r="F125" s="49"/>
       <c r="G125" s="21" t="s">
         <v>130</v>
       </c>
@@ -5228,134 +5312,134 @@
         <v>125</v>
       </c>
       <c r="K125" s="17"/>
-      <c r="L125" s="53" t="s">
+      <c r="L125" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="M125" s="53"/>
+      <c r="M125" s="55"/>
       <c r="N125" s="3"/>
       <c r="O125" s="17"/>
-      <c r="P125" s="51" t="s">
+      <c r="P125" s="53" t="s">
         <v>189</v>
       </c>
-      <c r="Q125" s="51"/>
-      <c r="R125" s="51"/>
-      <c r="S125" s="48"/>
-      <c r="T125" s="49"/>
+      <c r="Q125" s="53"/>
+      <c r="R125" s="53"/>
+      <c r="S125" s="50"/>
+      <c r="T125" s="51"/>
       <c r="U125" s="17"/>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A126" s="61" t="s">
+      <c r="A126" s="63" t="s">
         <v>171</v>
       </c>
-      <c r="B126" s="61"/>
+      <c r="B126" s="63"/>
       <c r="C126" s="3"/>
       <c r="D126" s="17"/>
-      <c r="E126" s="59" t="s">
+      <c r="E126" s="61" t="s">
         <v>175</v>
       </c>
-      <c r="F126" s="59"/>
+      <c r="F126" s="61"/>
       <c r="G126" s="3"/>
       <c r="H126" s="3"/>
       <c r="I126" s="3"/>
       <c r="J126" s="3"/>
       <c r="K126" s="17"/>
-      <c r="L126" s="54" t="s">
+      <c r="L126" s="56" t="s">
         <v>184</v>
       </c>
-      <c r="M126" s="54"/>
+      <c r="M126" s="56"/>
       <c r="N126" s="3"/>
       <c r="O126" s="17"/>
-      <c r="P126" s="51" t="s">
+      <c r="P126" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="Q126" s="51"/>
-      <c r="R126" s="51"/>
-      <c r="S126" s="48"/>
-      <c r="T126" s="49"/>
+      <c r="Q126" s="53"/>
+      <c r="R126" s="53"/>
+      <c r="S126" s="50"/>
+      <c r="T126" s="51"/>
       <c r="U126" s="17"/>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A127" s="57" t="s">
+      <c r="A127" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="B127" s="57"/>
+      <c r="B127" s="59"/>
       <c r="C127" s="3"/>
       <c r="D127" s="17"/>
-      <c r="E127" s="59" t="s">
+      <c r="E127" s="61" t="s">
         <v>176</v>
       </c>
-      <c r="F127" s="59"/>
+      <c r="F127" s="61"/>
       <c r="G127" s="3"/>
       <c r="H127" s="3"/>
       <c r="I127" s="3"/>
       <c r="J127" s="3"/>
       <c r="K127" s="17"/>
-      <c r="L127" s="54" t="s">
+      <c r="L127" s="56" t="s">
         <v>185</v>
       </c>
-      <c r="M127" s="54"/>
+      <c r="M127" s="56"/>
       <c r="N127" s="3"/>
       <c r="O127" s="17"/>
-      <c r="P127" s="52" t="s">
+      <c r="P127" s="54" t="s">
         <v>191</v>
       </c>
-      <c r="Q127" s="52"/>
-      <c r="R127" s="52"/>
-      <c r="S127" s="48"/>
-      <c r="T127" s="49"/>
+      <c r="Q127" s="54"/>
+      <c r="R127" s="54"/>
+      <c r="S127" s="50"/>
+      <c r="T127" s="51"/>
       <c r="U127" s="17"/>
     </row>
     <row r="128" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="57" t="s">
+      <c r="A128" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="B128" s="57"/>
+      <c r="B128" s="59"/>
       <c r="C128" s="3"/>
       <c r="D128" s="17"/>
-      <c r="E128" s="59" t="s">
+      <c r="E128" s="61" t="s">
         <v>177</v>
       </c>
-      <c r="F128" s="59"/>
+      <c r="F128" s="61"/>
       <c r="G128" s="3"/>
       <c r="H128" s="3"/>
       <c r="I128" s="3"/>
       <c r="J128" s="3"/>
       <c r="K128" s="17"/>
-      <c r="L128" s="54" t="s">
+      <c r="L128" s="56" t="s">
         <v>186</v>
       </c>
-      <c r="M128" s="54"/>
+      <c r="M128" s="56"/>
       <c r="N128" s="3"/>
       <c r="O128" s="17"/>
-      <c r="P128" s="50" t="s">
+      <c r="P128" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="Q128" s="50"/>
-      <c r="R128" s="50"/>
-      <c r="S128" s="48"/>
-      <c r="T128" s="49"/>
+      <c r="Q128" s="52"/>
+      <c r="R128" s="52"/>
+      <c r="S128" s="50"/>
+      <c r="T128" s="51"/>
       <c r="U128" s="17"/>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A129" s="57" t="s">
+      <c r="A129" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="B129" s="57"/>
+      <c r="B129" s="59"/>
       <c r="C129" s="3"/>
       <c r="D129" s="17"/>
-      <c r="E129" s="59" t="s">
+      <c r="E129" s="61" t="s">
         <v>178</v>
       </c>
-      <c r="F129" s="59"/>
+      <c r="F129" s="61"/>
       <c r="G129" s="3"/>
       <c r="H129" s="3"/>
       <c r="I129" s="3"/>
       <c r="J129" s="3"/>
       <c r="K129" s="17"/>
-      <c r="L129" s="54" t="s">
+      <c r="L129" s="56" t="s">
         <v>187</v>
       </c>
-      <c r="M129" s="54"/>
+      <c r="M129" s="56"/>
       <c r="N129" s="3"/>
       <c r="O129" s="17"/>
       <c r="P129" s="43"/>
@@ -5366,25 +5450,25 @@
       <c r="U129" s="17"/>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A130" s="57" t="s">
+      <c r="A130" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="B130" s="57"/>
+      <c r="B130" s="59"/>
       <c r="C130" s="3"/>
       <c r="D130" s="17"/>
-      <c r="E130" s="59" t="s">
+      <c r="E130" s="61" t="s">
         <v>179</v>
       </c>
-      <c r="F130" s="59"/>
+      <c r="F130" s="61"/>
       <c r="G130" s="3"/>
       <c r="H130" s="3"/>
       <c r="I130" s="3"/>
       <c r="J130" s="3"/>
       <c r="K130" s="17"/>
-      <c r="L130" s="50" t="s">
+      <c r="L130" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="M130" s="50"/>
+      <c r="M130" s="52"/>
       <c r="N130" s="3"/>
       <c r="O130" s="17"/>
       <c r="P130" s="17"/>
@@ -5395,16 +5479,16 @@
       <c r="U130" s="17"/>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A131" s="50" t="s">
+      <c r="A131" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="B131" s="50"/>
+      <c r="B131" s="52"/>
       <c r="C131" s="40"/>
       <c r="D131" s="17"/>
-      <c r="E131" s="59" t="s">
+      <c r="E131" s="61" t="s">
         <v>180</v>
       </c>
-      <c r="F131" s="59"/>
+      <c r="F131" s="61"/>
       <c r="G131" s="3"/>
       <c r="H131" s="3"/>
       <c r="I131" s="3"/>
@@ -5426,10 +5510,10 @@
       <c r="B132" s="17"/>
       <c r="C132" s="17"/>
       <c r="D132" s="17"/>
-      <c r="E132" s="58" t="s">
+      <c r="E132" s="60" t="s">
         <v>181</v>
       </c>
-      <c r="F132" s="58"/>
+      <c r="F132" s="60"/>
       <c r="G132" s="3"/>
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
@@ -5451,10 +5535,10 @@
       <c r="B133" s="17"/>
       <c r="C133" s="17"/>
       <c r="D133" s="17"/>
-      <c r="E133" s="50" t="s">
+      <c r="E133" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="F133" s="50"/>
+      <c r="F133" s="52"/>
       <c r="G133" s="3"/>
       <c r="H133" s="3"/>
       <c r="I133" s="3"/>
@@ -5656,7 +5740,7 @@
       <c r="U141" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="255">
+  <mergeCells count="262">
     <mergeCell ref="C83:E83"/>
     <mergeCell ref="A84:E84"/>
     <mergeCell ref="A85:E85"/>
@@ -5728,6 +5812,9 @@
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="A26:F27"/>
+    <mergeCell ref="A16:C17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:F18"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="L16:P16"/>
     <mergeCell ref="L17:L18"/>
@@ -5738,10 +5825,8 @@
     <mergeCell ref="A5:F6"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="C2:F2"/>
-    <mergeCell ref="A16:C18"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
     <mergeCell ref="A7:C9"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
@@ -5893,8 +5978,6 @@
     <mergeCell ref="G111:H111"/>
     <mergeCell ref="G112:H112"/>
     <mergeCell ref="G113:H113"/>
-    <mergeCell ref="P123:T123"/>
-    <mergeCell ref="S124:T124"/>
     <mergeCell ref="S125:T125"/>
     <mergeCell ref="S126:T126"/>
     <mergeCell ref="S127:T127"/>
@@ -5912,6 +5995,14 @@
     <mergeCell ref="L127:M127"/>
     <mergeCell ref="L128:M128"/>
     <mergeCell ref="L129:M129"/>
+    <mergeCell ref="M117:N117"/>
+    <mergeCell ref="M118:N118"/>
+    <mergeCell ref="M119:N119"/>
+    <mergeCell ref="M120:N120"/>
+    <mergeCell ref="M121:N121"/>
+    <mergeCell ref="P123:T123"/>
+    <mergeCell ref="S124:T124"/>
+    <mergeCell ref="M115:O116"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="7.874015748031496E-2" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="78" orientation="portrait" r:id="rId1"/>
